--- a/database_penyimpanan_aman/database_opname_parameter.xlsx
+++ b/database_penyimpanan_aman/database_opname_parameter.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\98 PROFORMA INVOICE\Dashboard Proforma Invoice General Services\database_penyimpanan_aman\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAC2B94E-81BC-4D2B-B128-893D82643EB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BABC646-2381-4246-B6B2-6BB7AF71A6BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="14">
   <si>
     <t>doc_key</t>
   </si>
@@ -31,13 +31,37 @@
     <t>Update Terakhir</t>
   </si>
   <si>
+    <t>Item Index</t>
+  </si>
+  <si>
+    <t>Lokasi Office</t>
+  </si>
+  <si>
+    <t>Tanggal Opname</t>
+  </si>
+  <si>
+    <t>Volume PO</t>
+  </si>
+  <si>
+    <t>Unit Price</t>
+  </si>
+  <si>
+    <t>Volume Previous</t>
+  </si>
+  <si>
+    <t>Volume Aktual</t>
+  </si>
+  <si>
     <t>opname_016_BSS-JOB_WS_VIII_2026_4500011739</t>
   </si>
   <si>
-    <t>{"lokasi_office": "Luwuk", "tanggal_opname": "2026-08-31", "items": {"1": {"po_vol": 18300.0, "unit_price": 65000.0, "prev_vol": 0.0, "current_vol": 2578.0}, "2": {"po_vol": 9200.0, "unit_price": 33000.0, "prev_vol": 0.0, "current_vol": 1157.0}}, "logo_1": null, "logo_2": null, "ttd_1": null, "ttd_2": null}</t>
-  </si>
-  <si>
-    <t>2026-09-19 18:30:16</t>
+    <t>2026-09-19 18:46:10</t>
+  </si>
+  <si>
+    <t>Luwuk</t>
+  </si>
+  <si>
+    <t>2026-08-31</t>
   </si>
 </sst>
 </file>
@@ -377,15 +401,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="37.46484375" customWidth="1"/>
-    <col min="2" max="2" width="24.46484375" customWidth="1"/>
-    <col min="3" max="3" width="18.59765625" customWidth="1"/>
+    <col min="1" max="1" width="44.9296875" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="17.6640625" customWidth="1"/>
+    <col min="4" max="4" width="11.796875" customWidth="1"/>
+    <col min="5" max="5" width="13.19921875" customWidth="1"/>
+    <col min="6" max="6" width="14.19921875" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
+    <col min="8" max="8" width="10.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -395,16 +424,84 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>5</v>
+        <v>11</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2">
+        <v>18300</v>
+      </c>
+      <c r="H2">
+        <v>65000</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>2578</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3">
+        <v>9200</v>
+      </c>
+      <c r="H3">
+        <v>33000</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>1157</v>
       </c>
     </row>
   </sheetData>

--- a/database_penyimpanan_aman/database_opname_parameter.xlsx
+++ b/database_penyimpanan_aman/database_opname_parameter.xlsx
@@ -1,85 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\98 PROFORMA INVOICE\Dashboard Proforma Invoice General Services\database_penyimpanan_aman\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BABC646-2381-4246-B6B2-6BB7AF71A6BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="14">
-  <si>
-    <t>doc_key</t>
-  </si>
-  <si>
-    <t>payload</t>
-  </si>
-  <si>
-    <t>Update Terakhir</t>
-  </si>
-  <si>
-    <t>Item Index</t>
-  </si>
-  <si>
-    <t>Lokasi Office</t>
-  </si>
-  <si>
-    <t>Tanggal Opname</t>
-  </si>
-  <si>
-    <t>Volume PO</t>
-  </si>
-  <si>
-    <t>Unit Price</t>
-  </si>
-  <si>
-    <t>Volume Previous</t>
-  </si>
-  <si>
-    <t>Volume Aktual</t>
-  </si>
-  <si>
-    <t>opname_016_BSS-JOB_WS_VIII_2026_4500011739</t>
-  </si>
-  <si>
-    <t>2026-09-19 18:46:10</t>
-  </si>
-  <si>
-    <t>Luwuk</t>
-  </si>
-  <si>
-    <t>2026-08-31</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -98,21 +47,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -400,108 +408,368 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J3"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="1" max="1" width="44.9296875" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="17.6640625" customWidth="1"/>
-    <col min="4" max="4" width="11.796875" customWidth="1"/>
-    <col min="5" max="5" width="13.19921875" customWidth="1"/>
-    <col min="6" max="6" width="14.19921875" customWidth="1"/>
-    <col min="7" max="7" width="12" customWidth="1"/>
-    <col min="8" max="8" width="10.6640625" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A1" t="s">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>doc_key</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>payload</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Update Terakhir</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Item Index</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Lokasi Office</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Tanggal Opname</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Volume PO</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Unit Price</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Volume Previous</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Volume Aktual</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>opname_016_BSS-JOB_WS_VIII_2026_4500011739</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-09-19 18:46:10</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>18300</v>
+      </c>
+      <c r="H2" t="n">
+        <v>65000</v>
+      </c>
+      <c r="I2" t="n">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="J2" t="n">
+        <v>2578</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>opname_016_BSS-JOB_WS_VIII_2026_4500011739</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-09-19 18:46:10</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>9200</v>
+      </c>
+      <c r="H3" t="n">
+        <v>33000</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1157</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>opname_023_BSS-JOB_WS_VIII_2026_4500011739</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-09-20 07:36:08</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>240</v>
+      </c>
+      <c r="H4" t="n">
+        <v>750000</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>opname_022_BSS-JOB_WS_IX_2026_4500011739</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-09-20 07:56:18</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>240</v>
+      </c>
+      <c r="H5" t="n">
+        <v>750000</v>
+      </c>
+      <c r="I5" t="n">
+        <v>22</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>opname_022_BSS-JOB_WS_IX_2026_4500011739</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-09-20 07:56:18</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>120</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>opname_023A_BSS-JOB_WS_VIII_2026_4500011739</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-09-20 08:25:47</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>120</v>
+      </c>
+      <c r="H7" t="n">
+        <v>500000</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>opname_023A_BSS-JOB_WS_VIII_2026_4500011739</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-09-20 08:25:47</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>120</v>
+      </c>
+      <c r="H8" t="n">
+        <v>500000</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>opname_023A_BSS-JOB_WS_VIII_2026_4500011739</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-09-20 08:25:47</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2">
-        <v>18300</v>
-      </c>
-      <c r="H2">
-        <v>65000</v>
-      </c>
-      <c r="I2">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>120</v>
+      </c>
+      <c r="H9" t="n">
+        <v>500000</v>
+      </c>
+      <c r="I9" t="n">
         <v>0</v>
       </c>
-      <c r="J2">
-        <v>2578</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="E3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3">
-        <v>9200</v>
-      </c>
-      <c r="H3">
-        <v>33000</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>1157</v>
+      <c r="J9" t="n">
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/database_penyimpanan_aman/database_opname_parameter.xlsx
+++ b/database_penyimpanan_aman/database_opname_parameter.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -772,6 +772,880 @@
         <v>24</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>opname_024_BSS-JOB_WS_VIII_2026_4500011739</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-09-20 09:41:22</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>13</v>
+      </c>
+      <c r="H10" t="n">
+        <v>750000</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>opname_024_BSS-JOB_WS_VIII_2026_4500011739</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-09-20 09:41:22</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>120</v>
+      </c>
+      <c r="H11" t="n">
+        <v>750000</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>opname_024_BSS-JOB_WS_VIII_2026_4500011739</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-09-20 09:41:22</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>107</v>
+      </c>
+      <c r="H12" t="n">
+        <v>750000</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>opname_024_BSS-JOB_WS_VIII_2026_4500011739</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-09-20 09:41:22</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>4</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>120</v>
+      </c>
+      <c r="H13" t="n">
+        <v>650000</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>opname_024_BSS-JOB_WS_VIII_2026_4500011739</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-09-20 09:41:22</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>5</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>120</v>
+      </c>
+      <c r="H14" t="n">
+        <v>650000</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>opname_024_BSS-JOB_WS_VIII_2026_4500011739</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-09-20 09:41:22</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>6</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>240</v>
+      </c>
+      <c r="H15" t="n">
+        <v>600000</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>opname_024_BSS-JOB_WS_VIII_2026_4500011739</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-09-20 09:41:22</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>7</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>240</v>
+      </c>
+      <c r="H16" t="n">
+        <v>600000</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>opname_024A_BSS-JOB_WS_VIII_2026_4500011739</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-09-20 09:57:06</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>120</v>
+      </c>
+      <c r="H17" t="n">
+        <v>500000</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>opname_025_BSS-JOB_WS_VIII_2026_4500011739</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:18:11</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>4</v>
+      </c>
+      <c r="H18" t="n">
+        <v>25000000</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>opname_025_BSS-JOB_WS_VIII_2026_4500011739</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:18:11</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>4</v>
+      </c>
+      <c r="H19" t="n">
+        <v>17500000</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>opname_025_BSS-JOB_WS_VIII_2026_4500011739</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:18:11</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>3</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>4</v>
+      </c>
+      <c r="H20" t="n">
+        <v>60000000</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>opname_025_BSS-JOB_WS_VIII_2026_4500011739</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:18:11</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>4</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>4</v>
+      </c>
+      <c r="H21" t="n">
+        <v>60000000</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>opname_025_BSS-JOB_WS_VIII_2026_4500011739</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:18:11</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>5</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>4</v>
+      </c>
+      <c r="H22" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>opname_025_BSS-JOB_WS_VIII_2026_4500011739</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:18:11</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>6</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>4</v>
+      </c>
+      <c r="H23" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>opname_026_BSS-JOB_WS_VIII_2026_4500011739</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:36:52</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>120</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>opname_026_BSS-JOB_WS_VIII_2026_4500011739</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:36:52</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>2</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>120</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>opname_026_BSS-JOB_WS_VIII_2026_4500011739</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:36:52</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>3</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>116</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>opname_026_BSS-JOB_WS_VIII_2026_4500011739</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:36:52</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>4</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>4</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>opname_026_BSS-JOB_WS_VIII_2026_4500011739</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:36:52</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>5</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>120</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>opname_026_BSS-JOB_WS_VIII_2026_4500011739</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2026-09-20 10:36:52</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>6</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>120</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>opname_027_BSS-JOB_WS_VIII_2026_4500011739</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2026-09-20 11:39:01</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>7</v>
+      </c>
+      <c r="H30" t="n">
+        <v>8500000</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>opname_027_BSS-JOB_WS_VIII_2026_4500011739</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2026-09-20 11:39:01</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>2</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>113</v>
+      </c>
+      <c r="H31" t="n">
+        <v>8500000</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>opname_027_BSS-JOB_WS_VIII_2026_4500011739</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2026-09-20 11:39:01</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>3</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>120</v>
+      </c>
+      <c r="H32" t="n">
+        <v>2750000</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database_penyimpanan_aman/database_opname_parameter.xlsx
+++ b/database_penyimpanan_aman/database_opname_parameter.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\98 PROFORMA INVOICE\Dashboard Proforma Invoice General Services\database_penyimpanan_aman\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EFBA480-3F22-41F3-A6ED-FA23632CE494}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{840548E7-4549-4B56-B380-A90D8E84361A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -122,7 +122,17 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+  </numFmts>
+  <fonts count="2" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -148,13 +158,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -462,12 +475,12 @@
     <col min="2" max="2" width="9.9296875" customWidth="1"/>
     <col min="3" max="3" width="19.796875" customWidth="1"/>
     <col min="6" max="6" width="12.19921875" customWidth="1"/>
-    <col min="7" max="7" width="12.1328125" customWidth="1"/>
-    <col min="8" max="8" width="14.46484375" customWidth="1"/>
+    <col min="7" max="7" width="12.1328125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="14.46484375" style="1" customWidth="1"/>
     <col min="9" max="10" width="14.19921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:10" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -486,10 +499,10 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
       <c r="I1" t="s">
@@ -515,10 +528,10 @@
       <c r="F2" t="s">
         <v>13</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="1">
         <v>18300</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="1">
         <v>65000</v>
       </c>
       <c r="I2">
@@ -544,10 +557,10 @@
       <c r="F3" t="s">
         <v>13</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="1">
         <v>9200</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="1">
         <v>33000</v>
       </c>
       <c r="I3">
@@ -573,10 +586,10 @@
       <c r="F4" t="s">
         <v>13</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="1">
         <v>240</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="1">
         <v>750000</v>
       </c>
       <c r="I4">
@@ -602,10 +615,10 @@
       <c r="F5" t="s">
         <v>18</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="1">
         <v>240</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="1">
         <v>750000</v>
       </c>
       <c r="I5">
@@ -631,10 +644,10 @@
       <c r="F6" t="s">
         <v>18</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="1">
         <v>120</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="1">
         <v>1600000</v>
       </c>
       <c r="I6">
@@ -660,10 +673,10 @@
       <c r="F7" t="s">
         <v>13</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="1">
         <v>120</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="1">
         <v>500000</v>
       </c>
       <c r="I7">
@@ -689,10 +702,10 @@
       <c r="F8" t="s">
         <v>13</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="1">
         <v>120</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="1">
         <v>500000</v>
       </c>
       <c r="I8">
@@ -718,10 +731,10 @@
       <c r="F9" t="s">
         <v>13</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="1">
         <v>120</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="1">
         <v>500000</v>
       </c>
       <c r="I9">
@@ -747,10 +760,10 @@
       <c r="F10" t="s">
         <v>13</v>
       </c>
-      <c r="G10">
-        <v>13</v>
-      </c>
-      <c r="H10">
+      <c r="G10" s="1">
+        <v>13</v>
+      </c>
+      <c r="H10" s="1">
         <v>750000</v>
       </c>
       <c r="I10">
@@ -776,10 +789,10 @@
       <c r="F11" t="s">
         <v>13</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="1">
         <v>120</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="1">
         <v>750000</v>
       </c>
       <c r="I11">
@@ -805,10 +818,10 @@
       <c r="F12" t="s">
         <v>13</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="1">
         <v>107</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="1">
         <v>750000</v>
       </c>
       <c r="I12">
@@ -834,10 +847,10 @@
       <c r="F13" t="s">
         <v>13</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="1">
         <v>120</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="1">
         <v>650000</v>
       </c>
       <c r="I13">
@@ -863,10 +876,10 @@
       <c r="F14" t="s">
         <v>13</v>
       </c>
-      <c r="G14">
+      <c r="G14" s="1">
         <v>120</v>
       </c>
-      <c r="H14">
+      <c r="H14" s="1">
         <v>650000</v>
       </c>
       <c r="I14">
@@ -892,10 +905,10 @@
       <c r="F15" t="s">
         <v>13</v>
       </c>
-      <c r="G15">
+      <c r="G15" s="1">
         <v>240</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="1">
         <v>600000</v>
       </c>
       <c r="I15">
@@ -921,10 +934,10 @@
       <c r="F16" t="s">
         <v>13</v>
       </c>
-      <c r="G16">
+      <c r="G16" s="1">
         <v>240</v>
       </c>
-      <c r="H16">
+      <c r="H16" s="1">
         <v>600000</v>
       </c>
       <c r="I16">
@@ -950,10 +963,10 @@
       <c r="F17" t="s">
         <v>25</v>
       </c>
-      <c r="G17">
+      <c r="G17" s="1">
         <v>120</v>
       </c>
-      <c r="H17">
+      <c r="H17" s="1">
         <v>500000</v>
       </c>
       <c r="I17">
@@ -979,10 +992,10 @@
       <c r="F18" t="s">
         <v>13</v>
       </c>
-      <c r="G18">
+      <c r="G18" s="1">
         <v>4</v>
       </c>
-      <c r="H18">
+      <c r="H18" s="1">
         <v>25000000</v>
       </c>
       <c r="I18">
@@ -1008,10 +1021,10 @@
       <c r="F19" t="s">
         <v>13</v>
       </c>
-      <c r="G19">
+      <c r="G19" s="1">
         <v>4</v>
       </c>
-      <c r="H19">
+      <c r="H19" s="1">
         <v>17500000</v>
       </c>
       <c r="I19">
@@ -1037,10 +1050,10 @@
       <c r="F20" t="s">
         <v>13</v>
       </c>
-      <c r="G20">
+      <c r="G20" s="1">
         <v>4</v>
       </c>
-      <c r="H20">
+      <c r="H20" s="1">
         <v>60000000</v>
       </c>
       <c r="I20">
@@ -1066,10 +1079,10 @@
       <c r="F21" t="s">
         <v>13</v>
       </c>
-      <c r="G21">
+      <c r="G21" s="1">
         <v>4</v>
       </c>
-      <c r="H21">
+      <c r="H21" s="1">
         <v>60000000</v>
       </c>
       <c r="I21">
@@ -1095,10 +1108,10 @@
       <c r="F22" t="s">
         <v>13</v>
       </c>
-      <c r="G22">
+      <c r="G22" s="1">
         <v>4</v>
       </c>
-      <c r="H22">
+      <c r="H22" s="1">
         <v>15000000</v>
       </c>
       <c r="I22">
@@ -1124,10 +1137,10 @@
       <c r="F23" t="s">
         <v>13</v>
       </c>
-      <c r="G23">
+      <c r="G23" s="1">
         <v>4</v>
       </c>
-      <c r="H23">
+      <c r="H23" s="1">
         <v>15000000</v>
       </c>
       <c r="I23">
@@ -1153,10 +1166,10 @@
       <c r="F24" t="s">
         <v>13</v>
       </c>
-      <c r="G24">
+      <c r="G24" s="1">
         <v>120</v>
       </c>
-      <c r="H24">
+      <c r="H24" s="1">
         <v>1600000</v>
       </c>
       <c r="I24">
@@ -1182,10 +1195,10 @@
       <c r="F25" t="s">
         <v>13</v>
       </c>
-      <c r="G25">
+      <c r="G25" s="1">
         <v>120</v>
       </c>
-      <c r="H25">
+      <c r="H25" s="1">
         <v>1600000</v>
       </c>
       <c r="I25">
@@ -1211,10 +1224,10 @@
       <c r="F26" t="s">
         <v>13</v>
       </c>
-      <c r="G26">
+      <c r="G26" s="1">
         <v>116</v>
       </c>
-      <c r="H26">
+      <c r="H26" s="1">
         <v>1600000</v>
       </c>
       <c r="I26">
@@ -1240,10 +1253,10 @@
       <c r="F27" t="s">
         <v>13</v>
       </c>
-      <c r="G27">
+      <c r="G27" s="1">
         <v>4</v>
       </c>
-      <c r="H27">
+      <c r="H27" s="1">
         <v>1600000</v>
       </c>
       <c r="I27">
@@ -1269,10 +1282,10 @@
       <c r="F28" t="s">
         <v>13</v>
       </c>
-      <c r="G28">
+      <c r="G28" s="1">
         <v>120</v>
       </c>
-      <c r="H28">
+      <c r="H28" s="1">
         <v>1600000</v>
       </c>
       <c r="I28">
@@ -1298,10 +1311,10 @@
       <c r="F29" t="s">
         <v>13</v>
       </c>
-      <c r="G29">
+      <c r="G29" s="1">
         <v>120</v>
       </c>
-      <c r="H29">
+      <c r="H29" s="1">
         <v>1600000</v>
       </c>
       <c r="I29">
@@ -1327,10 +1340,10 @@
       <c r="F30" t="s">
         <v>25</v>
       </c>
-      <c r="G30">
+      <c r="G30" s="1">
         <v>7</v>
       </c>
-      <c r="H30">
+      <c r="H30" s="1">
         <v>8500000</v>
       </c>
       <c r="I30">
@@ -1356,10 +1369,10 @@
       <c r="F31" t="s">
         <v>25</v>
       </c>
-      <c r="G31">
+      <c r="G31" s="1">
         <v>113</v>
       </c>
-      <c r="H31">
+      <c r="H31" s="1">
         <v>8500000</v>
       </c>
       <c r="I31">
@@ -1385,10 +1398,10 @@
       <c r="F32" t="s">
         <v>25</v>
       </c>
-      <c r="G32">
+      <c r="G32" s="1">
         <v>120</v>
       </c>
-      <c r="H32">
+      <c r="H32" s="1">
         <v>2750000</v>
       </c>
       <c r="I32">

--- a/database_penyimpanan_aman/database_opname_parameter.xlsx
+++ b/database_penyimpanan_aman/database_opname_parameter.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\98 PROFORMA INVOICE\Dashboard Proforma Invoice General Services\database_penyimpanan_aman\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{840548E7-4549-4B56-B380-A90D8E84361A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C646514D-FE87-42A2-8EC9-D6FD13CCB64D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="46">
   <si>
     <t>doc_key</t>
   </si>
@@ -52,6 +52,12 @@
     <t>Volume Aktual</t>
   </si>
   <si>
+    <t>Nomor PI</t>
+  </si>
+  <si>
+    <t>Nomor PO</t>
+  </si>
+  <si>
     <t>opname_016_BSS-JOB_WS_VIII_2026_4500011739</t>
   </si>
   <si>
@@ -116,23 +122,49 @@
   </si>
   <si>
     <t>2026-09-20 11:39:01</t>
+  </si>
+  <si>
+    <t>opname_028_BSS-JOB_WS_VIII_2026_45000000test</t>
+  </si>
+  <si>
+    <t>028/BSS-JOB/WS/VIII/2026</t>
+  </si>
+  <si>
+    <t>45000000test</t>
+  </si>
+  <si>
+    <t>016/BSS-JOB/WS/VIII/2026</t>
+  </si>
+  <si>
+    <t>023/BSS-JOB/WS/VIII/2026</t>
+  </si>
+  <si>
+    <t>022/BSS-JOB/WS/VIII/2026</t>
+  </si>
+  <si>
+    <t>023A/BSS-JOB/WS/VIII/2026</t>
+  </si>
+  <si>
+    <t>024/BSS-JOB/WS/VIII/2026</t>
+  </si>
+  <si>
+    <t>024A/BSS-JOB/WS/VIII/2026</t>
+  </si>
+  <si>
+    <t>025/BSS-JOB/WS/VIII/2026</t>
+  </si>
+  <si>
+    <t>026/BSS-JOB/WS/VIII/2026</t>
+  </si>
+  <si>
+    <t>027/BSS-JOB/WS/VIII/2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-  </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -158,16 +190,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -468,19 +497,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:L34"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="46.3984375" customWidth="1"/>
-    <col min="2" max="2" width="9.9296875" customWidth="1"/>
-    <col min="3" max="3" width="19.796875" customWidth="1"/>
-    <col min="6" max="6" width="12.19921875" customWidth="1"/>
-    <col min="7" max="7" width="12.1328125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="14.46484375" style="1" customWidth="1"/>
-    <col min="9" max="10" width="14.19921875" customWidth="1"/>
+    <col min="1" max="1" width="39.59765625" customWidth="1"/>
+    <col min="2" max="2" width="3.1328125" customWidth="1"/>
+    <col min="3" max="3" width="17.59765625" customWidth="1"/>
+    <col min="4" max="4" width="8.46484375" customWidth="1"/>
+    <col min="11" max="11" width="24.6640625" customWidth="1"/>
+    <col min="12" max="12" width="11.46484375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -499,10 +527,10 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
       <c r="I1" t="s">
@@ -511,27 +539,33 @@
       <c r="J1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D2">
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" s="1">
+        <v>15</v>
+      </c>
+      <c r="G2">
         <v>18300</v>
       </c>
-      <c r="H2" s="1">
+      <c r="H2">
         <v>65000</v>
       </c>
       <c r="I2">
@@ -540,27 +574,33 @@
       <c r="J2">
         <v>2578</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="K2" t="s">
+        <v>37</v>
+      </c>
+      <c r="L2">
+        <v>4500011739</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D3">
         <v>2</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3" s="1">
+        <v>15</v>
+      </c>
+      <c r="G3">
         <v>9200</v>
       </c>
-      <c r="H3" s="1">
+      <c r="H3">
         <v>33000</v>
       </c>
       <c r="I3">
@@ -569,27 +609,33 @@
       <c r="J3">
         <v>1157</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="K3" t="s">
+        <v>37</v>
+      </c>
+      <c r="L3">
+        <v>4500011739</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" s="1">
+        <v>15</v>
+      </c>
+      <c r="G4">
         <v>240</v>
       </c>
-      <c r="H4" s="1">
+      <c r="H4">
         <v>750000</v>
       </c>
       <c r="I4">
@@ -598,27 +644,33 @@
       <c r="J4">
         <v>22</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="K4" t="s">
+        <v>38</v>
+      </c>
+      <c r="L4">
+        <v>4500011739</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G5" s="1">
+        <v>20</v>
+      </c>
+      <c r="G5">
         <v>240</v>
       </c>
-      <c r="H5" s="1">
+      <c r="H5">
         <v>750000</v>
       </c>
       <c r="I5">
@@ -627,27 +679,33 @@
       <c r="J5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="K5" t="s">
+        <v>39</v>
+      </c>
+      <c r="L5">
+        <v>4500011739</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D6">
         <v>2</v>
       </c>
       <c r="E6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F6" t="s">
-        <v>18</v>
-      </c>
-      <c r="G6" s="1">
+        <v>20</v>
+      </c>
+      <c r="G6">
         <v>120</v>
       </c>
-      <c r="H6" s="1">
+      <c r="H6">
         <v>1600000</v>
       </c>
       <c r="I6">
@@ -656,27 +714,33 @@
       <c r="J6">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="K6" t="s">
+        <v>39</v>
+      </c>
+      <c r="L6">
+        <v>4500011739</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D7">
         <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F7" t="s">
-        <v>13</v>
-      </c>
-      <c r="G7" s="1">
+        <v>15</v>
+      </c>
+      <c r="G7">
         <v>120</v>
       </c>
-      <c r="H7" s="1">
+      <c r="H7">
         <v>500000</v>
       </c>
       <c r="I7">
@@ -685,27 +749,33 @@
       <c r="J7">
         <v>24</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="K7" t="s">
+        <v>40</v>
+      </c>
+      <c r="L7">
+        <v>4500011739</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D8">
         <v>2</v>
       </c>
       <c r="E8" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F8" t="s">
-        <v>13</v>
-      </c>
-      <c r="G8" s="1">
+        <v>15</v>
+      </c>
+      <c r="G8">
         <v>120</v>
       </c>
-      <c r="H8" s="1">
+      <c r="H8">
         <v>500000</v>
       </c>
       <c r="I8">
@@ -714,27 +784,33 @@
       <c r="J8">
         <v>24</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="K8" t="s">
+        <v>40</v>
+      </c>
+      <c r="L8">
+        <v>4500011739</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C9" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D9">
         <v>3</v>
       </c>
       <c r="E9" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G9" s="1">
+        <v>15</v>
+      </c>
+      <c r="G9">
         <v>120</v>
       </c>
-      <c r="H9" s="1">
+      <c r="H9">
         <v>500000</v>
       </c>
       <c r="I9">
@@ -743,27 +819,33 @@
       <c r="J9">
         <v>24</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="K9" t="s">
+        <v>40</v>
+      </c>
+      <c r="L9">
+        <v>4500011739</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C10" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D10">
         <v>1</v>
       </c>
       <c r="E10" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G10">
         <v>13</v>
       </c>
-      <c r="G10" s="1">
-        <v>13</v>
-      </c>
-      <c r="H10" s="1">
+      <c r="H10">
         <v>750000</v>
       </c>
       <c r="I10">
@@ -772,27 +854,33 @@
       <c r="J10">
         <v>13</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="K10" t="s">
+        <v>41</v>
+      </c>
+      <c r="L10">
+        <v>4500011739</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C11" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D11">
         <v>2</v>
       </c>
       <c r="E11" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F11" t="s">
-        <v>13</v>
-      </c>
-      <c r="G11" s="1">
+        <v>15</v>
+      </c>
+      <c r="G11">
         <v>120</v>
       </c>
-      <c r="H11" s="1">
+      <c r="H11">
         <v>750000</v>
       </c>
       <c r="I11">
@@ -801,27 +889,33 @@
       <c r="J11">
         <v>9</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="K11" t="s">
+        <v>41</v>
+      </c>
+      <c r="L11">
+        <v>4500011739</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C12" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D12">
         <v>3</v>
       </c>
       <c r="E12" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G12" s="1">
+        <v>15</v>
+      </c>
+      <c r="G12">
         <v>107</v>
       </c>
-      <c r="H12" s="1">
+      <c r="H12">
         <v>750000</v>
       </c>
       <c r="I12">
@@ -830,27 +924,33 @@
       <c r="J12">
         <v>17</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="K12" t="s">
+        <v>41</v>
+      </c>
+      <c r="L12">
+        <v>4500011739</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C13" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D13">
         <v>4</v>
       </c>
       <c r="E13" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F13" t="s">
-        <v>13</v>
-      </c>
-      <c r="G13" s="1">
+        <v>15</v>
+      </c>
+      <c r="G13">
         <v>120</v>
       </c>
-      <c r="H13" s="1">
+      <c r="H13">
         <v>650000</v>
       </c>
       <c r="I13">
@@ -859,27 +959,33 @@
       <c r="J13">
         <v>22</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="K13" t="s">
+        <v>41</v>
+      </c>
+      <c r="L13">
+        <v>4500011739</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C14" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D14">
         <v>5</v>
       </c>
       <c r="E14" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F14" t="s">
-        <v>13</v>
-      </c>
-      <c r="G14" s="1">
+        <v>15</v>
+      </c>
+      <c r="G14">
         <v>120</v>
       </c>
-      <c r="H14" s="1">
+      <c r="H14">
         <v>650000</v>
       </c>
       <c r="I14">
@@ -888,27 +994,33 @@
       <c r="J14">
         <v>21</v>
       </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="K14" t="s">
+        <v>41</v>
+      </c>
+      <c r="L14">
+        <v>4500011739</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C15" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D15">
         <v>6</v>
       </c>
       <c r="E15" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F15" t="s">
-        <v>13</v>
-      </c>
-      <c r="G15" s="1">
+        <v>15</v>
+      </c>
+      <c r="G15">
         <v>240</v>
       </c>
-      <c r="H15" s="1">
+      <c r="H15">
         <v>600000</v>
       </c>
       <c r="I15">
@@ -917,27 +1029,33 @@
       <c r="J15">
         <v>23</v>
       </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="K15" t="s">
+        <v>41</v>
+      </c>
+      <c r="L15">
+        <v>4500011739</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C16" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D16">
         <v>7</v>
       </c>
       <c r="E16" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F16" t="s">
-        <v>13</v>
-      </c>
-      <c r="G16" s="1">
+        <v>15</v>
+      </c>
+      <c r="G16">
         <v>240</v>
       </c>
-      <c r="H16" s="1">
+      <c r="H16">
         <v>600000</v>
       </c>
       <c r="I16">
@@ -946,27 +1064,33 @@
       <c r="J16">
         <v>23</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="K16" t="s">
+        <v>41</v>
+      </c>
+      <c r="L16">
+        <v>4500011739</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C17" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D17">
         <v>1</v>
       </c>
       <c r="E17" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F17" t="s">
-        <v>25</v>
-      </c>
-      <c r="G17" s="1">
+        <v>27</v>
+      </c>
+      <c r="G17">
         <v>120</v>
       </c>
-      <c r="H17" s="1">
+      <c r="H17">
         <v>500000</v>
       </c>
       <c r="I17">
@@ -975,27 +1099,33 @@
       <c r="J17">
         <v>21</v>
       </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="K17" t="s">
+        <v>42</v>
+      </c>
+      <c r="L17">
+        <v>4500011739</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C18" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D18">
         <v>1</v>
       </c>
       <c r="E18" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F18" t="s">
-        <v>13</v>
-      </c>
-      <c r="G18" s="1">
+        <v>15</v>
+      </c>
+      <c r="G18">
         <v>4</v>
       </c>
-      <c r="H18" s="1">
+      <c r="H18">
         <v>25000000</v>
       </c>
       <c r="I18">
@@ -1004,27 +1134,33 @@
       <c r="J18">
         <v>0.48</v>
       </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="K18" t="s">
+        <v>43</v>
+      </c>
+      <c r="L18">
+        <v>4500011739</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C19" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D19">
         <v>2</v>
       </c>
       <c r="E19" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F19" t="s">
-        <v>13</v>
-      </c>
-      <c r="G19" s="1">
+        <v>15</v>
+      </c>
+      <c r="G19">
         <v>4</v>
       </c>
-      <c r="H19" s="1">
+      <c r="H19">
         <v>17500000</v>
       </c>
       <c r="I19">
@@ -1033,27 +1169,33 @@
       <c r="J19">
         <v>0.48</v>
       </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="K19" t="s">
+        <v>43</v>
+      </c>
+      <c r="L19">
+        <v>4500011739</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C20" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D20">
         <v>3</v>
       </c>
       <c r="E20" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F20" t="s">
-        <v>13</v>
-      </c>
-      <c r="G20" s="1">
+        <v>15</v>
+      </c>
+      <c r="G20">
         <v>4</v>
       </c>
-      <c r="H20" s="1">
+      <c r="H20">
         <v>60000000</v>
       </c>
       <c r="I20">
@@ -1062,27 +1204,33 @@
       <c r="J20">
         <v>0.74</v>
       </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="K20" t="s">
+        <v>43</v>
+      </c>
+      <c r="L20">
+        <v>4500011739</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C21" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D21">
         <v>4</v>
       </c>
       <c r="E21" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F21" t="s">
-        <v>13</v>
-      </c>
-      <c r="G21" s="1">
+        <v>15</v>
+      </c>
+      <c r="G21">
         <v>4</v>
       </c>
-      <c r="H21" s="1">
+      <c r="H21">
         <v>60000000</v>
       </c>
       <c r="I21">
@@ -1091,27 +1239,33 @@
       <c r="J21">
         <v>0.74</v>
       </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="K21" t="s">
+        <v>43</v>
+      </c>
+      <c r="L21">
+        <v>4500011739</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C22" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D22">
         <v>5</v>
       </c>
       <c r="E22" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F22" t="s">
-        <v>13</v>
-      </c>
-      <c r="G22" s="1">
+        <v>15</v>
+      </c>
+      <c r="G22">
         <v>4</v>
       </c>
-      <c r="H22" s="1">
+      <c r="H22">
         <v>15000000</v>
       </c>
       <c r="I22">
@@ -1120,27 +1274,33 @@
       <c r="J22">
         <v>0.74</v>
       </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="K22" t="s">
+        <v>43</v>
+      </c>
+      <c r="L22">
+        <v>4500011739</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C23" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D23">
         <v>6</v>
       </c>
       <c r="E23" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F23" t="s">
-        <v>13</v>
-      </c>
-      <c r="G23" s="1">
+        <v>15</v>
+      </c>
+      <c r="G23">
         <v>4</v>
       </c>
-      <c r="H23" s="1">
+      <c r="H23">
         <v>15000000</v>
       </c>
       <c r="I23">
@@ -1149,27 +1309,33 @@
       <c r="J23">
         <v>0.74</v>
       </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="K23" t="s">
+        <v>43</v>
+      </c>
+      <c r="L23">
+        <v>4500011739</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C24" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D24">
         <v>1</v>
       </c>
       <c r="E24" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F24" t="s">
-        <v>13</v>
-      </c>
-      <c r="G24" s="1">
+        <v>15</v>
+      </c>
+      <c r="G24">
         <v>120</v>
       </c>
-      <c r="H24" s="1">
+      <c r="H24">
         <v>1600000</v>
       </c>
       <c r="I24">
@@ -1178,27 +1344,33 @@
       <c r="J24">
         <v>25</v>
       </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="K24" t="s">
+        <v>44</v>
+      </c>
+      <c r="L24">
+        <v>4500011739</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C25" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D25">
         <v>2</v>
       </c>
       <c r="E25" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F25" t="s">
-        <v>13</v>
-      </c>
-      <c r="G25" s="1">
+        <v>15</v>
+      </c>
+      <c r="G25">
         <v>120</v>
       </c>
-      <c r="H25" s="1">
+      <c r="H25">
         <v>1600000</v>
       </c>
       <c r="I25">
@@ -1207,27 +1379,33 @@
       <c r="J25">
         <v>15</v>
       </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="K25" t="s">
+        <v>44</v>
+      </c>
+      <c r="L25">
+        <v>4500011739</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C26" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D26">
         <v>3</v>
       </c>
       <c r="E26" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F26" t="s">
-        <v>13</v>
-      </c>
-      <c r="G26" s="1">
+        <v>15</v>
+      </c>
+      <c r="G26">
         <v>116</v>
       </c>
-      <c r="H26" s="1">
+      <c r="H26">
         <v>1600000</v>
       </c>
       <c r="I26">
@@ -1236,27 +1414,33 @@
       <c r="J26">
         <v>25</v>
       </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="K26" t="s">
+        <v>44</v>
+      </c>
+      <c r="L26">
+        <v>4500011739</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C27" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D27">
         <v>4</v>
       </c>
       <c r="E27" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F27" t="s">
-        <v>13</v>
-      </c>
-      <c r="G27" s="1">
+        <v>15</v>
+      </c>
+      <c r="G27">
         <v>4</v>
       </c>
-      <c r="H27" s="1">
+      <c r="H27">
         <v>1600000</v>
       </c>
       <c r="I27">
@@ -1265,27 +1449,33 @@
       <c r="J27">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="K27" t="s">
+        <v>44</v>
+      </c>
+      <c r="L27">
+        <v>4500011739</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C28" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D28">
         <v>5</v>
       </c>
       <c r="E28" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F28" t="s">
-        <v>13</v>
-      </c>
-      <c r="G28" s="1">
+        <v>15</v>
+      </c>
+      <c r="G28">
         <v>120</v>
       </c>
-      <c r="H28" s="1">
+      <c r="H28">
         <v>1600000</v>
       </c>
       <c r="I28">
@@ -1294,27 +1484,33 @@
       <c r="J28">
         <v>25</v>
       </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="K28" t="s">
+        <v>44</v>
+      </c>
+      <c r="L28">
+        <v>4500011739</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C29" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D29">
         <v>6</v>
       </c>
       <c r="E29" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F29" t="s">
-        <v>13</v>
-      </c>
-      <c r="G29" s="1">
+        <v>15</v>
+      </c>
+      <c r="G29">
         <v>120</v>
       </c>
-      <c r="H29" s="1">
+      <c r="H29">
         <v>1600000</v>
       </c>
       <c r="I29">
@@ -1323,27 +1519,33 @@
       <c r="J29">
         <v>22</v>
       </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="K29" t="s">
+        <v>44</v>
+      </c>
+      <c r="L29">
+        <v>4500011739</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C30" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D30">
         <v>1</v>
       </c>
       <c r="E30" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F30" t="s">
-        <v>25</v>
-      </c>
-      <c r="G30" s="1">
+        <v>27</v>
+      </c>
+      <c r="G30">
         <v>7</v>
       </c>
-      <c r="H30" s="1">
+      <c r="H30">
         <v>8500000</v>
       </c>
       <c r="I30">
@@ -1352,27 +1554,33 @@
       <c r="J30">
         <v>7</v>
       </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="K30" t="s">
+        <v>45</v>
+      </c>
+      <c r="L30">
+        <v>4500011739</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C31" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D31">
         <v>2</v>
       </c>
       <c r="E31" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F31" t="s">
-        <v>25</v>
-      </c>
-      <c r="G31" s="1">
+        <v>27</v>
+      </c>
+      <c r="G31">
         <v>113</v>
       </c>
-      <c r="H31" s="1">
+      <c r="H31">
         <v>8500000</v>
       </c>
       <c r="I31">
@@ -1381,27 +1589,33 @@
       <c r="J31">
         <v>9</v>
       </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="K31" t="s">
+        <v>45</v>
+      </c>
+      <c r="L31">
+        <v>4500011739</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C32" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D32">
         <v>3</v>
       </c>
       <c r="E32" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F32" t="s">
-        <v>25</v>
-      </c>
-      <c r="G32" s="1">
+        <v>27</v>
+      </c>
+      <c r="G32">
         <v>120</v>
       </c>
-      <c r="H32" s="1">
+      <c r="H32">
         <v>2750000</v>
       </c>
       <c r="I32">
@@ -1409,6 +1623,76 @@
       </c>
       <c r="J32">
         <v>21</v>
+      </c>
+      <c r="K32" t="s">
+        <v>45</v>
+      </c>
+      <c r="L32">
+        <v>4500011739</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A33" t="s">
+        <v>34</v>
+      </c>
+      <c r="D33">
+        <v>1</v>
+      </c>
+      <c r="E33" t="s">
+        <v>14</v>
+      </c>
+      <c r="F33" t="s">
+        <v>27</v>
+      </c>
+      <c r="G33">
+        <v>1800</v>
+      </c>
+      <c r="H33">
+        <v>7500</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>1800</v>
+      </c>
+      <c r="K33" t="s">
+        <v>35</v>
+      </c>
+      <c r="L33" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A34" t="s">
+        <v>34</v>
+      </c>
+      <c r="D34">
+        <v>2</v>
+      </c>
+      <c r="E34" t="s">
+        <v>14</v>
+      </c>
+      <c r="F34" t="s">
+        <v>27</v>
+      </c>
+      <c r="G34">
+        <v>18</v>
+      </c>
+      <c r="H34">
+        <v>53300</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>18</v>
+      </c>
+      <c r="K34" t="s">
+        <v>35</v>
+      </c>
+      <c r="L34" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/database_penyimpanan_aman/database_opname_parameter.xlsx
+++ b/database_penyimpanan_aman/database_opname_parameter.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\98 PROFORMA INVOICE\Dashboard Proforma Invoice General Services\database_penyimpanan_aman\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6CBEF1C-AA05-4559-8DE2-98040FBC39BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BD2570D-125C-43A7-9C05-951916642748}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -596,9 +596,9 @@
   <dimension ref="A1:M36"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="22.73046875" customWidth="1"/>
-    <col min="3" max="3" width="17.73046875" customWidth="1"/>
-    <col min="6" max="6" width="14.33203125" customWidth="1"/>
+    <col min="2" max="2" width="17.6640625" customWidth="1"/>
+    <col min="3" max="3" width="4" customWidth="1"/>
+    <col min="6" max="6" width="11.33203125" customWidth="1"/>
     <col min="11" max="11" width="27.796875" customWidth="1"/>
   </cols>
   <sheetData>

--- a/database_penyimpanan_aman/database_opname_parameter.xlsx
+++ b/database_penyimpanan_aman/database_opname_parameter.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\98 PROFORMA INVOICE\Dashboard Proforma Invoice General Services\database_penyimpanan_aman\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BD2570D-125C-43A7-9C05-951916642748}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE5E1242-8636-4CD4-9951-9576895727A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$M$36</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
@@ -593,6 +596,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:M36"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
@@ -600,6 +604,7 @@
     <col min="3" max="3" width="4" customWidth="1"/>
     <col min="6" max="6" width="11.33203125" customWidth="1"/>
     <col min="11" max="11" width="27.796875" customWidth="1"/>
+    <col min="12" max="12" width="14.46484375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.45">
@@ -643,7 +648,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -675,7 +680,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -777,7 +782,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>26</v>
       </c>
@@ -812,7 +817,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:13" hidden="1" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>31</v>
       </c>
@@ -1863,6 +1868,13 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:M36" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="11">
+      <filters>
+        <filter val="4500011739"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/database_penyimpanan_aman/database_opname_parameter.xlsx
+++ b/database_penyimpanan_aman/database_opname_parameter.xlsx
@@ -1360,7 +1360,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>opname_025_BSS-JOB_WS_VIII_2026_4500011739</t>
+          <t>opname_026_BSS-JOB_WS_VIII_2026_4500011739</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -1379,20 +1379,20 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>4</v>
+        <v>120</v>
       </c>
       <c r="H20" t="n">
-        <v>25000000</v>
+        <v>1600000</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0.48</v>
+        <v>25</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1402,14 +1402,14 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES - Portacamp - Office Camp,  ukuran 40 FT (Portacamp - Office Camp,  ukuran 40 FT Untuk Support Well Services di Lokasi Senoro)</t>
+          <t>CAR &amp; TANSPORTATION - Station wagon 7 seater diesel engine + driver + BBM, (Kendaraan Innova DN 1259 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>opname_025_BSS-JOB_WS_VIII_2026_4500011739</t>
+          <t>opname_026_BSS-JOB_WS_VIII_2026_4500011739</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -1428,20 +1428,20 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>4</v>
+        <v>120</v>
       </c>
       <c r="H21" t="n">
-        <v>17500000</v>
+        <v>1600000</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0.48</v>
+        <v>15</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1451,14 +1451,14 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES - Portacamp - Living camp,ukuran 40FT (4 sleepers) (Portacamp - Living camp,ukuran 40FT (8 sleepers) Untuk Support Well Services di Lokasi Senoro)</t>
+          <t>CAR &amp; TANSPORTATION - Station wagon 7 seater diesel engine + driver + BBM, (Kendaraan Innova DN 1258 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>opname_025_BSS-JOB_WS_VIII_2026_4500011739</t>
+          <t>opname_026_BSS-JOB_WS_VIII_2026_4500011739</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -1477,20 +1477,20 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>4</v>
+        <v>116</v>
       </c>
       <c r="H22" t="n">
-        <v>60000000</v>
+        <v>1600000</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0.74</v>
+        <v>25</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1500,14 +1500,14 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL - Genset, cap min 80 KVA, silent type, include maintenance (Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Siang)</t>
+          <t>CAR &amp; TANSPORTATION - Station wagon 7 seater diesel engine + driver + BBM, (Kendaraan Innova DN 1257 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>opname_025_BSS-JOB_WS_VIII_2026_4500011739</t>
+          <t>opname_026_BSS-JOB_WS_VIII_2026_4500011739</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -1529,17 +1529,17 @@
         <v>4</v>
       </c>
       <c r="H23" t="n">
-        <v>60000000</v>
+        <v>1600000</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>0.74</v>
+        <v>4</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1549,14 +1549,14 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL - Genset, cap min 80 KVA, silent type, include maintenance (Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Malam)</t>
+          <t>CAR &amp; TANSPORTATION - Station wagon 7 seater diesel engine + driver + BBM, (Kendaraan Pajero DN 1904 RA Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>opname_025_BSS-JOB_WS_VIII_2026_4500011739</t>
+          <t>opname_026_BSS-JOB_WS_VIII_2026_4500011739</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -1575,20 +1575,20 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>4</v>
+        <v>120</v>
       </c>
       <c r="H24" t="n">
-        <v>15000000</v>
+        <v>1600000</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0.74</v>
+        <v>25</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -1598,14 +1598,14 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL - Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories (Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam)</t>
+          <t>CAR &amp; TANSPORTATION - Double cabin 4x4, diesel engine + driver + BBM, (Kendaraan Hilux DN 1916 CH Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>opname_025_BSS-JOB_WS_VIII_2026_4500011739</t>
+          <t>opname_026_BSS-JOB_WS_VIII_2026_4500011739</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
@@ -1624,20 +1624,20 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>4</v>
+        <v>120</v>
       </c>
       <c r="H25" t="n">
-        <v>15000000</v>
+        <v>1600000</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>0.74</v>
+        <v>22</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -1647,14 +1647,14 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL - Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories (Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam)</t>
+          <t>CAR &amp; TANSPORTATION - Double cabin 4x4, diesel engine + driver + BBM, (Kendaraan Hilux DN 1917 CH Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>opname_026_BSS-JOB_WS_VIII_2026_4500011739</t>
+          <t>opname_027_BSS-JOB_WS_VIII_2026_4500011739</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -1669,24 +1669,24 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>120</v>
+        <v>7</v>
       </c>
       <c r="H26" t="n">
-        <v>1600000</v>
+        <v>8500000</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>026/BSS-JOB/WS/VIII/2026</t>
+          <t>027/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -1696,14 +1696,14 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION - Station wagon 7 seater diesel engine + driver + BBM, (Kendaraan Innova DN 1259 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL - crane min 70 ton, call out, (hanya unit) (Crane Tadano 70 ton Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>opname_026_BSS-JOB_WS_VIII_2026_4500011739</t>
+          <t>opname_027_BSS-JOB_WS_VIII_2026_4500011739</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -1718,24 +1718,24 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="H27" t="n">
-        <v>1600000</v>
+        <v>8500000</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>026/BSS-JOB/WS/VIII/2026</t>
+          <t>027/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -1745,14 +1745,14 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION - Station wagon 7 seater diesel engine + driver + BBM, (Kendaraan Innova DN 1258 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL - crane min 70 ton, call out, (hanya unit) (Crane Sany 100 Ton untuk menggantikan Crane Tadano 70 Ton yang rusak)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>opname_026_BSS-JOB_WS_VIII_2026_4500011739</t>
+          <t>opname_027_BSS-JOB_WS_VIII_2026_4500011739</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
@@ -1767,24 +1767,24 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="H28" t="n">
-        <v>1600000</v>
+        <v>2750000</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>026/BSS-JOB/WS/VIII/2026</t>
+          <t>027/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -1794,20 +1794,20 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION - Station wagon 7 seater diesel engine + driver + BBM, (Kendaraan Innova DN 1257 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL - Vacuum Truck , Call out, Cap  5000 ltr c/w vacuum pump &amp; acessories, call out, (hanya unit) (Vacuum Truck  5000 L DN 8806 CH untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>opname_026_BSS-JOB_WS_VIII_2026_4500011739</t>
+          <t>opname_022_BSS-JOB_WS_IX_2026_4500011739</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1816,24 +1816,24 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>4</v>
+        <v>240</v>
       </c>
       <c r="H29" t="n">
-        <v>1600000</v>
+        <v>750000</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="J29" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>026/BSS-JOB/WS/VIII/2026</t>
+          <t>022/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -1843,20 +1843,20 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION - Station wagon 7 seater diesel engine + driver + BBM, (Kendaraan Pajero DN 1904 RA Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
+          <t>PERSONEL ON CALL - Personnel GS in-charge di lokasi pemboran/ wellservices/ workover, personnel in charge (Tenaga Civil Engineer melakukan survey di Lokasi Sumur Senoro 16)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>opname_026_BSS-JOB_WS_VIII_2026_4500011739</t>
+          <t>opname_022_BSS-JOB_WS_IX_2026_4500011739</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -1875,14 +1875,14 @@
         <v>1600000</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J30" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>026/BSS-JOB/WS/VIII/2026</t>
+          <t>022/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -1892,20 +1892,20 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION - Double cabin 4x4, diesel engine + driver + BBM, (Kendaraan Hilux DN 1916 CH Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
+          <t>CAR &amp; TANSPORTATION - Double cabin 4x4, diesel engine + driver + BBM, (Kendaraan Operasional Double Cabin DN 8890 RG untuk transportasi Survey ke Lokasi)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>opname_026_BSS-JOB_WS_VIII_2026_4500011739</t>
+          <t>opname_033_BSS-JOB_WS_VIII_2026_4500011739</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1914,24 +1914,24 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>120</v>
+        <v>2</v>
       </c>
       <c r="H31" t="n">
-        <v>1600000</v>
+        <v>12500000</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>026/BSS-JOB/WS/VIII/2026</t>
+          <t>033/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -1941,14 +1941,14 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION - Double cabin 4x4, diesel engine + driver + BBM, (Kendaraan Hilux DN 1917 CH Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL - Mobilisasi/ Demobilisasi crane min 70 ton to/from Company Wellsite/ Contractor base (Mobilisasi Crane Mobile Tadano Kapasitas 70 ton dari Workshop di Lamo ke Cluster B)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>opname_027_BSS-JOB_WS_VIII_2026_4500011739</t>
+          <t>opname_032_BSS-JOB_WS_VIII_2026_4500011739</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -1963,24 +1963,24 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>7</v>
+        <v>300</v>
       </c>
       <c r="H32" t="n">
-        <v>8500000</v>
+        <v>250000</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>027/BSS-JOB/WS/VIII/2026</t>
+          <t>032/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -1990,20 +1990,20 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL - crane min 70 ton, call out, (hanya unit) (Crane Tadano 70 ton Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
+          <t>PERSONEL ON CALL - Helper Local (non Skilled) (Upah harian Flagman Periode tgl 08 sd 30 Agustus 2026)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>opname_027_BSS-JOB_WS_VIII_2026_4500011739</t>
+          <t>opname_031_BSS-JOB_WS_VIII_2026_4500011739</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -2012,24 +2012,24 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>113</v>
+        <v>4600</v>
       </c>
       <c r="H33" t="n">
-        <v>8500000</v>
+        <v>25000</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>9</v>
+        <v>316.8</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>027/BSS-JOB/WS/VIII/2026</t>
+          <t>031/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2039,20 +2039,20 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL - crane min 70 ton, call out, (hanya unit) (Crane Sany 100 Ton untuk menggantikan Crane Tadano 70 Ton yang rusak)</t>
+          <t>ADDITIONAL CAMP SERVICES - Laundry services (ADDITIONAL CAMP SERVICES Laundry services , crew di Lokasi)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>opname_027_BSS-JOB_WS_VIII_2026_4500011739</t>
+          <t>opname_029_BSS-JOB_WS_VIII_2026_0</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -2061,47 +2061,47 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>120</v>
+        <v>250</v>
       </c>
       <c r="H34" t="n">
-        <v>2750000</v>
+        <v>25000</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>21</v>
+        <v>250</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>027/BSS-JOB/WS/VIII/2026</t>
+          <t>029/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL - Vacuum Truck , Call out, Cap  5000 ltr c/w vacuum pump &amp; acessories, call out, (hanya unit) (Vacuum Truck  5000 L DN 8806 CH untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
+          <t>PENGADAAN MATERIAL - Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee, (Pengadaan Diesel Fuel include Tranportir fee, untuk Crane 70 Ton)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>opname_022_BSS-JOB_WS_IX_2026_4500011739</t>
+          <t>opname_029_BSS-JOB_WS_VIII_2026_0</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -2110,47 +2110,47 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="H35" t="n">
-        <v>750000</v>
+        <v>25000</v>
       </c>
       <c r="I35" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>1</v>
+        <v>200</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>022/BSS-JOB/WS/IX/2026</t>
+          <t>029/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL - Personnel GS in-charge di lokasi pemboran/ wellservices/ workover, personnel in charge (Tenaga Civil Engineer melakukan survey di Lokasi Sumur Senoro 16)</t>
+          <t>PENGADAAN MATERIAL - Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee, (Pengadaan Diesel Fuel include Tranportir fee, untuk Crane 100 Ton)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>opname_022_BSS-JOB_WS_IX_2026_4500011739</t>
+          <t>opname_029_BSS-JOB_WS_VIII_2026_0</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -2159,47 +2159,47 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="H36" t="n">
-        <v>1600000</v>
+        <v>25000</v>
       </c>
       <c r="I36" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>022/BSS-JOB/WS/IX/2026</t>
+          <t>029/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION - Double cabin 4x4, diesel engine + driver + BBM, (Kendaraan Operasional Double Cabin DN 8890 RG untuk transportasi Survey ke Lokasi)</t>
+          <t>PENGADAAN MATERIAL - Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee, (Pengadaan Diesel Fuel include Tranportir fee, untuk Genset 80 KVa)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>opname_033_BSS-JOB_WS_VIII_2026_4500011739</t>
+          <t>opname_029_BSS-JOB_WS_VIII_2026_0</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -2208,47 +2208,47 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="H37" t="n">
-        <v>12500000</v>
+        <v>25000</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>033/BSS-JOB/WS/VIII/2026</t>
+          <t>029/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL - Mobilisasi/ Demobilisasi crane min 70 ton to/from Company Wellsite/ Contractor base (Mobilisasi Crane Mobile Tadano Kapasitas 70 ton dari Workshop di Lamo ke Cluster B)</t>
+          <t>PENGADAAN MATERIAL - Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee, (Pengadaan Diesel Fuel include Tranportir fee, untuk Genset 80 KVa)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>opname_032_BSS-JOB_WS_VIII_2026_4500011739</t>
+          <t>opname_029_BSS-JOB_WS_VIII_2026_0</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -2257,47 +2257,47 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>300</v>
+        <v>50</v>
       </c>
       <c r="H38" t="n">
-        <v>250000</v>
+        <v>25000</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>032/BSS-JOB/WS/VIII/2026</t>
+          <t>029/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL - Helper Local (non Skilled) (Upah harian Flagman Periode tgl 08 sd 30 Agustus 2026)</t>
+          <t>PENGADAAN MATERIAL - Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee, (Pengadaan Diesel Fuel include Tranportir fee, untuk Lighting Tower 05)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>opname_031_BSS-JOB_WS_VIII_2026_4500011739</t>
+          <t>opname_029_BSS-JOB_WS_VIII_2026_0</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -2310,7 +2310,7 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>4600</v>
+        <v>50</v>
       </c>
       <c r="H39" t="n">
         <v>25000</v>
@@ -2319,21 +2319,21 @@
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>316.8</v>
+        <v>50</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>031/BSS-JOB/WS/VIII/2026</t>
+          <t>029/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES - Laundry services (ADDITIONAL CAMP SERVICES Laundry services , crew di Lokasi)</t>
+          <t>PENGADAAN MATERIAL - Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee, (Pengadaan Diesel Fuel include Tranportir fee, untuk Lighting Tower 06)</t>
         </is>
       </c>
     </row>
@@ -2346,7 +2346,7 @@
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>250</v>
+        <v>115</v>
       </c>
       <c r="H40" t="n">
         <v>25000</v>
@@ -2368,7 +2368,7 @@
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>250</v>
+        <v>115</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -2382,20 +2382,20 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL - Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee, (Pengadaan Diesel Fuel include Tranportir fee, untuk Crane 70 Ton)</t>
+          <t>PENGADAAN MATERIAL - Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee, (Pengadaan Diesel Fuel include Tranportir fee, untuk Vacuum Truck 5000 L)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>opname_029_BSS-JOB_WS_VIII_2026_0</t>
+          <t>opname_034_BSS-JOB_WS_IX_2026_0</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -2404,24 +2404,24 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>200</v>
+        <v>1</v>
       </c>
       <c r="H41" t="n">
-        <v>25000</v>
+        <v>5812675</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>200</v>
+        <v>1</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>029/BSS-JOB/WS/VIII/2026</t>
+          <t>034/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -2431,20 +2431,20 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL - Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee, (Pengadaan Diesel Fuel include Tranportir fee, untuk Crane 100 Ton)</t>
+          <t>PROVISIONAL SUM - At Cost + Fee 15% ((Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 19/09/2026)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>opname_029_BSS-JOB_WS_VIII_2026_0</t>
+          <t>opname_025_BSS-JOB_WS_VIII_2026_4500011739</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -2457,92 +2457,92 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="H42" t="n">
-        <v>25000</v>
+        <v>25000000</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>50</v>
+        <v>0.48</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>029/BSS-JOB/WS/VIII/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL - Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee, (Pengadaan Diesel Fuel include Tranportir fee, untuk Genset 80 KVa)</t>
+          <t>ADDITIONAL CAMP SERVICES - Portacamp - Office Camp,  ukuran 40 FT (Portacamp - Office Camp,  ukuran 40 FT Untuk Support Well Services di Lokasi Senoro)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>opname_029_BSS-JOB_WS_VIII_2026_0</t>
+          <t>opname_025_BSS-JOB_WS_VIII_2026_4500011739</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="n">
+        <v>2</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
         <v>4</v>
       </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Luwuk</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="G43" t="n">
-        <v>50</v>
-      </c>
       <c r="H43" t="n">
-        <v>25000</v>
+        <v>17500000</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>50</v>
+        <v>0.48</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>029/BSS-JOB/WS/VIII/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL - Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee, (Pengadaan Diesel Fuel include Tranportir fee, untuk Genset 80 KVa)</t>
+          <t>ADDITIONAL CAMP SERVICES - Portacamp - Living camp,ukuran 40FT (4 sleepers) (Portacamp - Living camp,ukuran 40FT (4 sleepers) Untuk Support Well Services di Lokasi Senoro)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>opname_029_BSS-JOB_WS_VIII_2026_0</t>
+          <t>opname_025_BSS-JOB_WS_VIII_2026_4500011739</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -2555,43 +2555,43 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="H44" t="n">
-        <v>25000</v>
+        <v>60000000</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>50</v>
+        <v>0.74</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>029/BSS-JOB/WS/VIII/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL - Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee, (Pengadaan Diesel Fuel include Tranportir fee, untuk Lighting Tower 05)</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL - Genset, cap min 80 KVA, silent type, include maintenance (Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Siang)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>opname_029_BSS-JOB_WS_VIII_2026_0</t>
+          <t>opname_025_BSS-JOB_WS_VIII_2026_4500011739</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -2604,43 +2604,43 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="H45" t="n">
-        <v>25000</v>
+        <v>60000000</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>50</v>
+        <v>0.74</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>029/BSS-JOB/WS/VIII/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL - Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee, (Pengadaan Diesel Fuel include Tranportir fee, untuk Lighting Tower 06)</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL - Genset, cap min 80 KVA, silent type, include maintenance (Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Malam)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>opname_029_BSS-JOB_WS_VIII_2026_0</t>
+          <t>opname_025_BSS-JOB_WS_VIII_2026_4500011739</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -2653,43 +2653,43 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>115</v>
+        <v>4</v>
       </c>
       <c r="H46" t="n">
-        <v>25000</v>
+        <v>15000000</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>115</v>
+        <v>0.74</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>029/BSS-JOB/WS/VIII/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL - Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee, (Pengadaan Diesel Fuel include Tranportir fee, untuk Vacuum Truck 5000 L)</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL - Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories (Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>opname_034_BSS-JOB_WS_IX_2026_0</t>
+          <t>opname_025_BSS-JOB_WS_VIII_2026_4500011739</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -2698,34 +2698,34 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H47" t="n">
-        <v>5812675</v>
+        <v>15000000</v>
       </c>
       <c r="I47" t="n">
         <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>1</v>
+        <v>0.74</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>034/BSS-JOB/WS/IX/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM - At Cost + Fee 15% ((Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 19/09/2026)</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL - Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories (Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam)</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_opname_parameter.xlsx
+++ b/database_penyimpanan_aman/database_opname_parameter.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M47"/>
+  <dimension ref="A1:M57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -968,7 +968,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>opname_024_BSS-JOB_WS_VIII_2026_4500011739</t>
+          <t>opname_024A_BSS-JOB_WS_VIII_2026_4500011739</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -983,24 +983,24 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>13</v>
+        <v>120</v>
       </c>
       <c r="H12" t="n">
-        <v>750000</v>
+        <v>500000</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>024/BSS-JOB/WS/VIII/2026</t>
+          <t>024A/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1010,20 +1010,20 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL - Operator Crane (Operator Crane Shift Siang atas nama Rasid A Laugi)</t>
+          <t>PERSONEL ON CALL - Operator Heavy Equipment (Vacuum Truck) (Supporting equipment kegiatan Wellservices 2026, Operator Heavy Equipment (Vacuum Truck))</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>opname_024_BSS-JOB_WS_VIII_2026_4500011739</t>
+          <t>opname_027_BSS-JOB_WS_VIII_2026_4500011739</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1032,24 +1032,24 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>120</v>
+        <v>7</v>
       </c>
       <c r="H13" t="n">
-        <v>750000</v>
+        <v>8500000</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>024/BSS-JOB/WS/VIII/2026</t>
+          <t>027/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1059,20 +1059,20 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL - Operator Crane (Operator Crane Shift Siang atas nama Wanhar)</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL - crane min 70 ton, call out, (hanya unit) (Crane Tadano 70 ton Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>opname_024_BSS-JOB_WS_VIII_2026_4500011739</t>
+          <t>opname_027_BSS-JOB_WS_VIII_2026_4500011739</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1081,24 +1081,24 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="H14" t="n">
-        <v>750000</v>
+        <v>8500000</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>024/BSS-JOB/WS/VIII/2026</t>
+          <t>027/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1108,20 +1108,20 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL - Operator Crane (Operator Crane Shift Malam  atas nama Ilsan Adjedar)</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL - crane min 70 ton, call out, (hanya unit) (Crane Sany 100 Ton untuk menggantikan Crane Tadano 70 Ton yang rusak)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>opname_024_BSS-JOB_WS_VIII_2026_4500011739</t>
+          <t>opname_027_BSS-JOB_WS_VIII_2026_4500011739</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1130,24 +1130,24 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="G15" t="n">
         <v>120</v>
       </c>
       <c r="H15" t="n">
-        <v>650000</v>
+        <v>2750000</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>024/BSS-JOB/WS/VIII/2026</t>
+          <t>027/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1157,20 +1157,20 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL - Rigger (Rigger  Crane Shift Siang  atas nama Tison)</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL - Vacuum Truck , Call out, Cap  5000 ltr c/w vacuum pump &amp; acessories, call out, (hanya unit) (Vacuum Truck  5000 L DN 8806 CH untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>opname_024_BSS-JOB_WS_VIII_2026_4500011739</t>
+          <t>opname_022_BSS-JOB_WS_IX_2026_4500011739</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1179,24 +1179,24 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="H16" t="n">
-        <v>650000</v>
+        <v>750000</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="J16" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>024/BSS-JOB/WS/VIII/2026</t>
+          <t>022/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1206,20 +1206,20 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL - Rigger (Rigger  Crane Shift Malam  atas nama Agus Dg Mangata)</t>
+          <t>PERSONEL ON CALL - Personnel GS in-charge di lokasi pemboran/ wellservices/ workover, personnel in charge (Tenaga Civil Engineer melakukan survey di Lokasi Sumur Senoro 16)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>opname_024_BSS-JOB_WS_VIII_2026_4500011739</t>
+          <t>opname_022_BSS-JOB_WS_IX_2026_4500011739</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1228,24 +1228,24 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>240</v>
+        <v>120</v>
       </c>
       <c r="H17" t="n">
-        <v>600000</v>
+        <v>1600000</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J17" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>024/BSS-JOB/WS/VIII/2026</t>
+          <t>022/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1255,20 +1255,20 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL - Mechanic/ Electrician (Mechanic/ Electrician operasikan Mesin Genset dan Lighting Tower atas nama Sugeng)</t>
+          <t>CAR &amp; TANSPORTATION - Double cabin 4x4, diesel engine + driver + BBM, (Kendaraan Operasional Double Cabin DN 8890 RG untuk transportasi Survey ke Lokasi)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>opname_024_BSS-JOB_WS_VIII_2026_4500011739</t>
+          <t>opname_033_BSS-JOB_WS_VIII_2026_4500011739</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1277,24 +1277,24 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>240</v>
+        <v>2</v>
       </c>
       <c r="H18" t="n">
-        <v>600000</v>
+        <v>12500000</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>024/BSS-JOB/WS/VIII/2026</t>
+          <t>033/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1304,14 +1304,14 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL - Mechanic/ Electrician (Mechanic/ Electrician operasikan Mesin Genset dan Lighting Tower atas nama Ahmad Dhani)</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL - Mobilisasi/ Demobilisasi crane min 70 ton to/from Company Wellsite/ Contractor base (Mobilisasi Crane Mobile Tadano Kapasitas 70 ton dari Workshop di Lamo ke Cluster B)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>opname_024A_BSS-JOB_WS_VIII_2026_4500011739</t>
+          <t>opname_031_BSS-JOB_WS_VIII_2026_4500011739</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -1326,24 +1326,24 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>120</v>
+        <v>4600</v>
       </c>
       <c r="H19" t="n">
-        <v>500000</v>
+        <v>25000</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>21</v>
+        <v>316.8</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>024A/BSS-JOB/WS/VIII/2026</t>
+          <t>031/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1353,14 +1353,14 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL - Operator Heavy Equipment (Vacuum Truck) (Supporting equipment kegiatan Wellservices 2026, Operator Heavy Equipment (Vacuum Truck))</t>
+          <t>ADDITIONAL CAMP SERVICES - Laundry services (ADDITIONAL CAMP SERVICES Laundry services , crew di Lokasi)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>opname_026_BSS-JOB_WS_VIII_2026_4500011739</t>
+          <t>opname_029_BSS-JOB_WS_VIII_2026_0</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -1379,37 +1379,37 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>120</v>
+        <v>250</v>
       </c>
       <c r="H20" t="n">
-        <v>1600000</v>
+        <v>25000</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>25</v>
+        <v>250</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>026/BSS-JOB/WS/VIII/2026</t>
+          <t>029/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION - Station wagon 7 seater diesel engine + driver + BBM, (Kendaraan Innova DN 1259 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
+          <t>PENGADAAN MATERIAL - Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee, (Pengadaan Diesel Fuel include Tranportir fee, untuk Crane 70 Ton)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>opname_026_BSS-JOB_WS_VIII_2026_4500011739</t>
+          <t>opname_029_BSS-JOB_WS_VIII_2026_0</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -1428,37 +1428,37 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="H21" t="n">
-        <v>1600000</v>
+        <v>25000</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>15</v>
+        <v>200</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>026/BSS-JOB/WS/VIII/2026</t>
+          <t>029/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION - Station wagon 7 seater diesel engine + driver + BBM, (Kendaraan Innova DN 1258 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
+          <t>PENGADAAN MATERIAL - Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee, (Pengadaan Diesel Fuel include Tranportir fee, untuk Crane 100 Ton)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>opname_026_BSS-JOB_WS_VIII_2026_4500011739</t>
+          <t>opname_029_BSS-JOB_WS_VIII_2026_0</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -1477,37 +1477,37 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>116</v>
+        <v>50</v>
       </c>
       <c r="H22" t="n">
-        <v>1600000</v>
+        <v>25000</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>026/BSS-JOB/WS/VIII/2026</t>
+          <t>029/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION - Station wagon 7 seater diesel engine + driver + BBM, (Kendaraan Innova DN 1257 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
+          <t>PENGADAAN MATERIAL - Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee, (Pengadaan Diesel Fuel include Tranportir fee, untuk Genset 80 KVa)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>opname_026_BSS-JOB_WS_VIII_2026_4500011739</t>
+          <t>opname_029_BSS-JOB_WS_VIII_2026_0</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -1526,37 +1526,37 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="H23" t="n">
-        <v>1600000</v>
+        <v>25000</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>026/BSS-JOB/WS/VIII/2026</t>
+          <t>029/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION - Station wagon 7 seater diesel engine + driver + BBM, (Kendaraan Pajero DN 1904 RA Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
+          <t>PENGADAAN MATERIAL - Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee, (Pengadaan Diesel Fuel include Tranportir fee, untuk Genset 80 KVa)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>opname_026_BSS-JOB_WS_VIII_2026_4500011739</t>
+          <t>opname_029_BSS-JOB_WS_VIII_2026_0</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -1575,37 +1575,37 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="H24" t="n">
-        <v>1600000</v>
+        <v>25000</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>026/BSS-JOB/WS/VIII/2026</t>
+          <t>029/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION - Double cabin 4x4, diesel engine + driver + BBM, (Kendaraan Hilux DN 1916 CH Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
+          <t>PENGADAAN MATERIAL - Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee, (Pengadaan Diesel Fuel include Tranportir fee, untuk Lighting Tower 05)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>opname_026_BSS-JOB_WS_VIII_2026_4500011739</t>
+          <t>opname_029_BSS-JOB_WS_VIII_2026_0</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
@@ -1624,43 +1624,43 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="H25" t="n">
-        <v>1600000</v>
+        <v>25000</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>026/BSS-JOB/WS/VIII/2026</t>
+          <t>029/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION - Double cabin 4x4, diesel engine + driver + BBM, (Kendaraan Hilux DN 1917 CH Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
+          <t>PENGADAAN MATERIAL - Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee, (Pengadaan Diesel Fuel include Tranportir fee, untuk Lighting Tower 06)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>opname_027_BSS-JOB_WS_VIII_2026_4500011739</t>
+          <t>opname_029_BSS-JOB_WS_VIII_2026_0</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1669,47 +1669,47 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>7</v>
+        <v>115</v>
       </c>
       <c r="H26" t="n">
-        <v>8500000</v>
+        <v>25000</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>7</v>
+        <v>115</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>027/BSS-JOB/WS/VIII/2026</t>
+          <t>029/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL - crane min 70 ton, call out, (hanya unit) (Crane Tadano 70 ton Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
+          <t>PENGADAAN MATERIAL - Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee, (Pengadaan Diesel Fuel include Tranportir fee, untuk Vacuum Truck 5000 L)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>opname_027_BSS-JOB_WS_VIII_2026_4500011739</t>
+          <t>opname_034_BSS-JOB_WS_IX_2026_0</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1718,47 +1718,47 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>113</v>
+        <v>1</v>
       </c>
       <c r="H27" t="n">
-        <v>8500000</v>
+        <v>5812675</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>027/BSS-JOB/WS/VIII/2026</t>
+          <t>034/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL - crane min 70 ton, call out, (hanya unit) (Crane Sany 100 Ton untuk menggantikan Crane Tadano 70 Ton yang rusak)</t>
+          <t>PROVISIONAL SUM - At Cost + Fee 15% ((Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 19/09/2026)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>opname_027_BSS-JOB_WS_VIII_2026_4500011739</t>
+          <t>opname_025_BSS-JOB_WS_VIII_2026_4500011739</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1767,24 +1767,24 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>120</v>
+        <v>4</v>
       </c>
       <c r="H28" t="n">
-        <v>2750000</v>
+        <v>25000000</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>21</v>
+        <v>0.48</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>027/BSS-JOB/WS/VIII/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -1794,20 +1794,20 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL - Vacuum Truck , Call out, Cap  5000 ltr c/w vacuum pump &amp; acessories, call out, (hanya unit) (Vacuum Truck  5000 L DN 8806 CH untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
+          <t>ADDITIONAL CAMP SERVICES - Portacamp - Office Camp,  ukuran 40 FT (Portacamp - Office Camp,  ukuran 40 FT Untuk Support Well Services di Lokasi Senoro)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>opname_022_BSS-JOB_WS_IX_2026_4500011739</t>
+          <t>opname_025_BSS-JOB_WS_VIII_2026_4500011739</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1816,24 +1816,24 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>240</v>
+        <v>4</v>
       </c>
       <c r="H29" t="n">
-        <v>750000</v>
+        <v>17500000</v>
       </c>
       <c r="I29" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>1</v>
+        <v>0.48</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>022/BSS-JOB/WS/IX/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -1843,20 +1843,20 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL - Personnel GS in-charge di lokasi pemboran/ wellservices/ workover, personnel in charge (Tenaga Civil Engineer melakukan survey di Lokasi Sumur Senoro 16)</t>
+          <t>ADDITIONAL CAMP SERVICES - Portacamp - Living camp,ukuran 40FT (4 sleepers) (Portacamp - Living camp,ukuran 40FT (4 sleepers) Untuk Support Well Services di Lokasi Senoro)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>opname_022_BSS-JOB_WS_IX_2026_4500011739</t>
+          <t>opname_025_BSS-JOB_WS_VIII_2026_4500011739</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1865,24 +1865,24 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>120</v>
+        <v>4</v>
       </c>
       <c r="H30" t="n">
-        <v>1600000</v>
+        <v>60000000</v>
       </c>
       <c r="I30" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>1</v>
+        <v>0.74</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>022/BSS-JOB/WS/IX/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -1892,20 +1892,20 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION - Double cabin 4x4, diesel engine + driver + BBM, (Kendaraan Operasional Double Cabin DN 8890 RG untuk transportasi Survey ke Lokasi)</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL - Genset, cap min 80 KVA, silent type, include maintenance (Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Siang)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>opname_033_BSS-JOB_WS_VIII_2026_4500011739</t>
+          <t>opname_025_BSS-JOB_WS_VIII_2026_4500011739</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1914,24 +1914,24 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H31" t="n">
-        <v>12500000</v>
+        <v>60000000</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>1</v>
+        <v>0.74</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>033/BSS-JOB/WS/VIII/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -1941,20 +1941,20 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL - Mobilisasi/ Demobilisasi crane min 70 ton to/from Company Wellsite/ Contractor base (Mobilisasi Crane Mobile Tadano Kapasitas 70 ton dari Workshop di Lamo ke Cluster B)</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL - Genset, cap min 80 KVA, silent type, include maintenance (Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Malam)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>opname_032_BSS-JOB_WS_VIII_2026_4500011739</t>
+          <t>opname_025_BSS-JOB_WS_VIII_2026_4500011739</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1963,24 +1963,24 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>300</v>
+        <v>4</v>
       </c>
       <c r="H32" t="n">
-        <v>250000</v>
+        <v>15000000</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>24</v>
+        <v>0.74</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>032/BSS-JOB/WS/VIII/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -1990,20 +1990,20 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL - Helper Local (non Skilled) (Upah harian Flagman Periode tgl 08 sd 30 Agustus 2026)</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL - Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories (Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>opname_031_BSS-JOB_WS_VIII_2026_4500011739</t>
+          <t>opname_025_BSS-JOB_WS_VIII_2026_4500011739</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -2016,20 +2016,20 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>4600</v>
+        <v>4</v>
       </c>
       <c r="H33" t="n">
-        <v>25000</v>
+        <v>15000000</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>316.8</v>
+        <v>0.74</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>031/BSS-JOB/WS/VIII/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2039,14 +2039,14 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES - Laundry services (ADDITIONAL CAMP SERVICES Laundry services , crew di Lokasi)</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL - Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories (Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>opname_029_BSS-JOB_WS_VIII_2026_0</t>
+          <t>opname_024_BSS-JOB_WS_VIII_2026_4500011739</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -2065,37 +2065,37 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>250</v>
+        <v>13</v>
       </c>
       <c r="H34" t="n">
-        <v>25000</v>
+        <v>750000</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>250</v>
+        <v>13</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>029/BSS-JOB/WS/VIII/2026</t>
+          <t>024/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL - Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee, (Pengadaan Diesel Fuel include Tranportir fee, untuk Crane 70 Ton)</t>
+          <t>PERSONEL ON CALL - Operator Crane (Operator Crane Shift Siang atas nama Rasid A Laugi)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>opname_029_BSS-JOB_WS_VIII_2026_0</t>
+          <t>opname_024_BSS-JOB_WS_VIII_2026_4500011739</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -2114,37 +2114,37 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="H35" t="n">
-        <v>25000</v>
+        <v>750000</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>200</v>
+        <v>9</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>029/BSS-JOB/WS/VIII/2026</t>
+          <t>024/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL - Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee, (Pengadaan Diesel Fuel include Tranportir fee, untuk Crane 100 Ton)</t>
+          <t>PERSONEL ON CALL - Operator Crane (Operator Crane Shift Siang atas nama Wanhar)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>opname_029_BSS-JOB_WS_VIII_2026_0</t>
+          <t>opname_024_BSS-JOB_WS_VIII_2026_4500011739</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -2163,37 +2163,37 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>50</v>
+        <v>107</v>
       </c>
       <c r="H36" t="n">
-        <v>25000</v>
+        <v>750000</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>029/BSS-JOB/WS/VIII/2026</t>
+          <t>024/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL - Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee, (Pengadaan Diesel Fuel include Tranportir fee, untuk Genset 80 KVa)</t>
+          <t>PERSONEL ON CALL - Operator Crane (Operator Crane Shift Malam  atas nama Ilsan Adjedar)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>opname_029_BSS-JOB_WS_VIII_2026_0</t>
+          <t>opname_024_BSS-JOB_WS_VIII_2026_4500011739</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
@@ -2212,37 +2212,37 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="H37" t="n">
-        <v>25000</v>
+        <v>650000</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>029/BSS-JOB/WS/VIII/2026</t>
+          <t>024/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL - Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee, (Pengadaan Diesel Fuel include Tranportir fee, untuk Genset 80 KVa)</t>
+          <t>PERSONEL ON CALL - Rigger (Rigger  Crane Shift Siang  atas nama Tison)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>opname_029_BSS-JOB_WS_VIII_2026_0</t>
+          <t>opname_024_BSS-JOB_WS_VIII_2026_4500011739</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -2261,37 +2261,37 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="H38" t="n">
-        <v>25000</v>
+        <v>650000</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>50</v>
+        <v>21</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>029/BSS-JOB/WS/VIII/2026</t>
+          <t>024/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL - Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee, (Pengadaan Diesel Fuel include Tranportir fee, untuk Lighting Tower 05)</t>
+          <t>PERSONEL ON CALL - Rigger (Rigger  Crane Shift Malam  atas nama Agus Dg Mangata)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>opname_029_BSS-JOB_WS_VIII_2026_0</t>
+          <t>opname_024_BSS-JOB_WS_VIII_2026_4500011739</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -2310,37 +2310,37 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>50</v>
+        <v>240</v>
       </c>
       <c r="H39" t="n">
-        <v>25000</v>
+        <v>600000</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>029/BSS-JOB/WS/VIII/2026</t>
+          <t>024/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL - Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee, (Pengadaan Diesel Fuel include Tranportir fee, untuk Lighting Tower 06)</t>
+          <t>PERSONEL ON CALL - Mechanic/ Electrician (Mechanic/ Electrician operasikan Mesin Genset dan Lighting Tower atas nama Sugeng)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>opname_029_BSS-JOB_WS_VIII_2026_0</t>
+          <t>opname_024_BSS-JOB_WS_VIII_2026_4500011739</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -2359,37 +2359,37 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>115</v>
+        <v>240</v>
       </c>
       <c r="H40" t="n">
-        <v>25000</v>
+        <v>600000</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>115</v>
+        <v>23</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>029/BSS-JOB/WS/VIII/2026</t>
+          <t>024/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL - Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee, (Pengadaan Diesel Fuel include Tranportir fee, untuk Vacuum Truck 5000 L)</t>
+          <t>PERSONEL ON CALL - Mechanic/ Electrician (Mechanic/ Electrician operasikan Mesin Genset dan Lighting Tower atas nama Ahmad Dhani)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>opname_034_BSS-JOB_WS_IX_2026_0</t>
+          <t>opname_026_BSS-JOB_WS_VIII_2026_4500011739</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -2404,47 +2404,47 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="H41" t="n">
-        <v>5812675</v>
+        <v>1600000</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>034/BSS-JOB/WS/IX/2026</t>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM - At Cost + Fee 15% ((Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 19/09/2026)</t>
+          <t>CAR &amp; TANSPORTATION - Station wagon 7 seater diesel engine + driver + BBM, (Kendaraan Innova DN 1259 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>opname_025_BSS-JOB_WS_VIII_2026_4500011739</t>
+          <t>opname_026_BSS-JOB_WS_VIII_2026_4500011739</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -2457,20 +2457,20 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>4</v>
+        <v>120</v>
       </c>
       <c r="H42" t="n">
-        <v>25000000</v>
+        <v>1600000</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>0.48</v>
+        <v>15</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -2480,20 +2480,20 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES - Portacamp - Office Camp,  ukuran 40 FT (Portacamp - Office Camp,  ukuran 40 FT Untuk Support Well Services di Lokasi Senoro)</t>
+          <t>CAR &amp; TANSPORTATION - Station wagon 7 seater diesel engine + driver + BBM, (Kendaraan Innova DN 1258 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>opname_025_BSS-JOB_WS_VIII_2026_4500011739</t>
+          <t>opname_026_BSS-JOB_WS_VIII_2026_4500011739</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -2506,20 +2506,20 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>4</v>
+        <v>116</v>
       </c>
       <c r="H43" t="n">
-        <v>17500000</v>
+        <v>1600000</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>0.48</v>
+        <v>25</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -2529,20 +2529,20 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES - Portacamp - Living camp,ukuran 40FT (4 sleepers) (Portacamp - Living camp,ukuran 40FT (4 sleepers) Untuk Support Well Services di Lokasi Senoro)</t>
+          <t>CAR &amp; TANSPORTATION - Station wagon 7 seater diesel engine + driver + BBM, (Kendaraan Innova DN 1257 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>opname_025_BSS-JOB_WS_VIII_2026_4500011739</t>
+          <t>opname_026_BSS-JOB_WS_VIII_2026_4500011739</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -2558,17 +2558,17 @@
         <v>4</v>
       </c>
       <c r="H44" t="n">
-        <v>60000000</v>
+        <v>1600000</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>0.74</v>
+        <v>4</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -2578,20 +2578,20 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL - Genset, cap min 80 KVA, silent type, include maintenance (Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Siang)</t>
+          <t>CAR &amp; TANSPORTATION - Station wagon 7 seater diesel engine + driver + BBM, (Kendaraan Pajero DN 1904 RA Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>opname_025_BSS-JOB_WS_VIII_2026_4500011739</t>
+          <t>opname_026_BSS-JOB_WS_VIII_2026_4500011739</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -2604,20 +2604,20 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>4</v>
+        <v>120</v>
       </c>
       <c r="H45" t="n">
-        <v>60000000</v>
+        <v>1600000</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>0.74</v>
+        <v>25</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -2627,20 +2627,20 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL - Genset, cap min 80 KVA, silent type, include maintenance (Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Malam)</t>
+          <t>CAR &amp; TANSPORTATION - Double cabin 4x4, diesel engine + driver + BBM, (Kendaraan Hilux DN 1916 CH Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>opname_025_BSS-JOB_WS_VIII_2026_4500011739</t>
+          <t>opname_026_BSS-JOB_WS_VIII_2026_4500011739</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -2653,20 +2653,20 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>4</v>
+        <v>120</v>
       </c>
       <c r="H46" t="n">
-        <v>15000000</v>
+        <v>1600000</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>0.74</v>
+        <v>22</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -2676,56 +2676,546 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL - Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories (Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam)</t>
+          <t>CAR &amp; TANSPORTATION - Double cabin 4x4, diesel engine + driver + BBM, (Kendaraan Hilux DN 1917 CH Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>opname_025_BSS-JOB_WS_VIII_2026_4500011739</t>
+          <t>opname_032_BSS-JOB_WS_VIII_2026_4500011739</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>300</v>
+      </c>
+      <c r="H47" t="n">
+        <v>250000</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="n">
+        <v>48</v>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>032/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL - Helper Local (non Skilled) (Upah harian Flagman Periode 08 sd 30 Agustus 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>opname_013_BSS-JOB_WS_VIII_2026_0</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>240</v>
+      </c>
+      <c r="H48" t="n">
+        <v>7500</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
+        <v>240</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM - Aqua 600 ml (Kebutuhan Logistic di Lapangan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>opname_013_BSS-JOB_WS_VIII_2026_0</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr"/>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="n">
+        <v>2</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>24</v>
+      </c>
+      <c r="H49" t="n">
+        <v>19500</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="n">
+        <v>24</v>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM - Chitato 68 g (Kebutuhan Logistic di Lapangan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>opname_013_BSS-JOB_WS_VIII_2026_0</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr"/>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="n">
+        <v>3</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>24</v>
+      </c>
+      <c r="H50" t="n">
+        <v>15600</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="n">
+        <v>24</v>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM - Coffe Nescafe Kaleng 220 ml (Kebutuhan Logistic di Lapangan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>opname_013_BSS-JOB_WS_VIII_2026_0</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="n">
+        <v>4</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>48</v>
+      </c>
+      <c r="H51" t="n">
+        <v>13000</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="n">
+        <v>48</v>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM - Pocari Sweat (Kebutuhan Logistic di Lapangan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>opname_013_BSS-JOB_WS_VIII_2026_0</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr"/>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="n">
+        <v>5</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>48</v>
+      </c>
+      <c r="H52" t="n">
+        <v>84500</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="n">
+        <v>48</v>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM - Kopi Kapal Api 380 g (Kebutuhan Logistic di Lapangan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>opname_013_BSS-JOB_WS_VIII_2026_0</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr"/>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="n">
         <v>6</v>
       </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>Luwuk</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="G47" t="n">
-        <v>4</v>
-      </c>
-      <c r="H47" t="n">
-        <v>15000000</v>
-      </c>
-      <c r="I47" t="n">
-        <v>0</v>
-      </c>
-      <c r="J47" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>4500011739</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL - Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories (Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam)</t>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>48</v>
+      </c>
+      <c r="H53" t="n">
+        <v>9750</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="n">
+        <v>48</v>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM - Coca Cola (Kebutuhan Logistic di Lapangan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>opname_013_BSS-JOB_WS_VIII_2026_0</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr"/>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="n">
+        <v>7</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>48</v>
+      </c>
+      <c r="H54" t="n">
+        <v>9750</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="n">
+        <v>48</v>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM - Fanta (Kebutuhan Logistic di Lapangan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>opname_013_BSS-JOB_WS_VIII_2026_0</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr"/>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="n">
+        <v>8</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>48</v>
+      </c>
+      <c r="H55" t="n">
+        <v>9750</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="n">
+        <v>48</v>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM - Pop Mie (Kebutuhan Logistic di Lapangan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>opname_013_BSS-JOB_WS_VIII_2026_0</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr"/>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="n">
+        <v>9</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>48</v>
+      </c>
+      <c r="H56" t="n">
+        <v>19500</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" t="n">
+        <v>48</v>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM - Susu Beruang (Kebutuhan Logistic di Lapangan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>opname_013_BSS-JOB_WS_VIII_2026_0</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr"/>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="n">
+        <v>10</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>48</v>
+      </c>
+      <c r="H57" t="n">
+        <v>9750</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" t="n">
+        <v>48</v>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM - Teh Kotak (Kebutuhan Logistic di Lapangan)</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_opname_parameter.xlsx
+++ b/database_penyimpanan_aman/database_opname_parameter.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M57"/>
+  <dimension ref="A1:M58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3219,6 +3219,55 @@
         </is>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>opname_035_BSS-JOB_WS_X_2026_0</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr"/>
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="n">
+        <v>1</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>1</v>
+      </c>
+      <c r="H58" t="n">
+        <v>151397500</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" t="n">
+        <v>1</v>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>035/BSS-JOB/WS/X/2026</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>PROVISIONAL SUM - At Cost + Fee 15% (Akomodasi Personel JOB Tomori dan Serco di Hotel King Amear Periode 07 Agustus 2026 sd 10 September 2026, Sesuai rekap  dan Kwitansi terlampir)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database_penyimpanan_aman/database_opname_parameter.xlsx
+++ b/database_penyimpanan_aman/database_opname_parameter.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M60"/>
+  <dimension ref="A1:M62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2732,7 +2732,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>opname_013_BSS-JOB_WS_VIII_2026_0</t>
+          <t>opname_035_BSS-JOB_WS_X_2026_0</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -2747,24 +2747,24 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>240</v>
+        <v>1</v>
       </c>
       <c r="H48" t="n">
-        <v>7500</v>
+        <v>151397500</v>
       </c>
       <c r="I48" t="n">
         <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>240</v>
+        <v>1</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>013/BSS-JOB/WS/VIII/2026</t>
+          <t>035/BSS-JOB/WS/X/2026</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -2774,20 +2774,20 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM - Aqua 600 ml (Kebutuhan Logistic di Lapangan)</t>
+          <t>PROVISIONAL SUM - At Cost + Fee 15% (Akomodasi Personel JOB Tomori dan Serco di Hotel King Amear Periode 07 Agustus 2026 sd 10 September 2026, Sesuai rekap  dan Kwitansi terlampir)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>opname_013_BSS-JOB_WS_VIII_2026_0</t>
+          <t>opname_036_BSS-JOB_WS_IX_2026_4500011739</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2796,47 +2796,47 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>24</v>
+        <v>4600</v>
       </c>
       <c r="H49" t="n">
-        <v>19500</v>
+        <v>25000</v>
       </c>
       <c r="I49" t="n">
-        <v>0</v>
+        <v>316.8</v>
       </c>
       <c r="J49" t="n">
-        <v>24</v>
+        <v>489.8</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>013/BSS-JOB/WS/VIII/2026</t>
+          <t>036/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM - Chitato 68 g (Kebutuhan Logistic di Lapangan)</t>
+          <t>ADDITIONAL CAMP SERVICES - Laundry services (Loundry Untuk Personel JOB dan Serco di Hotel King Amear Periode tanggal 07 Agustus sd 10 September 2026)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>opname_013_BSS-JOB_WS_VIII_2026_0</t>
+          <t>opname_030_BSS-JOB_WS_VIII_2026_-</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2845,34 +2845,34 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="H50" t="n">
-        <v>15600</v>
+        <v>53762499.99999999</v>
       </c>
       <c r="I50" t="n">
         <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>013/BSS-JOB/WS/VIII/2026</t>
+          <t>030/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM - Coffe Nescafe Kaleng 220 ml (Kebutuhan Logistic di Lapangan)</t>
+          <t>PROVISIONAL SUM - At Cost + Fee 15% (Provsum Akomodasi untuk crew well services di penginapan Yellow Toili Periode tanggal 07 Agustus sd 31 Agustus 2026)</t>
         </is>
       </c>
     </row>
@@ -2885,7 +2885,7 @@
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2898,16 +2898,16 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>48</v>
+        <v>240</v>
       </c>
       <c r="H51" t="n">
-        <v>13000</v>
+        <v>7500</v>
       </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>48</v>
+        <v>240</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM - Pocari Sweat (Kebutuhan Logistic di Lapangan)</t>
+          <t>ESTIMATED SUM - Indocafe Coffemix Renteng (Kebutuhan Logistic di Lapangan)</t>
         </is>
       </c>
     </row>
@@ -2934,7 +2934,7 @@
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2947,16 +2947,16 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="H52" t="n">
-        <v>84500</v>
+        <v>19500</v>
       </c>
       <c r="I52" t="n">
         <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -2983,7 +2983,7 @@
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2996,16 +2996,16 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="H53" t="n">
-        <v>9750</v>
+        <v>15600</v>
       </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -3019,7 +3019,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM - Coca Cola (Kebutuhan Logistic di Lapangan)</t>
+          <t>ESTIMATED SUM - Nescafe Classic renteng (Kebutuhan Logistic di Lapangan)</t>
         </is>
       </c>
     </row>
@@ -3032,7 +3032,7 @@
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         <v>48</v>
       </c>
       <c r="H54" t="n">
-        <v>9750</v>
+        <v>13000</v>
       </c>
       <c r="I54" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM - Fanta (Kebutuhan Logistic di Lapangan)</t>
+          <t>ESTIMATED SUM - Pop Mie (Kebutuhan Logistic di Lapangan)</t>
         </is>
       </c>
     </row>
@@ -3081,7 +3081,7 @@
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -3097,7 +3097,7 @@
         <v>48</v>
       </c>
       <c r="H55" t="n">
-        <v>9750</v>
+        <v>84500</v>
       </c>
       <c r="I55" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM - Pop Mie (Kebutuhan Logistic di Lapangan)</t>
+          <t>ESTIMATED SUM - Chitato 68 g (Kebutuhan Logistic di Lapangan)</t>
         </is>
       </c>
     </row>
@@ -3130,7 +3130,7 @@
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
         <v>48</v>
       </c>
       <c r="H56" t="n">
-        <v>19500</v>
+        <v>9750</v>
       </c>
       <c r="I56" t="n">
         <v>0</v>
@@ -3166,7 +3166,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM - Susu Beruang (Kebutuhan Logistic di Lapangan)</t>
+          <t>ESTIMATED SUM - Pocari Sweat (Kebutuhan Logistic di Lapangan)</t>
         </is>
       </c>
     </row>
@@ -3179,7 +3179,7 @@
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -3222,13 +3222,13 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>opname_035_BSS-JOB_WS_X_2026_0</t>
+          <t>opname_013_BSS-JOB_WS_VIII_2026_0</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -3237,24 +3237,24 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="H58" t="n">
-        <v>151397500</v>
+        <v>9750</v>
       </c>
       <c r="I58" t="n">
         <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>035/BSS-JOB/WS/X/2026</t>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -3264,20 +3264,20 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM - At Cost + Fee 15% (Akomodasi Personel JOB Tomori dan Serco di Hotel King Amear Periode 07 Agustus 2026 sd 10 September 2026, Sesuai rekap  dan Kwitansi terlampir)</t>
+          <t>ESTIMATED SUM - Susu Beruang (Kebutuhan Logistic di Lapangan)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>opname_036_BSS-JOB_WS_IX_2026_4500011739</t>
+          <t>opname_013_BSS-JOB_WS_VIII_2026_0</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -3286,47 +3286,47 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>4600</v>
+        <v>48</v>
       </c>
       <c r="H59" t="n">
-        <v>25000</v>
+        <v>19500</v>
       </c>
       <c r="I59" t="n">
-        <v>316.8</v>
+        <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>489.8</v>
+        <v>48</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>036/BSS-JOB/WS/IX/2026</t>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES - Laundry services (Loundry Untuk Personel JOB dan Serco di Hotel King Amear Periode tanggal 07 Agustus sd 10 September 2026)</t>
+          <t>ESTIMATED SUM - Roti Sari Roti Coklat (Kebutuhan Logistic di Lapangan)</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>opname_030_BSS-JOB_WS_VIII_2026_-</t>
+          <t>opname_013_BSS-JOB_WS_VIII_2026_0</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -3335,34 +3335,132 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="H60" t="n">
-        <v>53762499.99999999</v>
+        <v>9750</v>
       </c>
       <c r="I60" t="n">
         <v>0</v>
       </c>
       <c r="J60" t="n">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>030/BSS-JOB/WS/VIII/2026</t>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM - At Cost + Fee 15% (Provsum Akomodasi untuk crew well services di penginapan Yellow Toili Periode tanggal 07 Agustus sd 31 Agustus 2026)</t>
+          <t>ESTIMATED SUM - Roti Sari Roti Keju (Kebutuhan Logistic di Lapangan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>opname_013_BSS-JOB_WS_VIII_2026_0</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr"/>
+      <c r="C61" t="inlineStr"/>
+      <c r="D61" t="n">
+        <v>11</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
+        <v>36</v>
+      </c>
+      <c r="H61" t="n">
+        <v>32500</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" t="n">
+        <v>36</v>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM - Roti Tawar Sari Roti (Kebutuhan Logistic di Lapangan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>opname_013_BSS-JOB_WS_VIII_2026_0</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr"/>
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" t="n">
+        <v>12</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
+        <v>72</v>
+      </c>
+      <c r="H62" t="n">
+        <v>15600</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" t="n">
+        <v>72</v>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM - Coffe Nescafe Kaleng 220 ml (Kebutuhan Logistic di Lapangan)</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_opname_parameter.xlsx
+++ b/database_penyimpanan_aman/database_opname_parameter.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\98 PROFORMA INVOICE\Dashboard Proforma Invoice General Services\database_penyimpanan_aman\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9D5A061-3AAF-4A5C-B779-7830F3B400CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D15D45B9-B1B1-44E4-9BDD-94BA5E6FE264}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -704,7 +704,7 @@
   <dimension ref="A1:M50"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="24.3984375" customWidth="1"/>
+    <col min="1" max="1" width="26.59765625" customWidth="1"/>
     <col min="2" max="2" width="18.796875" customWidth="1"/>
   </cols>
   <sheetData>

--- a/database_penyimpanan_aman/database_opname_parameter.xlsx
+++ b/database_penyimpanan_aman/database_opname_parameter.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M60"/>
+  <dimension ref="A1:M82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1703,7 +1703,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>opname_034_BSS-JOB_WS_IX_2026_0</t>
+          <t>opname_025_BSS-JOB_WS_VIII_2026_4500011739</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -1718,34 +1718,34 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H27" t="n">
-        <v>5812675</v>
+        <v>25000000</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>0.48</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>034/BSS-JOB/WS/IX/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM - At Cost + Fee 15% ((Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 19/09/2026)</t>
+          <t>ADDITIONAL CAMP SERVICES - Portacamp - Office Camp,  ukuran 40 FT (Portacamp - Office Camp,  ukuran 40 FT Untuk Support Well Services di Lokasi Senoro)</t>
         </is>
       </c>
     </row>
@@ -1758,7 +1758,7 @@
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>4</v>
       </c>
       <c r="H28" t="n">
-        <v>25000000</v>
+        <v>17500000</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES - Portacamp - Office Camp,  ukuran 40 FT (Portacamp - Office Camp,  ukuran 40 FT Untuk Support Well Services di Lokasi Senoro)</t>
+          <t>ADDITIONAL CAMP SERVICES - Portacamp - Living camp,ukuran 40FT (4 sleepers) (Portacamp - Living camp,ukuran 40FT (4 sleepers) Untuk Support Well Services di Lokasi Senoro)</t>
         </is>
       </c>
     </row>
@@ -1807,7 +1807,7 @@
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1823,13 +1823,13 @@
         <v>4</v>
       </c>
       <c r="H29" t="n">
-        <v>17500000</v>
+        <v>60000000</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>0.48</v>
+        <v>0.74</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES - Portacamp - Living camp,ukuran 40FT (4 sleepers) (Portacamp - Living camp,ukuran 40FT (4 sleepers) Untuk Support Well Services di Lokasi Senoro)</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL - Genset, cap min 80 KVA, silent type, include maintenance (Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Siang)</t>
         </is>
       </c>
     </row>
@@ -1856,7 +1856,7 @@
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL - Genset, cap min 80 KVA, silent type, include maintenance (Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Siang)</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL - Genset, cap min 80 KVA, silent type, include maintenance (Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Malam)</t>
         </is>
       </c>
     </row>
@@ -1905,7 +1905,7 @@
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1921,7 +1921,7 @@
         <v>4</v>
       </c>
       <c r="H31" t="n">
-        <v>60000000</v>
+        <v>15000000</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
@@ -1941,7 +1941,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL - Genset, cap min 80 KVA, silent type, include maintenance (Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Malam)</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL - Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories (Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam)</t>
         </is>
       </c>
     </row>
@@ -1954,7 +1954,7 @@
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1997,13 +1997,13 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>opname_025_BSS-JOB_WS_VIII_2026_4500011739</t>
+          <t>opname_024_BSS-JOB_WS_VIII_2026_4500011739</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -2016,20 +2016,20 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="H33" t="n">
-        <v>15000000</v>
+        <v>750000</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>0.74</v>
+        <v>13</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>024/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL - Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories (Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam)</t>
+          <t>PERSONEL ON CALL - Operator Crane (Operator Crane Shift Siang atas nama Rasid A Laugi)</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -2065,7 +2065,7 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>13</v>
+        <v>120</v>
       </c>
       <c r="H34" t="n">
         <v>750000</v>
@@ -2074,7 +2074,7 @@
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL - Operator Crane (Operator Crane Shift Siang atas nama Rasid A Laugi)</t>
+          <t>PERSONEL ON CALL - Operator Crane (Operator Crane Shift Siang atas nama Wanhar)</t>
         </is>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="H35" t="n">
         <v>750000</v>
@@ -2123,7 +2123,7 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -2137,7 +2137,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL - Operator Crane (Operator Crane Shift Siang atas nama Wanhar)</t>
+          <t>PERSONEL ON CALL - Operator Crane (Operator Crane Shift Malam  atas nama Ilsan Adjedar)</t>
         </is>
       </c>
     </row>
@@ -2150,7 +2150,7 @@
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -2163,16 +2163,16 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="H36" t="n">
-        <v>750000</v>
+        <v>650000</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL - Operator Crane (Operator Crane Shift Malam  atas nama Ilsan Adjedar)</t>
+          <t>PERSONEL ON CALL - Rigger (Rigger  Crane Shift Siang  atas nama Tison)</t>
         </is>
       </c>
     </row>
@@ -2199,7 +2199,7 @@
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL - Rigger (Rigger  Crane Shift Siang  atas nama Tison)</t>
+          <t>PERSONEL ON CALL - Rigger (Rigger  Crane Shift Malam  atas nama Agus Dg Mangata)</t>
         </is>
       </c>
     </row>
@@ -2248,7 +2248,7 @@
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -2261,16 +2261,16 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="H38" t="n">
-        <v>650000</v>
+        <v>600000</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL - Rigger (Rigger  Crane Shift Malam  atas nama Agus Dg Mangata)</t>
+          <t>PERSONEL ON CALL - Mechanic/ Electrician (Mechanic/ Electrician operasikan Mesin Genset dan Lighting Tower atas nama Sugeng)</t>
         </is>
       </c>
     </row>
@@ -2297,7 +2297,7 @@
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -2333,20 +2333,20 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL - Mechanic/ Electrician (Mechanic/ Electrician operasikan Mesin Genset dan Lighting Tower atas nama Sugeng)</t>
+          <t>PERSONEL ON CALL - Mechanic/ Electrician (Mechanic/ Electrician operasikan Mesin Genset dan Lighting Tower atas nama Ahmad Dhani)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>opname_024_BSS-JOB_WS_VIII_2026_4500011739</t>
+          <t>opname_026_BSS-JOB_WS_VIII_2026_4500011739</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -2359,20 +2359,20 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>240</v>
+        <v>120</v>
       </c>
       <c r="H40" t="n">
-        <v>600000</v>
+        <v>1600000</v>
       </c>
       <c r="I40" t="n">
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>024/BSS-JOB/WS/VIII/2026</t>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL - Mechanic/ Electrician (Mechanic/ Electrician operasikan Mesin Genset dan Lighting Tower atas nama Ahmad Dhani)</t>
+          <t>CAR &amp; TANSPORTATION - Station wagon 7 seater diesel engine + driver + BBM, (Kendaraan Innova DN 1259 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
         </is>
       </c>
     </row>
@@ -2395,7 +2395,7 @@
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION - Station wagon 7 seater diesel engine + driver + BBM, (Kendaraan Innova DN 1259 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
+          <t>CAR &amp; TANSPORTATION - Station wagon 7 seater diesel engine + driver + BBM, (Kendaraan Innova DN 1258 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
         </is>
       </c>
     </row>
@@ -2444,7 +2444,7 @@
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="H42" t="n">
         <v>1600000</v>
@@ -2466,7 +2466,7 @@
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION - Station wagon 7 seater diesel engine + driver + BBM, (Kendaraan Innova DN 1258 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
+          <t>CAR &amp; TANSPORTATION - Station wagon 7 seater diesel engine + driver + BBM, (Kendaraan Innova DN 1257 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
         </is>
       </c>
     </row>
@@ -2493,7 +2493,7 @@
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -2506,7 +2506,7 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>116</v>
+        <v>4</v>
       </c>
       <c r="H43" t="n">
         <v>1600000</v>
@@ -2515,7 +2515,7 @@
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -2529,7 +2529,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION - Station wagon 7 seater diesel engine + driver + BBM, (Kendaraan Innova DN 1257 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
+          <t>CAR &amp; TANSPORTATION - Station wagon 7 seater diesel engine + driver + BBM, (Kendaraan Pajero DN 1904 RA Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
         </is>
       </c>
     </row>
@@ -2542,7 +2542,7 @@
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>4</v>
+        <v>120</v>
       </c>
       <c r="H44" t="n">
         <v>1600000</v>
@@ -2564,7 +2564,7 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION - Station wagon 7 seater diesel engine + driver + BBM, (Kendaraan Pajero DN 1904 RA Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
+          <t>CAR &amp; TANSPORTATION - Double cabin 4x4, diesel engine + driver + BBM, (Kendaraan Hilux DN 1916 CH Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
         </is>
       </c>
     </row>
@@ -2591,7 +2591,7 @@
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -2627,20 +2627,20 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION - Double cabin 4x4, diesel engine + driver + BBM, (Kendaraan Hilux DN 1916 CH Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
+          <t>CAR &amp; TANSPORTATION - Double cabin 4x4, diesel engine + driver + BBM, (Kendaraan Hilux DN 1917 CH Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>opname_026_BSS-JOB_WS_VIII_2026_4500011739</t>
+          <t>opname_032_BSS-JOB_WS_VIII_2026_4500011739</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -2649,24 +2649,24 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>120</v>
+        <v>300</v>
       </c>
       <c r="H46" t="n">
-        <v>1600000</v>
+        <v>250000</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>026/BSS-JOB/WS/VIII/2026</t>
+          <t>032/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -2676,14 +2676,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION - Double cabin 4x4, diesel engine + driver + BBM, (Kendaraan Hilux DN 1917 CH Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
+          <t>PERSONEL ON CALL - Helper Local (non Skilled) (Upah harian Flagman Periode 08 sd 30 Agustus 2026)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>opname_032_BSS-JOB_WS_VIII_2026_4500011739</t>
+          <t>opname_035_BSS-JOB_WS_X_2026_0</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -2698,41 +2698,41 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>300</v>
+        <v>1</v>
       </c>
       <c r="H47" t="n">
-        <v>250000</v>
+        <v>151397500</v>
       </c>
       <c r="I47" t="n">
         <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>032/BSS-JOB/WS/VIII/2026</t>
+          <t>035/BSS-JOB/WS/X/2026</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL - Helper Local (non Skilled) (Upah harian Flagman Periode 08 sd 30 Agustus 2026)</t>
+          <t>PROVISIONAL SUM - At Cost + Fee 15% (Akomodasi Personel JOB Tomori dan Serco di Hotel King Amear Periode 07 Agustus 2026 sd 10 September 2026, Sesuai rekap  dan Kwitansi terlampir)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>opname_035_BSS-JOB_WS_X_2026_0</t>
+          <t>opname_036_BSS-JOB_WS_IX_2026_4500011739</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -2747,41 +2747,41 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>1</v>
+        <v>4600</v>
       </c>
       <c r="H48" t="n">
-        <v>151397500</v>
+        <v>25000</v>
       </c>
       <c r="I48" t="n">
-        <v>0</v>
+        <v>316.8</v>
       </c>
       <c r="J48" t="n">
-        <v>1</v>
+        <v>489.8</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>035/BSS-JOB/WS/X/2026</t>
+          <t>036/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM - At Cost + Fee 15% (Akomodasi Personel JOB Tomori dan Serco di Hotel King Amear Periode 07 Agustus 2026 sd 10 September 2026, Sesuai rekap  dan Kwitansi terlampir)</t>
+          <t>ADDITIONAL CAMP SERVICES - Laundry services (Loundry Untuk Personel JOB dan Serco di Hotel King Amear Periode tanggal 07 Agustus sd 10 September 2026)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>opname_036_BSS-JOB_WS_IX_2026_4500011739</t>
+          <t>opname_030_BSS-JOB_WS_VIII_2026_-</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -2796,41 +2796,41 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>4600</v>
+        <v>1</v>
       </c>
       <c r="H49" t="n">
-        <v>25000</v>
+        <v>53762499.99999999</v>
       </c>
       <c r="I49" t="n">
-        <v>316.8</v>
+        <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>489.8</v>
+        <v>1</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>036/BSS-JOB/WS/IX/2026</t>
+          <t>030/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES - Laundry services (Loundry Untuk Personel JOB dan Serco di Hotel King Amear Periode tanggal 07 Agustus sd 10 September 2026)</t>
+          <t>PROVISIONAL SUM - At Cost + Fee 15% (Provsum Akomodasi untuk crew well services di penginapan Yellow Toili Periode tanggal 07 Agustus sd 31 Agustus 2026)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>opname_030_BSS-JOB_WS_VIII_2026_-</t>
+          <t>opname_005_BSS-JOB_WS_V_2026_-</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -2845,24 +2845,24 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="H50" t="n">
-        <v>53762499.99999999</v>
+        <v>200000</v>
       </c>
       <c r="I50" t="n">
         <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>030/BSS-JOB/WS/VIII/2026</t>
+          <t>005/BSS-JOB/WS/V/2026</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -2872,7 +2872,8 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM - At Cost + Fee 15% (Provsum Akomodasi untuk crew well services di penginapan Yellow Toili Periode tanggal 07 Agustus sd 31 Agustus 2026)</t>
+          <t>MOVING AIR FREIGHT TRANSPORT
+Jabodetabek - Luwuk/ Senoro atau sebaliknya (Pengiriman Sample air dari Lokasi Cluster B ke Jakarta)</t>
         </is>
       </c>
     </row>
@@ -2885,29 +2886,29 @@
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="n">
+        <v>2</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
         <v>1</v>
       </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Luwuk</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="G51" t="n">
-        <v>16</v>
-      </c>
       <c r="H51" t="n">
-        <v>200000</v>
+        <v>250000</v>
       </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -2922,7 +2923,7 @@
       <c r="M51" t="inlineStr">
         <is>
           <t>MOVING AIR FREIGHT TRANSPORT
-Jabodetabek - Luwuk/ Senoro atau sebaliknya (Pengiriman Sample air dari Lokasi Cluster B ke Jakarta)</t>
+Jasa repacking for Airfreight, estimasi ukuran pallet 100x100x100 cm (Pembuatan Pallet Sample Air (packing Barang))</t>
         </is>
       </c>
     </row>
@@ -2935,7 +2936,7 @@
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2951,7 +2952,7 @@
         <v>1</v>
       </c>
       <c r="H52" t="n">
-        <v>250000</v>
+        <v>1600000</v>
       </c>
       <c r="I52" t="n">
         <v>0</v>
@@ -2971,8 +2972,8 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>MOVING AIR FREIGHT TRANSPORT
-Jasa repacking for Airfreight, estimasi ukuran pallet 100x100x100 cm (Pembuatan Pallet Sample Air (packing Barang))</t>
+          <t>CAR &amp; TANSPORTATION
+Double cabin 4x4, diesel engine + driver + BBM, (Pickup Material di Luwuk tgl 18 Mei 2026 dari Lokasi ke Bandara)</t>
         </is>
       </c>
     </row>
@@ -2985,7 +2986,7 @@
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2998,16 +2999,16 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H53" t="n">
-        <v>1600000</v>
+        <v>350000</v>
       </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -3021,8 +3022,8 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION
-Double cabin 4x4, diesel engine + driver + BBM, (Pickup Material di Luwuk tgl 18 Mei 2026 dari Lokasi ke Bandara)</t>
+          <t>PERSONEL ON CALL
+Helper Local (Skilled) (Personel untuk pengurusan Barang di Luwuk dan Personel untuk pengurusan barang di Jakarta)</t>
         </is>
       </c>
     </row>
@@ -3035,7 +3036,7 @@
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -3048,16 +3049,16 @@
         </is>
       </c>
       <c r="G54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H54" t="n">
-        <v>350000</v>
+        <v>3250000</v>
       </c>
       <c r="I54" t="n">
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -3071,21 +3072,21 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL
-Helper Local (Skilled) (Personel untuk pengurusan Barang di Luwuk dan Personel untuk pengurusan barang di Jakarta)</t>
+          <t>ESTIMATED SUM
+Jasa Transportasi dari dan ke Bandara Jasa transportasi menggunakan Pickup Air Port Cengkareng ke Jabodetabek dan sebaliknya (Land transportasi dari bandara Cengkareng ke alamat penerima sample air PT.Haliburton)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>opname_005_BSS-JOB_WS_V_2026_-</t>
+          <t>opname_011_BSS-JOB_WS_VIII_2026_-</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -3094,14 +3095,14 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G55" t="n">
         <v>1</v>
       </c>
       <c r="H55" t="n">
-        <v>3250000</v>
+        <v>1600000</v>
       </c>
       <c r="I55" t="n">
         <v>0</v>
@@ -3111,7 +3112,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>005/BSS-JOB/WS/V/2026</t>
+          <t>011/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -3121,8 +3122,8 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM
-Jasa Transportasi dari dan ke Bandara Jasa transportasi menggunakan Pickup Air Port Cengkareng ke Jabodetabek dan sebaliknya (Land transportasi dari bandara Cengkareng ke alamat penerima sample air PT.Haliburton)</t>
+          <t>CAR &amp; TANSPORTATION
+Double cabin 4x4, diesel engine + driver + BBM, (Pengambilan Material Pop Joint di Senoro 2 ke Luwuk)</t>
         </is>
       </c>
     </row>
@@ -3135,7 +3136,7 @@
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -3151,7 +3152,7 @@
         <v>1</v>
       </c>
       <c r="H56" t="n">
-        <v>1600000</v>
+        <v>250000</v>
       </c>
       <c r="I56" t="n">
         <v>0</v>
@@ -3171,8 +3172,8 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION
-Double cabin 4x4, diesel engine + driver + BBM, (Pengambilan Material Pop Joint di Senoro 2 ke Luwuk)</t>
+          <t>MOVING AIR FREIGHT TRANSPORT
+Jasa repacking for Airfreight, estimasi ukuran pallet 100x100x100 cm (Pembuatan Pallet untuk Pop Joint)</t>
         </is>
       </c>
     </row>
@@ -3185,29 +3186,29 @@
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="n">
+        <v>3</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
         <v>2</v>
       </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Luwuk</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="G57" t="n">
-        <v>1</v>
-      </c>
       <c r="H57" t="n">
-        <v>250000</v>
+        <v>350000</v>
       </c>
       <c r="I57" t="n">
         <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
@@ -3221,8 +3222,8 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>MOVING AIR FREIGHT TRANSPORT
-Jasa repacking for Airfreight, estimasi ukuran pallet 100x100x100 cm (Pembuatan Pallet untuk Pop Joint)</t>
+          <t>PERSONEL ON CALL
+Helper Local (Skilled) (Personel Handling di Luwuk-Bandara 1 orang dan Jakarta-Bogor 1 orang)</t>
         </is>
       </c>
     </row>
@@ -3235,7 +3236,7 @@
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -3248,16 +3249,16 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>2</v>
+        <v>105</v>
       </c>
       <c r="H58" t="n">
-        <v>350000</v>
+        <v>200000</v>
       </c>
       <c r="I58" t="n">
         <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>2</v>
+        <v>105</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -3271,8 +3272,8 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL
-Helper Local (Skilled) (Personel Handling di Luwuk-Bandara 1 orang dan Jakarta-Bogor 1 orang)</t>
+          <t>MOVING AIR FREIGHT TRANSPORT
+Jabodetabek - Luwuk/ Senoro atau sebaliknya (Cargo Barang   Air Freight Material Pop Joint yang dikirim)</t>
         </is>
       </c>
     </row>
@@ -3285,7 +3286,7 @@
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -3298,16 +3299,16 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>105</v>
+        <v>1</v>
       </c>
       <c r="H59" t="n">
-        <v>200000</v>
+        <v>3250000</v>
       </c>
       <c r="I59" t="n">
         <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>105</v>
+        <v>1</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -3321,58 +3322,1158 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>MOVING AIR FREIGHT TRANSPORT
-Jabodetabek - Luwuk/ Senoro atau sebaliknya (Cargo Barang   Air Freight Material Pop Joint yang dikirim)</t>
+          <t>ESTIMATED SUM
+Jasa Transportasi dari dan ke Bandara Jasa transportasi menggunakan Pickup Air Port Cengkareng ke Jabodetabek dan sebaliknya (Pengiriman barang Pop Joint dari Bandara Cengkareng ke Bogor alamat  Lamda Multi Dinamika yard)</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>opname_011_BSS-JOB_WS_VIII_2026_-</t>
+          <t>opname_034_BSS-JOB_WS_IX_2026_0</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="n">
+        <v>2</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
+        <v>6</v>
+      </c>
+      <c r="H60" t="n">
+        <v>84500</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" t="n">
+        <v>6</v>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>034/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM
+Kopi Kapal Api 380 g (Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>opname_034_BSS-JOB_WS_IX_2026_0</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr"/>
+      <c r="C61" t="inlineStr"/>
+      <c r="D61" t="n">
+        <v>3</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
         <v>5</v>
       </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>Luwuk</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="G60" t="n">
+      <c r="H61" t="n">
+        <v>26000</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" t="n">
+        <v>5</v>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>034/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM
+Nescafe Classic renteng (Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>opname_034_BSS-JOB_WS_IX_2026_0</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr"/>
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" t="n">
+        <v>4</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
+        <v>72</v>
+      </c>
+      <c r="H62" t="n">
+        <v>9750</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" t="n">
+        <v>72</v>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>034/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM
+Pop Mie (Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>opname_034_BSS-JOB_WS_IX_2026_0</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr"/>
+      <c r="C63" t="inlineStr"/>
+      <c r="D63" t="n">
+        <v>5</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>10</v>
+      </c>
+      <c r="H63" t="n">
+        <v>19500</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" t="n">
+        <v>10</v>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>034/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM
+Chitato 68 g (Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>opname_034_BSS-JOB_WS_IX_2026_0</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr"/>
+      <c r="C64" t="inlineStr"/>
+      <c r="D64" t="n">
+        <v>6</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
+        <v>72</v>
+      </c>
+      <c r="H64" t="n">
+        <v>13000</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" t="n">
+        <v>72</v>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>034/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM
+Pocari Sweat (Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>opname_034_BSS-JOB_WS_IX_2026_0</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr"/>
+      <c r="C65" t="inlineStr"/>
+      <c r="D65" t="n">
+        <v>7</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
+        <v>72</v>
+      </c>
+      <c r="H65" t="n">
+        <v>9750</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" t="n">
+        <v>72</v>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>034/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM
+Teh Kotak (Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>opname_034_BSS-JOB_WS_IX_2026_0</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr"/>
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" t="n">
+        <v>8</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G66" t="n">
+        <v>72</v>
+      </c>
+      <c r="H66" t="n">
+        <v>19500</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" t="n">
+        <v>72</v>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>034/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM
+Susu Beruang (Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>opname_034_BSS-JOB_WS_IX_2026_0</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr"/>
+      <c r="C67" t="inlineStr"/>
+      <c r="D67" t="n">
+        <v>9</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G67" t="n">
+        <v>48</v>
+      </c>
+      <c r="H67" t="n">
+        <v>15600</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" t="n">
+        <v>48</v>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>034/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM
+Coffe Nescafe Kaleng 220 ml (Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>opname_034_BSS-JOB_WS_IX_2026_0</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr"/>
+      <c r="C68" t="inlineStr"/>
+      <c r="D68" t="n">
+        <v>10</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G68" t="n">
+        <v>10</v>
+      </c>
+      <c r="H68" t="n">
+        <v>32500</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" t="n">
+        <v>10</v>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>034/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM
+Roti Sari Roti Coklat (Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>opname_034_BSS-JOB_WS_IX_2026_0</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr"/>
+      <c r="C69" t="inlineStr"/>
+      <c r="D69" t="n">
+        <v>11</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>10</v>
+      </c>
+      <c r="H69" t="n">
+        <v>32500</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" t="n">
+        <v>10</v>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>034/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM
+Roti Sari Roti Keju (Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>opname_034_BSS-JOB_WS_IX_2026_0</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr"/>
+      <c r="C70" t="inlineStr"/>
+      <c r="D70" t="n">
+        <v>12</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G70" t="n">
+        <v>10</v>
+      </c>
+      <c r="H70" t="n">
+        <v>32500</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" t="n">
+        <v>10</v>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>034/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM
+Roti Tawar Sari Roti (Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>opname_037_BSS-JOB_WS_IX_2026_0</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr"/>
+      <c r="C71" t="inlineStr"/>
+      <c r="D71" t="n">
         <v>1</v>
       </c>
-      <c r="H60" t="n">
-        <v>3250000</v>
-      </c>
-      <c r="I60" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" t="n">
-        <v>1</v>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>011/BSS-JOB/WS/VIII/2026</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr">
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G71" t="n">
+        <v>5</v>
+      </c>
+      <c r="H71" t="n">
+        <v>32500</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" t="n">
+        <v>5</v>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>037/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
         <is>
           <t>ESTIMATED SUM
-Jasa Transportasi dari dan ke Bandara Jasa transportasi menggunakan Pickup Air Port Cengkareng ke Jabodetabek dan sebaliknya (Pengiriman barang Pop Joint dari Bandara Cengkareng ke Bogor alamat  Lamda Multi Dinamika yard)</t>
+Indocafe Coffemix Renteng (Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>opname_037_BSS-JOB_WS_IX_2026_0</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr"/>
+      <c r="C72" t="inlineStr"/>
+      <c r="D72" t="n">
+        <v>2</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
+        <v>6</v>
+      </c>
+      <c r="H72" t="n">
+        <v>84500</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" t="n">
+        <v>6</v>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>037/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM
+Kopi Kapal Api 380 g (Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>opname_037_BSS-JOB_WS_IX_2026_0</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr"/>
+      <c r="C73" t="inlineStr"/>
+      <c r="D73" t="n">
+        <v>3</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G73" t="n">
+        <v>5</v>
+      </c>
+      <c r="H73" t="n">
+        <v>26000</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" t="n">
+        <v>5</v>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>037/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM
+Nescafe Classic renteng (Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>opname_037_BSS-JOB_WS_IX_2026_0</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr"/>
+      <c r="C74" t="inlineStr"/>
+      <c r="D74" t="n">
+        <v>4</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G74" t="n">
+        <v>72</v>
+      </c>
+      <c r="H74" t="n">
+        <v>9750</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" t="n">
+        <v>72</v>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>037/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM
+Pop Mie (Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>opname_037_BSS-JOB_WS_IX_2026_0</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr"/>
+      <c r="C75" t="inlineStr"/>
+      <c r="D75" t="n">
+        <v>5</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G75" t="n">
+        <v>10</v>
+      </c>
+      <c r="H75" t="n">
+        <v>19500</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" t="n">
+        <v>10</v>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>037/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM
+Chitato 68 g (Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>opname_037_BSS-JOB_WS_IX_2026_0</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr"/>
+      <c r="C76" t="inlineStr"/>
+      <c r="D76" t="n">
+        <v>6</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G76" t="n">
+        <v>72</v>
+      </c>
+      <c r="H76" t="n">
+        <v>13000</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" t="n">
+        <v>72</v>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>037/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM
+Pocari Sweat (Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>opname_037_BSS-JOB_WS_IX_2026_0</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr"/>
+      <c r="C77" t="inlineStr"/>
+      <c r="D77" t="n">
+        <v>7</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G77" t="n">
+        <v>72</v>
+      </c>
+      <c r="H77" t="n">
+        <v>9750</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" t="n">
+        <v>72</v>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>037/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM
+Teh Kotak (Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>opname_037_BSS-JOB_WS_IX_2026_0</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr"/>
+      <c r="C78" t="inlineStr"/>
+      <c r="D78" t="n">
+        <v>8</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G78" t="n">
+        <v>72</v>
+      </c>
+      <c r="H78" t="n">
+        <v>19500</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" t="n">
+        <v>72</v>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>037/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM
+Susu Beruang (Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>opname_037_BSS-JOB_WS_IX_2026_0</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr"/>
+      <c r="C79" t="inlineStr"/>
+      <c r="D79" t="n">
+        <v>9</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G79" t="n">
+        <v>48</v>
+      </c>
+      <c r="H79" t="n">
+        <v>15600</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" t="n">
+        <v>48</v>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>037/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM
+Coffe Nescafe Kaleng 220 ml (Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>opname_037_BSS-JOB_WS_IX_2026_0</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr"/>
+      <c r="C80" t="inlineStr"/>
+      <c r="D80" t="n">
+        <v>10</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G80" t="n">
+        <v>10</v>
+      </c>
+      <c r="H80" t="n">
+        <v>32500</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" t="n">
+        <v>10</v>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>037/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM
+Roti Sari Roti Coklat (Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>opname_037_BSS-JOB_WS_IX_2026_0</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr"/>
+      <c r="C81" t="inlineStr"/>
+      <c r="D81" t="n">
+        <v>11</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G81" t="n">
+        <v>10</v>
+      </c>
+      <c r="H81" t="n">
+        <v>32500</v>
+      </c>
+      <c r="I81" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" t="n">
+        <v>10</v>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>037/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM
+Roti Sari Roti Keju (Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>opname_037_BSS-JOB_WS_IX_2026_0</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr"/>
+      <c r="C82" t="inlineStr"/>
+      <c r="D82" t="n">
+        <v>12</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G82" t="n">
+        <v>10</v>
+      </c>
+      <c r="H82" t="n">
+        <v>32500</v>
+      </c>
+      <c r="I82" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" t="n">
+        <v>10</v>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>037/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM
+Roti Tawar Sari Roti (Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026)</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_opname_parameter.xlsx
+++ b/database_penyimpanan_aman/database_opname_parameter.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M82"/>
+  <dimension ref="A1:M103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4477,6 +4477,1056 @@
         </is>
       </c>
     </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>opname_038_BSS-JOB_WS_IX_2026_4500011739</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr"/>
+      <c r="C83" t="inlineStr"/>
+      <c r="D83" t="n">
+        <v>1</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G83" t="n">
+        <v>18300</v>
+      </c>
+      <c r="H83" t="n">
+        <v>65000</v>
+      </c>
+      <c r="I83" t="n">
+        <v>2578</v>
+      </c>
+      <c r="J83" t="n">
+        <v>3195</v>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>038/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES
+Food &amp; beverage, main course (DDITIONAL CAMP SERVICES, Operational Consumption)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>opname_038_BSS-JOB_WS_IX_2026_4500011739</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr"/>
+      <c r="C84" t="inlineStr"/>
+      <c r="D84" t="n">
+        <v>2</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G84" t="n">
+        <v>9200</v>
+      </c>
+      <c r="H84" t="n">
+        <v>33000</v>
+      </c>
+      <c r="I84" t="n">
+        <v>1157</v>
+      </c>
+      <c r="J84" t="n">
+        <v>1486.5</v>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>038/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES
+Food &amp; beverage, snack coffee/ tea &amp; desert (ADDITIONAL CAMP SERVICES, Operational side consumption)</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>opname_040_BSS-JOB_WS_IX_2026_4500011739</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr"/>
+      <c r="C85" t="inlineStr"/>
+      <c r="D85" t="n">
+        <v>1</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G85" t="n">
+        <v>240</v>
+      </c>
+      <c r="H85" t="n">
+        <v>750000</v>
+      </c>
+      <c r="I85" t="n">
+        <v>23</v>
+      </c>
+      <c r="J85" t="n">
+        <v>30</v>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>040/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL
+Personnel GS in-charge di lokasi pemboran/ wellservices/ workover, personnel in charge (Personnel GS - Koordinator Lapangan atas nama Nur Afiata Periode 01 sd 30 September 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>opname_041_BSS-JOB_WS_IX_2026_4500011739</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr"/>
+      <c r="C86" t="inlineStr"/>
+      <c r="D86" t="n">
+        <v>1</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G86" t="n">
+        <v>30</v>
+      </c>
+      <c r="H86" t="n">
+        <v>500000</v>
+      </c>
+      <c r="I86" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" t="n">
+        <v>30</v>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>041/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL
+Welder (GTAW) (Support Kegiatan Well Services di Senoro personel  Welder = HSE Officer ( Gusti Ngurah Dwipayana))</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>opname_041_BSS-JOB_WS_IX_2026_4500011739</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr"/>
+      <c r="C87" t="inlineStr"/>
+      <c r="D87" t="n">
+        <v>2</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G87" t="n">
+        <v>30</v>
+      </c>
+      <c r="H87" t="n">
+        <v>500000</v>
+      </c>
+      <c r="I87" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" t="n">
+        <v>30</v>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>041/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL
+Welder (GTAW) (Support Kegiatan Well Services di Senoro personel  Welder = Paramedic  ( Meliita Bella))</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>opname_041_BSS-JOB_WS_IX_2026_4500011739</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr"/>
+      <c r="C88" t="inlineStr"/>
+      <c r="D88" t="n">
+        <v>3</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G88" t="n">
+        <v>30</v>
+      </c>
+      <c r="H88" t="n">
+        <v>500000</v>
+      </c>
+      <c r="I88" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" t="n">
+        <v>30</v>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>041/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL
+Welder (GTAW) (Support Kegiatan Well Services di Senoro personel  Welder = Paramedic  ( Widiya Satuo))</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>opname_042_BSS-JOB_WS_IX_2026_4500011739</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr"/>
+      <c r="C89" t="inlineStr"/>
+      <c r="D89" t="n">
+        <v>1</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G89" t="n">
+        <v>120</v>
+      </c>
+      <c r="H89" t="n">
+        <v>750000</v>
+      </c>
+      <c r="I89" t="n">
+        <v>9</v>
+      </c>
+      <c r="J89" t="n">
+        <v>30</v>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>042/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL
+Operator Crane (Operator Crane Shift Siang atas Nama Wanhar Renaldi)</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>opname_042_BSS-JOB_WS_IX_2026_4500011739</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr"/>
+      <c r="C90" t="inlineStr"/>
+      <c r="D90" t="n">
+        <v>2</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G90" t="n">
+        <v>120</v>
+      </c>
+      <c r="H90" t="n">
+        <v>750000</v>
+      </c>
+      <c r="I90" t="n">
+        <v>30</v>
+      </c>
+      <c r="J90" t="n">
+        <v>30</v>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>042/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL
+Operator Crane (Operator Crane Shift Malam atas Nama Ilsan Adjedar)</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>opname_042_BSS-JOB_WS_IX_2026_4500011739</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr"/>
+      <c r="C91" t="inlineStr"/>
+      <c r="D91" t="n">
+        <v>3</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G91" t="n">
+        <v>120</v>
+      </c>
+      <c r="H91" t="n">
+        <v>650000</v>
+      </c>
+      <c r="I91" t="n">
+        <v>22</v>
+      </c>
+      <c r="J91" t="n">
+        <v>30</v>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>042/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL
+Rigger (RIgger Crane Shift Siang atas Nama Tison)</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>opname_042_BSS-JOB_WS_IX_2026_4500011739</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr"/>
+      <c r="C92" t="inlineStr"/>
+      <c r="D92" t="n">
+        <v>4</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G92" t="n">
+        <v>120</v>
+      </c>
+      <c r="H92" t="n">
+        <v>650000</v>
+      </c>
+      <c r="I92" t="n">
+        <v>21</v>
+      </c>
+      <c r="J92" t="n">
+        <v>30</v>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>042/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL
+Rigger (Rigger Crane Shift Malam atas Nama Agus Dg Mangata)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>opname_042_BSS-JOB_WS_IX_2026_4500011739</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr"/>
+      <c r="C93" t="inlineStr"/>
+      <c r="D93" t="n">
+        <v>5</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G93" t="n">
+        <v>240</v>
+      </c>
+      <c r="H93" t="n">
+        <v>600000</v>
+      </c>
+      <c r="I93" t="n">
+        <v>23</v>
+      </c>
+      <c r="J93" t="n">
+        <v>30</v>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>042/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL
+Mechanic/ Electrician (Operator Mesin Genset dan Ligting Tower Shift Siang atas nama Sugeng)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>opname_042_BSS-JOB_WS_IX_2026_4500011739</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr"/>
+      <c r="C94" t="inlineStr"/>
+      <c r="D94" t="n">
+        <v>6</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G94" t="n">
+        <v>240</v>
+      </c>
+      <c r="H94" t="n">
+        <v>600000</v>
+      </c>
+      <c r="I94" t="n">
+        <v>23</v>
+      </c>
+      <c r="J94" t="n">
+        <v>30</v>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>042/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL
+Mechanic/ Electrician (Operator Mesin Genset dan Ligting Tower Shift Siang atas nama Ahmad Dhani)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>opname_043_BSS-JOB_WS_IX_2026_4500011739</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr"/>
+      <c r="C95" t="inlineStr"/>
+      <c r="D95" t="n">
+        <v>1</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G95" t="n">
+        <v>30</v>
+      </c>
+      <c r="H95" t="n">
+        <v>500000</v>
+      </c>
+      <c r="I95" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" t="n">
+        <v>30</v>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>043/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL
+Operator Heavy Equipment (Vacuum Truck) (Driver Vacuum Truck atas nama Wijayanto Sucipto)</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>opname_044_BSS-JOB_WS_IX_2026_4500011739</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr"/>
+      <c r="C96" t="inlineStr"/>
+      <c r="D96" t="n">
+        <v>1</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="G96" t="n">
+        <v>300</v>
+      </c>
+      <c r="H96" t="n">
+        <v>250000</v>
+      </c>
+      <c r="I96" t="n">
+        <v>48</v>
+      </c>
+      <c r="J96" t="n">
+        <v>48</v>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>044/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL
+Helper Local (non Skilled) (PERSONNEL ON-CALL Helper Local (non Skilled) Tenaga Flagman Periode tgl 4 sd 11 September 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>opname_045_BSS-JOB_WS_IX_2026_4500011739</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr"/>
+      <c r="C97" t="inlineStr"/>
+      <c r="D97" t="n">
+        <v>1</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G97" t="n">
+        <v>120</v>
+      </c>
+      <c r="H97" t="n">
+        <v>8500000</v>
+      </c>
+      <c r="I97" t="n">
+        <v>16</v>
+      </c>
+      <c r="J97" t="n">
+        <v>30</v>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>045/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL
+crane min 70 ton, call out, (hanya unit) (Crane Sany 100 ton menggantikan Crane Tadano 70 ton yang rusak Operasi periode 01 sd 30 September 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>opname_045_BSS-JOB_WS_IX_2026_4500011739</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr"/>
+      <c r="C98" t="inlineStr"/>
+      <c r="D98" t="n">
+        <v>2</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G98" t="n">
+        <v>120</v>
+      </c>
+      <c r="H98" t="n">
+        <v>2750000</v>
+      </c>
+      <c r="I98" t="n">
+        <v>21</v>
+      </c>
+      <c r="J98" t="n">
+        <v>30</v>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>045/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL
+Vacuum Truck , Call out, Cap  5000 ltr c/w vacuum pump &amp; acessories, call out, (hanya unit) (Vacuum Truck , Call out, Cap  5000 ltr  Operasi periode 01 sd 30 September 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>opname_046_BSS-JOB_WS_IX_2026_4500011739</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr"/>
+      <c r="C99" t="inlineStr"/>
+      <c r="D99" t="n">
+        <v>1</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="G99" t="n">
+        <v>120</v>
+      </c>
+      <c r="H99" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="I99" t="n">
+        <v>25</v>
+      </c>
+      <c r="J99" t="n">
+        <v>30</v>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>046/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>CAR &amp; TANSPORTATION
+Station wagon 7 seater diesel engine + driver + BBM, (Kendaraan Inova DN 1259 CL  Support Well Services Periode tanggal 01 sd 30 September 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>opname_046_BSS-JOB_WS_IX_2026_4500011739</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr"/>
+      <c r="C100" t="inlineStr"/>
+      <c r="D100" t="n">
+        <v>2</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="G100" t="n">
+        <v>120</v>
+      </c>
+      <c r="H100" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="I100" t="n">
+        <v>25</v>
+      </c>
+      <c r="J100" t="n">
+        <v>30</v>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>046/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>CAR &amp; TANSPORTATION
+Station wagon 7 seater diesel engine + driver + BBM, (Kendaraan Inova DN 1257 CL  Support Well Services Periode tanggal 01 sd 30 September 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>opname_046_BSS-JOB_WS_IX_2026_4500011739</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr"/>
+      <c r="C101" t="inlineStr"/>
+      <c r="D101" t="n">
+        <v>3</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="G101" t="n">
+        <v>120</v>
+      </c>
+      <c r="H101" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="I101" t="n">
+        <v>19</v>
+      </c>
+      <c r="J101" t="n">
+        <v>4</v>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>046/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>CAR &amp; TANSPORTATION
+Station wagon 7 seater diesel engine + driver + BBM, (Kendaraan Inova DN 1258 CL  Support Well Services Periode tanggal 27 sd 30 September 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>opname_046_BSS-JOB_WS_IX_2026_4500011739</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr"/>
+      <c r="C102" t="inlineStr"/>
+      <c r="D102" t="n">
+        <v>4</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="G102" t="n">
+        <v>120</v>
+      </c>
+      <c r="H102" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="I102" t="n">
+        <v>25</v>
+      </c>
+      <c r="J102" t="n">
+        <v>30</v>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>046/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>CAR &amp; TANSPORTATION
+Double cabin 4x4, diesel engine + driver + BBM, (Kendaraan Double Cabin Hilux DN 1916 CH  Support Well Services Periode tanggal 01 sd 30 September 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>opname_046_BSS-JOB_WS_IX_2026_4500011739</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr"/>
+      <c r="C103" t="inlineStr"/>
+      <c r="D103" t="n">
+        <v>5</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="G103" t="n">
+        <v>120</v>
+      </c>
+      <c r="H103" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="I103" t="n">
+        <v>22</v>
+      </c>
+      <c r="J103" t="n">
+        <v>30</v>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>046/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>CAR &amp; TANSPORTATION
+Double cabin 4x4, diesel engine + driver + BBM, (Kendaraan Double Cabin Hilux DN 1917 CH  Support Well Services Periode tanggal 01 sd 30 September 2026)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database_penyimpanan_aman/database_opname_parameter.xlsx
+++ b/database_penyimpanan_aman/database_opname_parameter.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M103"/>
+  <dimension ref="A1:M113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5295,7 +5295,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -5345,7 +5345,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -5395,7 +5395,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -5445,7 +5445,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -5455,7 +5455,7 @@
         <v>1600000</v>
       </c>
       <c r="I102" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J102" t="n">
         <v>30</v>
@@ -5495,7 +5495,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -5524,6 +5524,506 @@
         <is>
           <t>CAR &amp; TANSPORTATION
 Double cabin 4x4, diesel engine + driver + BBM, (Kendaraan Double Cabin Hilux DN 1917 CH  Support Well Services Periode tanggal 01 sd 30 September 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>opname_047_BSS-JOB_WS_IX_2026_4500011739</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr"/>
+      <c r="C104" t="inlineStr"/>
+      <c r="D104" t="n">
+        <v>1</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G104" t="n">
+        <v>4</v>
+      </c>
+      <c r="H104" t="n">
+        <v>25000000</v>
+      </c>
+      <c r="I104" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="J104" t="n">
+        <v>1</v>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>047/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES
+Portacamp - Office Camp,  ukuran 40 FT (Portacamp - Office Camp,  ukuran 40 FT, Support Well Services Senoro Periode 01 sd 30 September 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>opname_047_BSS-JOB_WS_IX_2026_4500011739</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr"/>
+      <c r="C105" t="inlineStr"/>
+      <c r="D105" t="n">
+        <v>2</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G105" t="n">
+        <v>4</v>
+      </c>
+      <c r="H105" t="n">
+        <v>17500000</v>
+      </c>
+      <c r="I105" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="J105" t="n">
+        <v>1</v>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>047/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES
+Portacamp - Living camp,ukuran 40FT (4 sleepers) (Portacamp - Living camp,ukuran 40FT (4 sleepers)  Support Well Services Senoro Periode 01 sd 30 September 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>opname_047_BSS-JOB_WS_IX_2026_4500011739</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr"/>
+      <c r="C106" t="inlineStr"/>
+      <c r="D106" t="n">
+        <v>3</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G106" t="n">
+        <v>4</v>
+      </c>
+      <c r="H106" t="n">
+        <v>60000000</v>
+      </c>
+      <c r="I106" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="J106" t="n">
+        <v>1</v>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>047/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL
+Genset, cap min 80 KVA, silent type, include maintenance (Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Siang Periode 01 sd 30 September 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>opname_047_BSS-JOB_WS_IX_2026_4500011739</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr"/>
+      <c r="C107" t="inlineStr"/>
+      <c r="D107" t="n">
+        <v>4</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G107" t="n">
+        <v>4</v>
+      </c>
+      <c r="H107" t="n">
+        <v>60000000</v>
+      </c>
+      <c r="I107" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="J107" t="n">
+        <v>1</v>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>047/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL
+Genset, cap min 80 KVA, silent type, include maintenance (Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Malam Periode 01 sd 30 September 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>opname_047_BSS-JOB_WS_IX_2026_4500011739</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr"/>
+      <c r="C108" t="inlineStr"/>
+      <c r="D108" t="n">
+        <v>5</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G108" t="n">
+        <v>4</v>
+      </c>
+      <c r="H108" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="I108" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="J108" t="n">
+        <v>1</v>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>047/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL
+Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories (Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories, Operasi Shift Malam Periode 01 sd 30 September 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>opname_047_BSS-JOB_WS_IX_2026_4500011739</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr"/>
+      <c r="C109" t="inlineStr"/>
+      <c r="D109" t="n">
+        <v>6</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G109" t="n">
+        <v>4</v>
+      </c>
+      <c r="H109" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="I109" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="J109" t="n">
+        <v>1</v>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>047/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL
+Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories (Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Shift Malam Periode 01 sd 30 September 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>opname_048_BSS-JOB_WS_IX_2026_4500011739</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr"/>
+      <c r="C110" t="inlineStr"/>
+      <c r="D110" t="n">
+        <v>1</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G110" t="n">
+        <v>4600</v>
+      </c>
+      <c r="H110" t="n">
+        <v>25000</v>
+      </c>
+      <c r="I110" t="n">
+        <v>806.6</v>
+      </c>
+      <c r="J110" t="n">
+        <v>458.4</v>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>048/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES
+Laundry services (Laundry services, Untuk Personel Serco Periode 01 sd 30 September 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>opname_049_BSS-JOB_WS_IX_2026_-</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr"/>
+      <c r="C111" t="inlineStr"/>
+      <c r="D111" t="n">
+        <v>1</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G111" t="n">
+        <v>2188</v>
+      </c>
+      <c r="H111" t="n">
+        <v>7500</v>
+      </c>
+      <c r="I111" t="n">
+        <v>0</v>
+      </c>
+      <c r="J111" t="n">
+        <v>2188</v>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>049/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM
+Aqua 600 ml (Etimated SUM Penyediaan  Air Mineral Aqua 600 ml untuk Support Pekerjaan Well Services di Senoro Periode 01 sd 30 September 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>opname_049_BSS-JOB_WS_IX_2026_-</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr"/>
+      <c r="C112" t="inlineStr"/>
+      <c r="D112" t="n">
+        <v>2</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G112" t="n">
+        <v>15</v>
+      </c>
+      <c r="H112" t="n">
+        <v>53300</v>
+      </c>
+      <c r="I112" t="n">
+        <v>0</v>
+      </c>
+      <c r="J112" t="n">
+        <v>15</v>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>049/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM
+Aqua Galon Segel (Etimated SUM Penyediaan  Air Mineral Aqua Galon Segel untuk Support Pekerjaan Well Services di Senoro Periode 01 sd 30 September 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>opname_050_BSS-JOB_WS_IX_2026_-</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr"/>
+      <c r="C113" t="inlineStr"/>
+      <c r="D113" t="n">
+        <v>1</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G113" t="n">
+        <v>1</v>
+      </c>
+      <c r="H113" t="n">
+        <v>69000000</v>
+      </c>
+      <c r="I113" t="n">
+        <v>0</v>
+      </c>
+      <c r="J113" t="n">
+        <v>1</v>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>050/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>PROVISIONAL SUM
+At Cost + Fee 15% (Provisional SUM  Akomodasi untuk crew well services di penginapan Yellow Toili Periode 01 sd 30 September 2026)</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_opname_parameter.xlsx
+++ b/database_penyimpanan_aman/database_opname_parameter.xlsx
@@ -5530,7 +5530,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>opname_047_BSS-JOB_WS_IX_2026_4500011739</t>
+          <t>opname_048_BSS-JOB_WS_IX_2026_4500011739</t>
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
@@ -5549,20 +5549,20 @@
         </is>
       </c>
       <c r="G104" t="n">
-        <v>4</v>
+        <v>4600</v>
       </c>
       <c r="H104" t="n">
-        <v>25000000</v>
+        <v>25000</v>
       </c>
       <c r="I104" t="n">
-        <v>0.48</v>
+        <v>806.6</v>
       </c>
       <c r="J104" t="n">
-        <v>1</v>
+        <v>458.4</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>047/BSS-JOB/WS/IX/2026</t>
+          <t>048/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -5573,20 +5573,20 @@
       <c r="M104" t="inlineStr">
         <is>
           <t>ADDITIONAL CAMP SERVICES
-Portacamp - Office Camp,  ukuran 40 FT (Portacamp - Office Camp,  ukuran 40 FT, Support Well Services Senoro Periode 01 sd 30 September 2026)</t>
+Laundry services (Laundry services, Untuk Personel Serco Periode 01 sd 30 September 2026)</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>opname_047_BSS-JOB_WS_IX_2026_4500011739</t>
+          <t>opname_049_BSS-JOB_WS_IX_2026_-</t>
         </is>
       </c>
       <c r="B105" t="inlineStr"/>
       <c r="C105" t="inlineStr"/>
       <c r="D105" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -5599,44 +5599,44 @@
         </is>
       </c>
       <c r="G105" t="n">
-        <v>4</v>
+        <v>2188</v>
       </c>
       <c r="H105" t="n">
-        <v>17500000</v>
+        <v>7500</v>
       </c>
       <c r="I105" t="n">
-        <v>0.48</v>
+        <v>0</v>
       </c>
       <c r="J105" t="n">
-        <v>1</v>
+        <v>2188</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>047/BSS-JOB/WS/IX/2026</t>
+          <t>049/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES
-Portacamp - Living camp,ukuran 40FT (4 sleepers) (Portacamp - Living camp,ukuran 40FT (4 sleepers)  Support Well Services Senoro Periode 01 sd 30 September 2026)</t>
+          <t>ESTIMATED SUM
+Aqua 600 ml (Etimated SUM Penyediaan  Air Mineral Aqua 600 ml untuk Support Pekerjaan Well Services di Senoro Periode 01 sd 30 September 2026)</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>opname_047_BSS-JOB_WS_IX_2026_4500011739</t>
+          <t>opname_049_BSS-JOB_WS_IX_2026_-</t>
         </is>
       </c>
       <c r="B106" t="inlineStr"/>
       <c r="C106" t="inlineStr"/>
       <c r="D106" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -5649,44 +5649,44 @@
         </is>
       </c>
       <c r="G106" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="H106" t="n">
-        <v>60000000</v>
+        <v>53300</v>
       </c>
       <c r="I106" t="n">
-        <v>0.74</v>
+        <v>0</v>
       </c>
       <c r="J106" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>047/BSS-JOB/WS/IX/2026</t>
+          <t>049/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL
-Genset, cap min 80 KVA, silent type, include maintenance (Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Siang Periode 01 sd 30 September 2026)</t>
+          <t>ESTIMATED SUM
+Aqua Galon Segel (Etimated SUM Penyediaan  Air Mineral Aqua Galon Segel untuk Support Pekerjaan Well Services di Senoro Periode 01 sd 30 September 2026)</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>opname_047_BSS-JOB_WS_IX_2026_4500011739</t>
+          <t>opname_050_BSS-JOB_WS_IX_2026_-</t>
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
       <c r="C107" t="inlineStr"/>
       <c r="D107" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -5699,31 +5699,31 @@
         </is>
       </c>
       <c r="G107" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H107" t="n">
-        <v>60000000</v>
+        <v>69000000</v>
       </c>
       <c r="I107" t="n">
-        <v>0.74</v>
+        <v>0</v>
       </c>
       <c r="J107" t="n">
         <v>1</v>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>047/BSS-JOB/WS/IX/2026</t>
+          <t>050/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL
-Genset, cap min 80 KVA, silent type, include maintenance (Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Malam Periode 01 sd 30 September 2026)</t>
+          <t>PROVISIONAL SUM
+At Cost + Fee 15% (Provisional SUM  Akomodasi untuk crew well services di penginapan Yellow Toili Periode 01 sd 30 September 2026)</t>
         </is>
       </c>
     </row>
@@ -5736,7 +5736,7 @@
       <c r="B108" t="inlineStr"/>
       <c r="C108" t="inlineStr"/>
       <c r="D108" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -5752,10 +5752,10 @@
         <v>4</v>
       </c>
       <c r="H108" t="n">
-        <v>15000000</v>
+        <v>25000000</v>
       </c>
       <c r="I108" t="n">
-        <v>0.74</v>
+        <v>0.48</v>
       </c>
       <c r="J108" t="n">
         <v>1</v>
@@ -5772,8 +5772,8 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL
-Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories (Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories, Operasi Shift Malam Periode 01 sd 30 September 2026)</t>
+          <t>ADDITIONAL CAMP SERVICES
+Portacamp - Office Camp,  ukuran 40 FT (Support Well Services Senoro Periode 01 sd 30 September 2026)</t>
         </is>
       </c>
     </row>
@@ -5786,7 +5786,7 @@
       <c r="B109" t="inlineStr"/>
       <c r="C109" t="inlineStr"/>
       <c r="D109" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -5802,10 +5802,10 @@
         <v>4</v>
       </c>
       <c r="H109" t="n">
-        <v>15000000</v>
+        <v>17500000</v>
       </c>
       <c r="I109" t="n">
-        <v>0.74</v>
+        <v>0.48</v>
       </c>
       <c r="J109" t="n">
         <v>1</v>
@@ -5822,21 +5822,21 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL
-Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories (Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Shift Malam Periode 01 sd 30 September 2026)</t>
+          <t>ADDITIONAL CAMP SERVICES
+Portacamp - Living camp,ukuran 40FT (4 sleepers) (Support Well Services Senoro Periode 01 sd 30 September 2026)</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>opname_048_BSS-JOB_WS_IX_2026_4500011739</t>
+          <t>opname_047_BSS-JOB_WS_IX_2026_4500011739</t>
         </is>
       </c>
       <c r="B110" t="inlineStr"/>
       <c r="C110" t="inlineStr"/>
       <c r="D110" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -5849,20 +5849,20 @@
         </is>
       </c>
       <c r="G110" t="n">
-        <v>4600</v>
+        <v>4</v>
       </c>
       <c r="H110" t="n">
-        <v>25000</v>
+        <v>60000000</v>
       </c>
       <c r="I110" t="n">
-        <v>806.6</v>
+        <v>0.74</v>
       </c>
       <c r="J110" t="n">
-        <v>458.4</v>
+        <v>1</v>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>048/BSS-JOB/WS/IX/2026</t>
+          <t>047/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -5872,21 +5872,21 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES
-Laundry services (Laundry services, Untuk Personel Serco Periode 01 sd 30 September 2026)</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL
+Genset, cap min 80 KVA, silent type, include maintenance (Operasi Shift Siang Periode 01 sd 30 September 2026)</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>opname_049_BSS-JOB_WS_IX_2026_-</t>
+          <t>opname_047_BSS-JOB_WS_IX_2026_4500011739</t>
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
       <c r="C111" t="inlineStr"/>
       <c r="D111" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -5899,44 +5899,44 @@
         </is>
       </c>
       <c r="G111" t="n">
-        <v>2188</v>
+        <v>4</v>
       </c>
       <c r="H111" t="n">
-        <v>7500</v>
+        <v>60000000</v>
       </c>
       <c r="I111" t="n">
-        <v>0</v>
+        <v>0.74</v>
       </c>
       <c r="J111" t="n">
-        <v>2188</v>
+        <v>1</v>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>049/BSS-JOB/WS/IX/2026</t>
+          <t>047/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM
-Aqua 600 ml (Etimated SUM Penyediaan  Air Mineral Aqua 600 ml untuk Support Pekerjaan Well Services di Senoro Periode 01 sd 30 September 2026)</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL
+Genset, cap min 80 KVA, silent type, include maintenance (Operasi Shift Malam Periode 01 sd 30 September 2026)</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>opname_049_BSS-JOB_WS_IX_2026_-</t>
+          <t>opname_047_BSS-JOB_WS_IX_2026_4500011739</t>
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
       <c r="C112" t="inlineStr"/>
       <c r="D112" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -5949,44 +5949,44 @@
         </is>
       </c>
       <c r="G112" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="H112" t="n">
-        <v>53300</v>
+        <v>15000000</v>
       </c>
       <c r="I112" t="n">
-        <v>0</v>
+        <v>0.74</v>
       </c>
       <c r="J112" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>049/BSS-JOB/WS/IX/2026</t>
+          <t>047/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM
-Aqua Galon Segel (Etimated SUM Penyediaan  Air Mineral Aqua Galon Segel untuk Support Pekerjaan Well Services di Senoro Periode 01 sd 30 September 2026)</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL
+Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories (Operasi Shift Malam Periode 01 sd 30 September 2026)</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>opname_050_BSS-JOB_WS_IX_2026_-</t>
+          <t>opname_047_BSS-JOB_WS_IX_2026_4500011739</t>
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
       <c r="C113" t="inlineStr"/>
       <c r="D113" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -5999,31 +5999,31 @@
         </is>
       </c>
       <c r="G113" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H113" t="n">
-        <v>69000000</v>
+        <v>15000000</v>
       </c>
       <c r="I113" t="n">
-        <v>0</v>
+        <v>0.74</v>
       </c>
       <c r="J113" t="n">
         <v>1</v>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>050/BSS-JOB/WS/IX/2026</t>
+          <t>047/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM
-At Cost + Fee 15% (Provisional SUM  Akomodasi untuk crew well services di penginapan Yellow Toili Periode 01 sd 30 September 2026)</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL
+Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories (Operasi Shift Malam Periode 01 sd 30 September 2026)</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_opname_parameter.xlsx
+++ b/database_penyimpanan_aman/database_opname_parameter.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M113"/>
+  <dimension ref="A1:M127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6027,6 +6027,706 @@
         </is>
       </c>
     </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>opname_039_BSS-JOB_WS_VIII_2026_4500011739</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr"/>
+      <c r="C114" t="inlineStr"/>
+      <c r="D114" t="n">
+        <v>1</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="G114" t="n">
+        <v>4</v>
+      </c>
+      <c r="H114" t="n">
+        <v>7500000</v>
+      </c>
+      <c r="I114" t="n">
+        <v>0</v>
+      </c>
+      <c r="J114" t="n">
+        <v>1</v>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>039/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL
+Mobilization/ Demobilization of Rental Equipments (Genset/ Air Compressor/ Light Tower/ Fuel Tank, etc) to/from Company Wellsite/ Contractor base (Tronton Muat Mesin Genset dan Light tower dari Lamo ke Cluster B)</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>opname_039_BSS-JOB_WS_VIII_2026_4500011739</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr"/>
+      <c r="C115" t="inlineStr"/>
+      <c r="D115" t="n">
+        <v>2</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="G115" t="n">
+        <v>4</v>
+      </c>
+      <c r="H115" t="n">
+        <v>7500000</v>
+      </c>
+      <c r="I115" t="n">
+        <v>0</v>
+      </c>
+      <c r="J115" t="n">
+        <v>1</v>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>039/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL
+Mobilization/ Demobilization of Rental Equipments (Genset/ Air Compressor/ Light Tower/ Fuel Tank, etc) to/from Company Wellsite/ Contractor base (Tronton Muat  Tenda, Meja, Kursi dan Counter Weight dari Lamo ke Cluster B)</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>opname_039A_BSS-JOB_WS_VIII_2026_-</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr"/>
+      <c r="C116" t="inlineStr"/>
+      <c r="D116" t="n">
+        <v>1</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="G116" t="n">
+        <v>2</v>
+      </c>
+      <c r="H116" t="n">
+        <v>7600000</v>
+      </c>
+      <c r="I116" t="n">
+        <v>0</v>
+      </c>
+      <c r="J116" t="n">
+        <v>1</v>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>039A/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES
+Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base (Trailler 40 feet Mobilisasi Portacamp Office dari Lamo ke Cluster B)</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>opname_039A_BSS-JOB_WS_VIII_2026_-</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr"/>
+      <c r="C117" t="inlineStr"/>
+      <c r="D117" t="n">
+        <v>2</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="G117" t="n">
+        <v>2</v>
+      </c>
+      <c r="H117" t="n">
+        <v>7600000</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0</v>
+      </c>
+      <c r="J117" t="n">
+        <v>1</v>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>039A/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES
+Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base (Trailler 40 feet Mobilisasi Portacamp Sleeper  dari Lamo ke Cluster B)</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>opname_039B_BSS-JOB_WS_VIII_2026_-</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr"/>
+      <c r="C118" t="inlineStr"/>
+      <c r="D118" t="n">
+        <v>1</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G118" t="n">
+        <v>1</v>
+      </c>
+      <c r="H118" t="n">
+        <v>5290000</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0</v>
+      </c>
+      <c r="J118" t="n">
+        <v>1</v>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>039B/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>LAND TRANSPORTATION
+trailer 20" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver (Tronton DN 8639 CH muat tenda, meja - kursi dan Counter Weight)</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>opname_039B_BSS-JOB_WS_VIII_2026_-</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr"/>
+      <c r="C119" t="inlineStr"/>
+      <c r="D119" t="n">
+        <v>2</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G119" t="n">
+        <v>1</v>
+      </c>
+      <c r="H119" t="n">
+        <v>5290000</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0</v>
+      </c>
+      <c r="J119" t="n">
+        <v>1</v>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>039B/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>LAND TRANSPORTATION
+trailer 20" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver (Tronton DN 8140 CA Muat Mesin Genset 2 unit, Lighting tower 2 unit dan panel Listrik)</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>opname_039B_BSS-JOB_WS_VIII_2026_-</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr"/>
+      <c r="C120" t="inlineStr"/>
+      <c r="D120" t="n">
+        <v>3</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G120" t="n">
+        <v>1</v>
+      </c>
+      <c r="H120" t="n">
+        <v>6555000</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0</v>
+      </c>
+      <c r="J120" t="n">
+        <v>1</v>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>039B/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>LAND TRANSPORTATION
+trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver (Trailler 40 feet DN 8785 RA muat equipment well services)</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>opname_039B_BSS-JOB_WS_VIII_2026_-</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr"/>
+      <c r="C121" t="inlineStr"/>
+      <c r="D121" t="n">
+        <v>4</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G121" t="n">
+        <v>1</v>
+      </c>
+      <c r="H121" t="n">
+        <v>6555000</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0</v>
+      </c>
+      <c r="J121" t="n">
+        <v>1</v>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>039B/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>LAND TRANSPORTATION
+trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver (Trailler 40 feet DN 8950 RA muat Portacamp sleeper 40 feet)</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>opname_039B_BSS-JOB_WS_VIII_2026_-</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr"/>
+      <c r="C122" t="inlineStr"/>
+      <c r="D122" t="n">
+        <v>5</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G122" t="n">
+        <v>1</v>
+      </c>
+      <c r="H122" t="n">
+        <v>6555000</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0</v>
+      </c>
+      <c r="J122" t="n">
+        <v>1</v>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>039B/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>LAND TRANSPORTATION
+trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver (Trailler 40 feet DN 8959 RA muat Portacamp Office 40 feet)</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>opname_039C_BSS-JOB_WS_VIII_2026_-</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr"/>
+      <c r="C123" t="inlineStr"/>
+      <c r="D123" t="n">
+        <v>1</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G123" t="n">
+        <v>1</v>
+      </c>
+      <c r="H123" t="n">
+        <v>5290000</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0</v>
+      </c>
+      <c r="J123" t="n">
+        <v>1</v>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>039C/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>LAND TRANSPORTATION
+trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver (tronton DN 8639 CH muat tenda, meja-kursi, Counter Weight ABC)</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>opname_039C_BSS-JOB_WS_VIII_2026_-</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr"/>
+      <c r="C124" t="inlineStr"/>
+      <c r="D124" t="n">
+        <v>2</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G124" t="n">
+        <v>1</v>
+      </c>
+      <c r="H124" t="n">
+        <v>5290000</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0</v>
+      </c>
+      <c r="J124" t="n">
+        <v>1</v>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>039C/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>LAND TRANSPORTATION
+trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver (Tronton DN 8140 CA Muat Mesin Genset 2 unit, Lighting tower 2 unit dan panel Listrik)</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>opname_039C_BSS-JOB_WS_VIII_2026_-</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr"/>
+      <c r="C125" t="inlineStr"/>
+      <c r="D125" t="n">
+        <v>3</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G125" t="n">
+        <v>1</v>
+      </c>
+      <c r="H125" t="n">
+        <v>6555000</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0</v>
+      </c>
+      <c r="J125" t="n">
+        <v>1</v>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>039C/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>LAND TRANSPORTATION
+trailer 40" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver (Trailler 40 feet DN 8950 RA muat Equipment Well Services)</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>opname_039C_BSS-JOB_WS_VIII_2026_-</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr"/>
+      <c r="C126" t="inlineStr"/>
+      <c r="D126" t="n">
+        <v>4</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G126" t="n">
+        <v>1</v>
+      </c>
+      <c r="H126" t="n">
+        <v>7600000</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0</v>
+      </c>
+      <c r="J126" t="n">
+        <v>1</v>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>039C/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES
+Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base (Trailler 40 feet DN 8785 RA Demobilisasi portacamp Sleeper 40 feet  dari Senoro 2 ke Lamo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>opname_039C_BSS-JOB_WS_VIII_2026_-</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr"/>
+      <c r="C127" t="inlineStr"/>
+      <c r="D127" t="n">
+        <v>5</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G127" t="n">
+        <v>1</v>
+      </c>
+      <c r="H127" t="n">
+        <v>7600000</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0</v>
+      </c>
+      <c r="J127" t="n">
+        <v>1</v>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>039C/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES
+Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base (Trailler 40 feet DN 8959 RA  Demobilisasi portacamp Office 40 feet  dari Senoro 2 ke Lamo)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database_penyimpanan_aman/database_opname_parameter.xlsx
+++ b/database_penyimpanan_aman/database_opname_parameter.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M127"/>
+  <dimension ref="A1:M130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4480,7 +4480,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>opname_038_BSS-JOB_WS_IX_2026_4500011739</t>
+          <t>opname_040_BSS-JOB_WS_IX_2026_4500011739</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
@@ -4499,20 +4499,20 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>18300</v>
+        <v>240</v>
       </c>
       <c r="H83" t="n">
-        <v>65000</v>
+        <v>750000</v>
       </c>
       <c r="I83" t="n">
-        <v>2578</v>
+        <v>23</v>
       </c>
       <c r="J83" t="n">
-        <v>3195</v>
+        <v>30</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>038/BSS-JOB/WS/IX/2026</t>
+          <t>040/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -4522,21 +4522,21 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES
-Food &amp; beverage, main course (DDITIONAL CAMP SERVICES, Operational Consumption)</t>
+          <t>PERSONEL ON CALL
+Personnel GS in-charge di lokasi pemboran/ wellservices/ workover, personnel in charge (Personnel GS - Koordinator Lapangan atas nama Nur Afiata Periode 01 sd 30 September 2026)</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>opname_038_BSS-JOB_WS_IX_2026_4500011739</t>
+          <t>opname_041_BSS-JOB_WS_IX_2026_4500011739</t>
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -4549,20 +4549,20 @@
         </is>
       </c>
       <c r="G84" t="n">
-        <v>9200</v>
+        <v>30</v>
       </c>
       <c r="H84" t="n">
-        <v>33000</v>
+        <v>500000</v>
       </c>
       <c r="I84" t="n">
-        <v>1157</v>
+        <v>0</v>
       </c>
       <c r="J84" t="n">
-        <v>1486.5</v>
+        <v>30</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>038/BSS-JOB/WS/IX/2026</t>
+          <t>041/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -4572,21 +4572,21 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES
-Food &amp; beverage, snack coffee/ tea &amp; desert (ADDITIONAL CAMP SERVICES, Operational side consumption)</t>
+          <t>PERSONEL ON CALL
+Welder (GTAW) (Support Kegiatan Well Services di Senoro personel  Welder = HSE Officer ( Gusti Ngurah Dwipayana))</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>opname_040_BSS-JOB_WS_IX_2026_4500011739</t>
+          <t>opname_041_BSS-JOB_WS_IX_2026_4500011739</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -4599,20 +4599,20 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>240</v>
+        <v>30</v>
       </c>
       <c r="H85" t="n">
-        <v>750000</v>
+        <v>500000</v>
       </c>
       <c r="I85" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="J85" t="n">
         <v>30</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>040/BSS-JOB/WS/IX/2026</t>
+          <t>041/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -4623,7 +4623,7 @@
       <c r="M85" t="inlineStr">
         <is>
           <t>PERSONEL ON CALL
-Personnel GS in-charge di lokasi pemboran/ wellservices/ workover, personnel in charge (Personnel GS - Koordinator Lapangan atas nama Nur Afiata Periode 01 sd 30 September 2026)</t>
+Welder (GTAW) (Support Kegiatan Well Services di Senoro personel  Welder = Paramedic  ( Meliita Bella))</t>
         </is>
       </c>
     </row>
@@ -4636,7 +4636,7 @@
       <c r="B86" t="inlineStr"/>
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -4673,20 +4673,20 @@
       <c r="M86" t="inlineStr">
         <is>
           <t>PERSONEL ON CALL
-Welder (GTAW) (Support Kegiatan Well Services di Senoro personel  Welder = HSE Officer ( Gusti Ngurah Dwipayana))</t>
+Welder (GTAW) (Support Kegiatan Well Services di Senoro personel  Welder = Paramedic  ( Widiya Satuo))</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>opname_041_BSS-JOB_WS_IX_2026_4500011739</t>
+          <t>opname_042_BSS-JOB_WS_IX_2026_4500011739</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -4699,20 +4699,20 @@
         </is>
       </c>
       <c r="G87" t="n">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="H87" t="n">
-        <v>500000</v>
+        <v>750000</v>
       </c>
       <c r="I87" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J87" t="n">
         <v>30</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>041/BSS-JOB/WS/IX/2026</t>
+          <t>042/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -4723,20 +4723,20 @@
       <c r="M87" t="inlineStr">
         <is>
           <t>PERSONEL ON CALL
-Welder (GTAW) (Support Kegiatan Well Services di Senoro personel  Welder = Paramedic  ( Meliita Bella))</t>
+Operator Crane (Operator Crane Shift Siang atas Nama Wanhar Renaldi)</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>opname_041_BSS-JOB_WS_IX_2026_4500011739</t>
+          <t>opname_042_BSS-JOB_WS_IX_2026_4500011739</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -4749,20 +4749,20 @@
         </is>
       </c>
       <c r="G88" t="n">
+        <v>120</v>
+      </c>
+      <c r="H88" t="n">
+        <v>750000</v>
+      </c>
+      <c r="I88" t="n">
         <v>30</v>
-      </c>
-      <c r="H88" t="n">
-        <v>500000</v>
-      </c>
-      <c r="I88" t="n">
-        <v>0</v>
       </c>
       <c r="J88" t="n">
         <v>30</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>041/BSS-JOB/WS/IX/2026</t>
+          <t>042/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -4773,7 +4773,7 @@
       <c r="M88" t="inlineStr">
         <is>
           <t>PERSONEL ON CALL
-Welder (GTAW) (Support Kegiatan Well Services di Senoro personel  Welder = Paramedic  ( Widiya Satuo))</t>
+Operator Crane (Operator Crane Shift Malam atas Nama Ilsan Adjedar)</t>
         </is>
       </c>
     </row>
@@ -4786,7 +4786,7 @@
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="inlineStr"/>
       <c r="D89" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -4802,10 +4802,10 @@
         <v>120</v>
       </c>
       <c r="H89" t="n">
-        <v>750000</v>
+        <v>650000</v>
       </c>
       <c r="I89" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="J89" t="n">
         <v>30</v>
@@ -4823,7 +4823,7 @@
       <c r="M89" t="inlineStr">
         <is>
           <t>PERSONEL ON CALL
-Operator Crane (Operator Crane Shift Siang atas Nama Wanhar Renaldi)</t>
+Rigger (RIgger Crane Shift Siang atas Nama Tison)</t>
         </is>
       </c>
     </row>
@@ -4836,7 +4836,7 @@
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="inlineStr"/>
       <c r="D90" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -4852,10 +4852,10 @@
         <v>120</v>
       </c>
       <c r="H90" t="n">
-        <v>750000</v>
+        <v>650000</v>
       </c>
       <c r="I90" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="J90" t="n">
         <v>30</v>
@@ -4873,7 +4873,7 @@
       <c r="M90" t="inlineStr">
         <is>
           <t>PERSONEL ON CALL
-Operator Crane (Operator Crane Shift Malam atas Nama Ilsan Adjedar)</t>
+Rigger (Rigger Crane Shift Malam atas Nama Agus Dg Mangata)</t>
         </is>
       </c>
     </row>
@@ -4886,7 +4886,7 @@
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="inlineStr"/>
       <c r="D91" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -4899,13 +4899,13 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="H91" t="n">
-        <v>650000</v>
+        <v>600000</v>
       </c>
       <c r="I91" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J91" t="n">
         <v>30</v>
@@ -4923,7 +4923,7 @@
       <c r="M91" t="inlineStr">
         <is>
           <t>PERSONEL ON CALL
-Rigger (RIgger Crane Shift Siang atas Nama Tison)</t>
+Mechanic/ Electrician (Operator Mesin Genset dan Ligting Tower Shift Siang atas nama Sugeng)</t>
         </is>
       </c>
     </row>
@@ -4936,7 +4936,7 @@
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="inlineStr"/>
       <c r="D92" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -4949,13 +4949,13 @@
         </is>
       </c>
       <c r="G92" t="n">
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="H92" t="n">
-        <v>650000</v>
+        <v>600000</v>
       </c>
       <c r="I92" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J92" t="n">
         <v>30</v>
@@ -4973,20 +4973,20 @@
       <c r="M92" t="inlineStr">
         <is>
           <t>PERSONEL ON CALL
-Rigger (Rigger Crane Shift Malam atas Nama Agus Dg Mangata)</t>
+Mechanic/ Electrician (Operator Mesin Genset dan Ligting Tower Shift Siang atas nama Ahmad Dhani)</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>opname_042_BSS-JOB_WS_IX_2026_4500011739</t>
+          <t>opname_043_BSS-JOB_WS_IX_2026_4500011739</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="inlineStr"/>
       <c r="D93" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -4999,20 +4999,20 @@
         </is>
       </c>
       <c r="G93" t="n">
-        <v>240</v>
+        <v>30</v>
       </c>
       <c r="H93" t="n">
-        <v>600000</v>
+        <v>500000</v>
       </c>
       <c r="I93" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="J93" t="n">
         <v>30</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>042/BSS-JOB/WS/IX/2026</t>
+          <t>043/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -5023,20 +5023,20 @@
       <c r="M93" t="inlineStr">
         <is>
           <t>PERSONEL ON CALL
-Mechanic/ Electrician (Operator Mesin Genset dan Ligting Tower Shift Siang atas nama Sugeng)</t>
+Operator Heavy Equipment (Vacuum Truck) (Driver Vacuum Truck atas nama Wijayanto Sucipto)</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>opname_042_BSS-JOB_WS_IX_2026_4500011739</t>
+          <t>opname_044_BSS-JOB_WS_IX_2026_4500011739</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="inlineStr"/>
       <c r="D94" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -5045,24 +5045,24 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G94" t="n">
-        <v>240</v>
+        <v>300</v>
       </c>
       <c r="H94" t="n">
-        <v>600000</v>
+        <v>250000</v>
       </c>
       <c r="I94" t="n">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="J94" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>042/BSS-JOB/WS/IX/2026</t>
+          <t>044/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -5073,14 +5073,14 @@
       <c r="M94" t="inlineStr">
         <is>
           <t>PERSONEL ON CALL
-Mechanic/ Electrician (Operator Mesin Genset dan Ligting Tower Shift Siang atas nama Ahmad Dhani)</t>
+Helper Local (non Skilled) (PERSONNEL ON-CALL Helper Local (non Skilled) Tenaga Flagman Periode tgl 4 sd 11 September 2026)</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>opname_043_BSS-JOB_WS_IX_2026_4500011739</t>
+          <t>opname_045_BSS-JOB_WS_IX_2026_4500011739</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
@@ -5099,20 +5099,20 @@
         </is>
       </c>
       <c r="G95" t="n">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="H95" t="n">
-        <v>500000</v>
+        <v>8500000</v>
       </c>
       <c r="I95" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J95" t="n">
         <v>30</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>043/BSS-JOB/WS/IX/2026</t>
+          <t>045/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -5122,21 +5122,21 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL
-Operator Heavy Equipment (Vacuum Truck) (Driver Vacuum Truck atas nama Wijayanto Sucipto)</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL
+crane min 70 ton, call out, (hanya unit) (Crane Sany 100 ton menggantikan Crane Tadano 70 ton yang rusak Operasi periode 01 sd 30 September 2026)</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>opname_044_BSS-JOB_WS_IX_2026_4500011739</t>
+          <t>opname_045_BSS-JOB_WS_IX_2026_4500011739</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -5145,24 +5145,24 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G96" t="n">
-        <v>300</v>
+        <v>120</v>
       </c>
       <c r="H96" t="n">
-        <v>250000</v>
+        <v>2750000</v>
       </c>
       <c r="I96" t="n">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="J96" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>044/BSS-JOB/WS/IX/2026</t>
+          <t>045/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -5172,15 +5172,15 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL
-Helper Local (non Skilled) (PERSONNEL ON-CALL Helper Local (non Skilled) Tenaga Flagman Periode tgl 4 sd 11 September 2026)</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL
+Vacuum Truck , Call out, Cap  5000 ltr c/w vacuum pump &amp; acessories, call out, (hanya unit) (Vacuum Truck , Call out, Cap  5000 ltr  Operasi periode 01 sd 30 September 2026)</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>opname_045_BSS-JOB_WS_IX_2026_4500011739</t>
+          <t>opname_046_BSS-JOB_WS_IX_2026_4500011739</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
@@ -5202,17 +5202,17 @@
         <v>120</v>
       </c>
       <c r="H97" t="n">
-        <v>8500000</v>
+        <v>1600000</v>
       </c>
       <c r="I97" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J97" t="n">
         <v>30</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>045/BSS-JOB/WS/IX/2026</t>
+          <t>046/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -5222,15 +5222,15 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL
-crane min 70 ton, call out, (hanya unit) (Crane Sany 100 ton menggantikan Crane Tadano 70 ton yang rusak Operasi periode 01 sd 30 September 2026)</t>
+          <t>CAR &amp; TANSPORTATION
+Station wagon 7 seater diesel engine + driver + BBM, (Kendaraan Inova DN 1259 CL  Support Well Services Periode tanggal 01 sd 30 September 2026)</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>opname_045_BSS-JOB_WS_IX_2026_4500011739</t>
+          <t>opname_046_BSS-JOB_WS_IX_2026_4500011739</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
@@ -5252,17 +5252,17 @@
         <v>120</v>
       </c>
       <c r="H98" t="n">
-        <v>2750000</v>
+        <v>1600000</v>
       </c>
       <c r="I98" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J98" t="n">
         <v>30</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>045/BSS-JOB/WS/IX/2026</t>
+          <t>046/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -5272,8 +5272,8 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL
-Vacuum Truck , Call out, Cap  5000 ltr c/w vacuum pump &amp; acessories, call out, (hanya unit) (Vacuum Truck , Call out, Cap  5000 ltr  Operasi periode 01 sd 30 September 2026)</t>
+          <t>CAR &amp; TANSPORTATION
+Station wagon 7 seater diesel engine + driver + BBM, (Kendaraan Inova DN 1257 CL  Support Well Services Periode tanggal 01 sd 30 September 2026)</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="inlineStr"/>
       <c r="D99" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -5305,10 +5305,10 @@
         <v>1600000</v>
       </c>
       <c r="I99" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J99" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
@@ -5323,7 +5323,7 @@
       <c r="M99" t="inlineStr">
         <is>
           <t>CAR &amp; TANSPORTATION
-Station wagon 7 seater diesel engine + driver + BBM, (Kendaraan Inova DN 1259 CL  Support Well Services Periode tanggal 01 sd 30 September 2026)</t>
+Station wagon 7 seater diesel engine + driver + BBM, (Kendaraan Inova DN 1258 CL  Support Well Services Periode tanggal 27 sd 30 September 2026)</t>
         </is>
       </c>
     </row>
@@ -5336,7 +5336,7 @@
       <c r="B100" t="inlineStr"/>
       <c r="C100" t="inlineStr"/>
       <c r="D100" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -5355,7 +5355,7 @@
         <v>1600000</v>
       </c>
       <c r="I100" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J100" t="n">
         <v>30</v>
@@ -5373,7 +5373,7 @@
       <c r="M100" t="inlineStr">
         <is>
           <t>CAR &amp; TANSPORTATION
-Station wagon 7 seater diesel engine + driver + BBM, (Kendaraan Inova DN 1257 CL  Support Well Services Periode tanggal 01 sd 30 September 2026)</t>
+Double cabin 4x4, diesel engine + driver + BBM, (Kendaraan Double Cabin Hilux DN 1916 CH  Support Well Services Periode tanggal 01 sd 30 September 2026)</t>
         </is>
       </c>
     </row>
@@ -5386,7 +5386,7 @@
       <c r="B101" t="inlineStr"/>
       <c r="C101" t="inlineStr"/>
       <c r="D101" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -5405,10 +5405,10 @@
         <v>1600000</v>
       </c>
       <c r="I101" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J101" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
@@ -5423,20 +5423,20 @@
       <c r="M101" t="inlineStr">
         <is>
           <t>CAR &amp; TANSPORTATION
-Station wagon 7 seater diesel engine + driver + BBM, (Kendaraan Inova DN 1258 CL  Support Well Services Periode tanggal 27 sd 30 September 2026)</t>
+Double cabin 4x4, diesel engine + driver + BBM, (Kendaraan Double Cabin Hilux DN 1917 CH  Support Well Services Periode tanggal 01 sd 30 September 2026)</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>opname_046_BSS-JOB_WS_IX_2026_4500011739</t>
+          <t>opname_048_BSS-JOB_WS_IX_2026_4500011739</t>
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
       <c r="C102" t="inlineStr"/>
       <c r="D102" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -5449,20 +5449,20 @@
         </is>
       </c>
       <c r="G102" t="n">
-        <v>120</v>
+        <v>4600</v>
       </c>
       <c r="H102" t="n">
-        <v>1600000</v>
+        <v>25000</v>
       </c>
       <c r="I102" t="n">
-        <v>26</v>
+        <v>806.6</v>
       </c>
       <c r="J102" t="n">
-        <v>30</v>
+        <v>458.4</v>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>046/BSS-JOB/WS/IX/2026</t>
+          <t>048/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -5472,21 +5472,21 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION
-Double cabin 4x4, diesel engine + driver + BBM, (Kendaraan Double Cabin Hilux DN 1916 CH  Support Well Services Periode tanggal 01 sd 30 September 2026)</t>
+          <t>ADDITIONAL CAMP SERVICES
+Laundry services (Laundry services, Untuk Personel Serco Periode 01 sd 30 September 2026)</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>opname_046_BSS-JOB_WS_IX_2026_4500011739</t>
+          <t>opname_049_BSS-JOB_WS_IX_2026_-</t>
         </is>
       </c>
       <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr"/>
       <c r="D103" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -5499,44 +5499,44 @@
         </is>
       </c>
       <c r="G103" t="n">
-        <v>120</v>
+        <v>2188</v>
       </c>
       <c r="H103" t="n">
-        <v>1600000</v>
+        <v>7500</v>
       </c>
       <c r="I103" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="J103" t="n">
-        <v>30</v>
+        <v>2188</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>046/BSS-JOB/WS/IX/2026</t>
+          <t>049/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION
-Double cabin 4x4, diesel engine + driver + BBM, (Kendaraan Double Cabin Hilux DN 1917 CH  Support Well Services Periode tanggal 01 sd 30 September 2026)</t>
+          <t>ESTIMATED SUM
+Aqua 600 ml (Etimated SUM Penyediaan  Air Mineral Aqua 600 ml untuk Support Pekerjaan Well Services di Senoro Periode 01 sd 30 September 2026)</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>opname_048_BSS-JOB_WS_IX_2026_4500011739</t>
+          <t>opname_049_BSS-JOB_WS_IX_2026_-</t>
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr"/>
       <c r="D104" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -5549,38 +5549,38 @@
         </is>
       </c>
       <c r="G104" t="n">
-        <v>4600</v>
+        <v>15</v>
       </c>
       <c r="H104" t="n">
-        <v>25000</v>
+        <v>53300</v>
       </c>
       <c r="I104" t="n">
-        <v>806.6</v>
+        <v>0</v>
       </c>
       <c r="J104" t="n">
-        <v>458.4</v>
+        <v>15</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>048/BSS-JOB/WS/IX/2026</t>
+          <t>049/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES
-Laundry services (Laundry services, Untuk Personel Serco Periode 01 sd 30 September 2026)</t>
+          <t>ESTIMATED SUM
+Aqua Galon Segel (Etimated SUM Penyediaan  Air Mineral Aqua Galon Segel untuk Support Pekerjaan Well Services di Senoro Periode 01 sd 30 September 2026)</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>opname_049_BSS-JOB_WS_IX_2026_-</t>
+          <t>opname_050_BSS-JOB_WS_IX_2026_-</t>
         </is>
       </c>
       <c r="B105" t="inlineStr"/>
@@ -5599,20 +5599,20 @@
         </is>
       </c>
       <c r="G105" t="n">
-        <v>2188</v>
+        <v>1</v>
       </c>
       <c r="H105" t="n">
-        <v>7500</v>
+        <v>69000000</v>
       </c>
       <c r="I105" t="n">
         <v>0</v>
       </c>
       <c r="J105" t="n">
-        <v>2188</v>
+        <v>1</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>049/BSS-JOB/WS/IX/2026</t>
+          <t>050/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -5622,21 +5622,21 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM
-Aqua 600 ml (Etimated SUM Penyediaan  Air Mineral Aqua 600 ml untuk Support Pekerjaan Well Services di Senoro Periode 01 sd 30 September 2026)</t>
+          <t>PROVISIONAL SUM
+At Cost + Fee 15% (Provisional SUM  Akomodasi untuk crew well services di penginapan Yellow Toili Periode 01 sd 30 September 2026)</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>opname_049_BSS-JOB_WS_IX_2026_-</t>
+          <t>opname_047_BSS-JOB_WS_IX_2026_4500011739</t>
         </is>
       </c>
       <c r="B106" t="inlineStr"/>
       <c r="C106" t="inlineStr"/>
       <c r="D106" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -5649,44 +5649,44 @@
         </is>
       </c>
       <c r="G106" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="H106" t="n">
-        <v>53300</v>
+        <v>25000000</v>
       </c>
       <c r="I106" t="n">
-        <v>0</v>
+        <v>0.48</v>
       </c>
       <c r="J106" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>049/BSS-JOB/WS/IX/2026</t>
+          <t>047/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM
-Aqua Galon Segel (Etimated SUM Penyediaan  Air Mineral Aqua Galon Segel untuk Support Pekerjaan Well Services di Senoro Periode 01 sd 30 September 2026)</t>
+          <t>ADDITIONAL CAMP SERVICES
+Portacamp - Office Camp,  ukuran 40 FT (Support Well Services Senoro Periode 01 sd 30 September 2026)</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>opname_050_BSS-JOB_WS_IX_2026_-</t>
+          <t>opname_047_BSS-JOB_WS_IX_2026_4500011739</t>
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
       <c r="C107" t="inlineStr"/>
       <c r="D107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -5699,31 +5699,31 @@
         </is>
       </c>
       <c r="G107" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H107" t="n">
-        <v>69000000</v>
+        <v>17500000</v>
       </c>
       <c r="I107" t="n">
-        <v>0</v>
+        <v>0.48</v>
       </c>
       <c r="J107" t="n">
         <v>1</v>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>050/BSS-JOB/WS/IX/2026</t>
+          <t>047/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM
-At Cost + Fee 15% (Provisional SUM  Akomodasi untuk crew well services di penginapan Yellow Toili Periode 01 sd 30 September 2026)</t>
+          <t>ADDITIONAL CAMP SERVICES
+Portacamp - Living camp,ukuran 40FT (4 sleepers) (Support Well Services Senoro Periode 01 sd 30 September 2026)</t>
         </is>
       </c>
     </row>
@@ -5736,7 +5736,7 @@
       <c r="B108" t="inlineStr"/>
       <c r="C108" t="inlineStr"/>
       <c r="D108" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -5752,10 +5752,10 @@
         <v>4</v>
       </c>
       <c r="H108" t="n">
-        <v>25000000</v>
+        <v>60000000</v>
       </c>
       <c r="I108" t="n">
-        <v>0.48</v>
+        <v>0.74</v>
       </c>
       <c r="J108" t="n">
         <v>1</v>
@@ -5772,8 +5772,8 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES
-Portacamp - Office Camp,  ukuran 40 FT (Support Well Services Senoro Periode 01 sd 30 September 2026)</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL
+Genset, cap min 80 KVA, silent type, include maintenance (Operasi Shift Siang Periode 01 sd 30 September 2026)</t>
         </is>
       </c>
     </row>
@@ -5786,7 +5786,7 @@
       <c r="B109" t="inlineStr"/>
       <c r="C109" t="inlineStr"/>
       <c r="D109" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -5802,10 +5802,10 @@
         <v>4</v>
       </c>
       <c r="H109" t="n">
-        <v>17500000</v>
+        <v>60000000</v>
       </c>
       <c r="I109" t="n">
-        <v>0.48</v>
+        <v>0.74</v>
       </c>
       <c r="J109" t="n">
         <v>1</v>
@@ -5822,8 +5822,8 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES
-Portacamp - Living camp,ukuran 40FT (4 sleepers) (Support Well Services Senoro Periode 01 sd 30 September 2026)</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL
+Genset, cap min 80 KVA, silent type, include maintenance (Operasi Shift Malam Periode 01 sd 30 September 2026)</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       <c r="B110" t="inlineStr"/>
       <c r="C110" t="inlineStr"/>
       <c r="D110" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -5852,7 +5852,7 @@
         <v>4</v>
       </c>
       <c r="H110" t="n">
-        <v>60000000</v>
+        <v>15000000</v>
       </c>
       <c r="I110" t="n">
         <v>0.74</v>
@@ -5873,7 +5873,7 @@
       <c r="M110" t="inlineStr">
         <is>
           <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL
-Genset, cap min 80 KVA, silent type, include maintenance (Operasi Shift Siang Periode 01 sd 30 September 2026)</t>
+Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories (Operasi Shift Malam Periode 01 sd 30 September 2026)</t>
         </is>
       </c>
     </row>
@@ -5886,7 +5886,7 @@
       <c r="B111" t="inlineStr"/>
       <c r="C111" t="inlineStr"/>
       <c r="D111" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -5902,7 +5902,7 @@
         <v>4</v>
       </c>
       <c r="H111" t="n">
-        <v>60000000</v>
+        <v>15000000</v>
       </c>
       <c r="I111" t="n">
         <v>0.74</v>
@@ -5923,20 +5923,20 @@
       <c r="M111" t="inlineStr">
         <is>
           <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL
-Genset, cap min 80 KVA, silent type, include maintenance (Operasi Shift Malam Periode 01 sd 30 September 2026)</t>
+Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories (Operasi Shift Malam Periode 01 sd 30 September 2026)</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>opname_047_BSS-JOB_WS_IX_2026_4500011739</t>
+          <t>opname_039_BSS-JOB_WS_VIII_2026_4500011739</t>
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
       <c r="C112" t="inlineStr"/>
       <c r="D112" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -5945,24 +5945,24 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G112" t="n">
         <v>4</v>
       </c>
       <c r="H112" t="n">
-        <v>15000000</v>
+        <v>7500000</v>
       </c>
       <c r="I112" t="n">
-        <v>0.74</v>
+        <v>0</v>
       </c>
       <c r="J112" t="n">
         <v>1</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>047/BSS-JOB/WS/IX/2026</t>
+          <t>039/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -5973,20 +5973,20 @@
       <c r="M112" t="inlineStr">
         <is>
           <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL
-Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories (Operasi Shift Malam Periode 01 sd 30 September 2026)</t>
+Mobilization/ Demobilization of Rental Equipments (Genset/ Air Compressor/ Light Tower/ Fuel Tank, etc) to/from Company Wellsite/ Contractor base (Tronton Muat Mesin Genset dan Light tower dari Lamo ke Cluster B)</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>opname_047_BSS-JOB_WS_IX_2026_4500011739</t>
+          <t>opname_039_BSS-JOB_WS_VIII_2026_4500011739</t>
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
       <c r="C113" t="inlineStr"/>
       <c r="D113" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -5995,24 +5995,24 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G113" t="n">
         <v>4</v>
       </c>
       <c r="H113" t="n">
-        <v>15000000</v>
+        <v>7500000</v>
       </c>
       <c r="I113" t="n">
-        <v>0.74</v>
+        <v>0</v>
       </c>
       <c r="J113" t="n">
         <v>1</v>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>047/BSS-JOB/WS/IX/2026</t>
+          <t>039/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -6023,14 +6023,14 @@
       <c r="M113" t="inlineStr">
         <is>
           <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL
-Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories (Operasi Shift Malam Periode 01 sd 30 September 2026)</t>
+Mobilization/ Demobilization of Rental Equipments (Genset/ Air Compressor/ Light Tower/ Fuel Tank, etc) to/from Company Wellsite/ Contractor base (Tronton Muat  Tenda, Meja, Kursi dan Counter Weight dari Lamo ke Cluster B)</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>opname_039_BSS-JOB_WS_VIII_2026_4500011739</t>
+          <t>opname_039A_BSS-JOB_WS_VIII_2026_-</t>
         </is>
       </c>
       <c r="B114" t="inlineStr"/>
@@ -6049,10 +6049,10 @@
         </is>
       </c>
       <c r="G114" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H114" t="n">
-        <v>7500000</v>
+        <v>7600000</v>
       </c>
       <c r="I114" t="n">
         <v>0</v>
@@ -6062,25 +6062,25 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>039/BSS-JOB/WS/VIII/2026</t>
+          <t>039A/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL
-Mobilization/ Demobilization of Rental Equipments (Genset/ Air Compressor/ Light Tower/ Fuel Tank, etc) to/from Company Wellsite/ Contractor base (Tronton Muat Mesin Genset dan Light tower dari Lamo ke Cluster B)</t>
+          <t>ADDITIONAL CAMP SERVICES
+Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base (Trailler 40 feet Mobilisasi Portacamp Office dari Lamo ke Cluster B)</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>opname_039_BSS-JOB_WS_VIII_2026_4500011739</t>
+          <t>opname_039A_BSS-JOB_WS_VIII_2026_-</t>
         </is>
       </c>
       <c r="B115" t="inlineStr"/>
@@ -6099,10 +6099,10 @@
         </is>
       </c>
       <c r="G115" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H115" t="n">
-        <v>7500000</v>
+        <v>7600000</v>
       </c>
       <c r="I115" t="n">
         <v>0</v>
@@ -6112,25 +6112,25 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>039/BSS-JOB/WS/VIII/2026</t>
+          <t>039A/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL
-Mobilization/ Demobilization of Rental Equipments (Genset/ Air Compressor/ Light Tower/ Fuel Tank, etc) to/from Company Wellsite/ Contractor base (Tronton Muat  Tenda, Meja, Kursi dan Counter Weight dari Lamo ke Cluster B)</t>
+          <t>ADDITIONAL CAMP SERVICES
+Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base (Trailler 40 feet Mobilisasi Portacamp Sleeper  dari Lamo ke Cluster B)</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>opname_039A_BSS-JOB_WS_VIII_2026_-</t>
+          <t>opname_039B_BSS-JOB_WS_VIII_2026_-</t>
         </is>
       </c>
       <c r="B116" t="inlineStr"/>
@@ -6145,14 +6145,14 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G116" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H116" t="n">
-        <v>7600000</v>
+        <v>5290000</v>
       </c>
       <c r="I116" t="n">
         <v>0</v>
@@ -6162,7 +6162,7 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>039A/BSS-JOB/WS/VIII/2026</t>
+          <t>039B/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -6172,15 +6172,15 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES
-Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base (Trailler 40 feet Mobilisasi Portacamp Office dari Lamo ke Cluster B)</t>
+          <t>LAND TRANSPORTATION
+trailer 20" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver (Tronton DN 8639 CH muat tenda, meja - kursi dan Counter Weight)</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>opname_039A_BSS-JOB_WS_VIII_2026_-</t>
+          <t>opname_039B_BSS-JOB_WS_VIII_2026_-</t>
         </is>
       </c>
       <c r="B117" t="inlineStr"/>
@@ -6195,14 +6195,14 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G117" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H117" t="n">
-        <v>7600000</v>
+        <v>5290000</v>
       </c>
       <c r="I117" t="n">
         <v>0</v>
@@ -6212,7 +6212,7 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>039A/BSS-JOB/WS/VIII/2026</t>
+          <t>039B/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -6222,8 +6222,8 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES
-Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base (Trailler 40 feet Mobilisasi Portacamp Sleeper  dari Lamo ke Cluster B)</t>
+          <t>LAND TRANSPORTATION
+trailer 20" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver (Tronton DN 8140 CA Muat Mesin Genset 2 unit, Lighting tower 2 unit dan panel Listrik)</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6236,7 @@
       <c r="B118" t="inlineStr"/>
       <c r="C118" t="inlineStr"/>
       <c r="D118" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -6252,7 +6252,7 @@
         <v>1</v>
       </c>
       <c r="H118" t="n">
-        <v>5290000</v>
+        <v>6555000</v>
       </c>
       <c r="I118" t="n">
         <v>0</v>
@@ -6273,7 +6273,7 @@
       <c r="M118" t="inlineStr">
         <is>
           <t>LAND TRANSPORTATION
-trailer 20" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver (Tronton DN 8639 CH muat tenda, meja - kursi dan Counter Weight)</t>
+trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver (Trailler 40 feet DN 8785 RA muat equipment well services)</t>
         </is>
       </c>
     </row>
@@ -6286,7 +6286,7 @@
       <c r="B119" t="inlineStr"/>
       <c r="C119" t="inlineStr"/>
       <c r="D119" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -6302,7 +6302,7 @@
         <v>1</v>
       </c>
       <c r="H119" t="n">
-        <v>5290000</v>
+        <v>6555000</v>
       </c>
       <c r="I119" t="n">
         <v>0</v>
@@ -6323,7 +6323,7 @@
       <c r="M119" t="inlineStr">
         <is>
           <t>LAND TRANSPORTATION
-trailer 20" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver (Tronton DN 8140 CA Muat Mesin Genset 2 unit, Lighting tower 2 unit dan panel Listrik)</t>
+trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver (Trailler 40 feet DN 8950 RA muat Portacamp sleeper 40 feet)</t>
         </is>
       </c>
     </row>
@@ -6336,7 +6336,7 @@
       <c r="B120" t="inlineStr"/>
       <c r="C120" t="inlineStr"/>
       <c r="D120" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -6373,20 +6373,20 @@
       <c r="M120" t="inlineStr">
         <is>
           <t>LAND TRANSPORTATION
-trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver (Trailler 40 feet DN 8785 RA muat equipment well services)</t>
+trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver (Trailler 40 feet DN 8959 RA muat Portacamp Office 40 feet)</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>opname_039B_BSS-JOB_WS_VIII_2026_-</t>
+          <t>opname_039C_BSS-JOB_WS_VIII_2026_-</t>
         </is>
       </c>
       <c r="B121" t="inlineStr"/>
       <c r="C121" t="inlineStr"/>
       <c r="D121" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -6395,14 +6395,14 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G121" t="n">
         <v>1</v>
       </c>
       <c r="H121" t="n">
-        <v>6555000</v>
+        <v>5290000</v>
       </c>
       <c r="I121" t="n">
         <v>0</v>
@@ -6412,7 +6412,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>039B/BSS-JOB/WS/VIII/2026</t>
+          <t>039C/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -6423,20 +6423,20 @@
       <c r="M121" t="inlineStr">
         <is>
           <t>LAND TRANSPORTATION
-trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver (Trailler 40 feet DN 8950 RA muat Portacamp sleeper 40 feet)</t>
+trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver (tronton DN 8639 CH muat tenda, meja-kursi, Counter Weight ABC)</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>opname_039B_BSS-JOB_WS_VIII_2026_-</t>
+          <t>opname_039C_BSS-JOB_WS_VIII_2026_-</t>
         </is>
       </c>
       <c r="B122" t="inlineStr"/>
       <c r="C122" t="inlineStr"/>
       <c r="D122" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -6445,14 +6445,14 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G122" t="n">
         <v>1</v>
       </c>
       <c r="H122" t="n">
-        <v>6555000</v>
+        <v>5290000</v>
       </c>
       <c r="I122" t="n">
         <v>0</v>
@@ -6462,7 +6462,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>039B/BSS-JOB/WS/VIII/2026</t>
+          <t>039C/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -6473,7 +6473,7 @@
       <c r="M122" t="inlineStr">
         <is>
           <t>LAND TRANSPORTATION
-trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver (Trailler 40 feet DN 8959 RA muat Portacamp Office 40 feet)</t>
+trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver (Tronton DN 8140 CA Muat Mesin Genset 2 unit, Lighting tower 2 unit dan panel Listrik)</t>
         </is>
       </c>
     </row>
@@ -6486,7 +6486,7 @@
       <c r="B123" t="inlineStr"/>
       <c r="C123" t="inlineStr"/>
       <c r="D123" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         <v>1</v>
       </c>
       <c r="H123" t="n">
-        <v>5290000</v>
+        <v>6555000</v>
       </c>
       <c r="I123" t="n">
         <v>0</v>
@@ -6523,7 +6523,7 @@
       <c r="M123" t="inlineStr">
         <is>
           <t>LAND TRANSPORTATION
-trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver (tronton DN 8639 CH muat tenda, meja-kursi, Counter Weight ABC)</t>
+trailer 40" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver (Trailler 40 feet DN 8950 RA muat Equipment Well Services)</t>
         </is>
       </c>
     </row>
@@ -6536,7 +6536,7 @@
       <c r="B124" t="inlineStr"/>
       <c r="C124" t="inlineStr"/>
       <c r="D124" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -6552,7 +6552,7 @@
         <v>1</v>
       </c>
       <c r="H124" t="n">
-        <v>5290000</v>
+        <v>7600000</v>
       </c>
       <c r="I124" t="n">
         <v>0</v>
@@ -6572,8 +6572,8 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>LAND TRANSPORTATION
-trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver (Tronton DN 8140 CA Muat Mesin Genset 2 unit, Lighting tower 2 unit dan panel Listrik)</t>
+          <t>ADDITIONAL CAMP SERVICES
+Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base (Trailler 40 feet DN 8785 RA Demobilisasi portacamp Sleeper 40 feet  dari Senoro 2 ke Lamo)</t>
         </is>
       </c>
     </row>
@@ -6586,7 +6586,7 @@
       <c r="B125" t="inlineStr"/>
       <c r="C125" t="inlineStr"/>
       <c r="D125" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -6602,7 +6602,7 @@
         <v>1</v>
       </c>
       <c r="H125" t="n">
-        <v>6555000</v>
+        <v>7600000</v>
       </c>
       <c r="I125" t="n">
         <v>0</v>
@@ -6622,21 +6622,21 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>LAND TRANSPORTATION
-trailer 40" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver (Trailler 40 feet DN 8950 RA muat Equipment Well Services)</t>
+          <t>ADDITIONAL CAMP SERVICES
+Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base (Trailler 40 feet DN 8959 RA  Demobilisasi portacamp Office 40 feet  dari Senoro 2 ke Lamo)</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>opname_039C_BSS-JOB_WS_VIII_2026_-</t>
+          <t>opname_039D_BSS-JOB_WS_VIII_2026_-</t>
         </is>
       </c>
       <c r="B126" t="inlineStr"/>
       <c r="C126" t="inlineStr"/>
       <c r="D126" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -6645,7 +6645,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -6662,7 +6662,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>039C/BSS-JOB/WS/VIII/2026</t>
+          <t>039D/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -6673,20 +6673,20 @@
       <c r="M126" t="inlineStr">
         <is>
           <t>ADDITIONAL CAMP SERVICES
-Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base (Trailler 40 feet DN 8785 RA Demobilisasi portacamp Sleeper 40 feet  dari Senoro 2 ke Lamo)</t>
+Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base (Trailler 40 feet DN 8785 RA mobilisasi Portacamp office dari Lamo ke Senoro)</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>opname_039C_BSS-JOB_WS_VIII_2026_-</t>
+          <t>opname_039D_BSS-JOB_WS_VIII_2026_-</t>
         </is>
       </c>
       <c r="B127" t="inlineStr"/>
       <c r="C127" t="inlineStr"/>
       <c r="D127" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -6695,7 +6695,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -6712,7 +6712,7 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>039C/BSS-JOB/WS/VIII/2026</t>
+          <t>039D/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -6723,7 +6723,157 @@
       <c r="M127" t="inlineStr">
         <is>
           <t>ADDITIONAL CAMP SERVICES
-Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base (Trailler 40 feet DN 8959 RA  Demobilisasi portacamp Office 40 feet  dari Senoro 2 ke Lamo)</t>
+Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base (Trailler 40 feet DN 8959 RA mobilisasi Portacamp Sleeper  dari Lamo ke Senoro)</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>opname_039D_BSS-JOB_WS_VIII_2026_-</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr"/>
+      <c r="C128" t="inlineStr"/>
+      <c r="D128" t="n">
+        <v>3</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="G128" t="n">
+        <v>1</v>
+      </c>
+      <c r="H128" t="n">
+        <v>5520000</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0</v>
+      </c>
+      <c r="J128" t="n">
+        <v>1</v>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>039D/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>LAND TRANSPORTATION
+trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Contractor's alternative jetty atau sebaliknya c/w BBM &amp; driver (Tronton 20 feet DN 9639 CH dari Lamo ke Senoro 2 pindahkan Barang TGE di lokasi senoro 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>opname_038_BSS-JOB_WS_IX_2026_4500011739</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr"/>
+      <c r="C129" t="inlineStr"/>
+      <c r="D129" t="n">
+        <v>1</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G129" t="n">
+        <v>18300</v>
+      </c>
+      <c r="H129" t="n">
+        <v>65000</v>
+      </c>
+      <c r="I129" t="n">
+        <v>2578</v>
+      </c>
+      <c r="J129" t="n">
+        <v>3195</v>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>038/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES
+Food &amp; beverage, main course (DDITIONAL CAMP SERVICES, Operational Consumption)</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>opname_038_BSS-JOB_WS_IX_2026_4500011739</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr"/>
+      <c r="C130" t="inlineStr"/>
+      <c r="D130" t="n">
+        <v>2</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G130" t="n">
+        <v>9200</v>
+      </c>
+      <c r="H130" t="n">
+        <v>33000</v>
+      </c>
+      <c r="I130" t="n">
+        <v>1157</v>
+      </c>
+      <c r="J130" t="n">
+        <v>1488</v>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>038/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES
+Food &amp; beverage, snack coffee/ tea &amp; desert (ADDITIONAL CAMP SERVICES, Operational side consumption)</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_opname_parameter.xlsx
+++ b/database_penyimpanan_aman/database_opname_parameter.xlsx
@@ -5180,7 +5180,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>opname_046_BSS-JOB_WS_IX_2026_4500011739</t>
+          <t>opname_048_BSS-JOB_WS_IX_2026_4500011739</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
@@ -5199,20 +5199,20 @@
         </is>
       </c>
       <c r="G97" t="n">
-        <v>120</v>
+        <v>4600</v>
       </c>
       <c r="H97" t="n">
-        <v>1600000</v>
+        <v>25000</v>
       </c>
       <c r="I97" t="n">
-        <v>25</v>
+        <v>806.6</v>
       </c>
       <c r="J97" t="n">
-        <v>30</v>
+        <v>458.4</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>046/BSS-JOB/WS/IX/2026</t>
+          <t>048/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -5222,21 +5222,21 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION
-Station wagon 7 seater diesel engine + driver + BBM, (Kendaraan Inova DN 1259 CL  Support Well Services Periode tanggal 01 sd 30 September 2026)</t>
+          <t>ADDITIONAL CAMP SERVICES
+Laundry services (Laundry services, Untuk Personel Serco Periode 01 sd 30 September 2026)</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>opname_046_BSS-JOB_WS_IX_2026_4500011739</t>
+          <t>opname_049_BSS-JOB_WS_IX_2026_-</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="inlineStr"/>
       <c r="D98" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -5249,44 +5249,44 @@
         </is>
       </c>
       <c r="G98" t="n">
-        <v>120</v>
+        <v>2188</v>
       </c>
       <c r="H98" t="n">
-        <v>1600000</v>
+        <v>7500</v>
       </c>
       <c r="I98" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="J98" t="n">
-        <v>30</v>
+        <v>2188</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>046/BSS-JOB/WS/IX/2026</t>
+          <t>049/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION
-Station wagon 7 seater diesel engine + driver + BBM, (Kendaraan Inova DN 1257 CL  Support Well Services Periode tanggal 01 sd 30 September 2026)</t>
+          <t>ESTIMATED SUM
+Aqua 600 ml (Etimated SUM Penyediaan  Air Mineral Aqua 600 ml untuk Support Pekerjaan Well Services di Senoro Periode 01 sd 30 September 2026)</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>opname_046_BSS-JOB_WS_IX_2026_4500011739</t>
+          <t>opname_049_BSS-JOB_WS_IX_2026_-</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="inlineStr"/>
       <c r="D99" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -5299,44 +5299,44 @@
         </is>
       </c>
       <c r="G99" t="n">
-        <v>120</v>
+        <v>15</v>
       </c>
       <c r="H99" t="n">
-        <v>1600000</v>
+        <v>53300</v>
       </c>
       <c r="I99" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J99" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>046/BSS-JOB/WS/IX/2026</t>
+          <t>049/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION
-Station wagon 7 seater diesel engine + driver + BBM, (Kendaraan Inova DN 1258 CL  Support Well Services Periode tanggal 27 sd 30 September 2026)</t>
+          <t>ESTIMATED SUM
+Aqua Galon Segel (Etimated SUM Penyediaan  Air Mineral Aqua Galon Segel untuk Support Pekerjaan Well Services di Senoro Periode 01 sd 30 September 2026)</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>opname_046_BSS-JOB_WS_IX_2026_4500011739</t>
+          <t>opname_050_BSS-JOB_WS_IX_2026_-</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
       <c r="C100" t="inlineStr"/>
       <c r="D100" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -5349,44 +5349,44 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>120</v>
+        <v>1</v>
       </c>
       <c r="H100" t="n">
-        <v>1600000</v>
+        <v>69000000</v>
       </c>
       <c r="I100" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J100" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>046/BSS-JOB/WS/IX/2026</t>
+          <t>050/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION
-Double cabin 4x4, diesel engine + driver + BBM, (Kendaraan Double Cabin Hilux DN 1916 CH  Support Well Services Periode tanggal 01 sd 30 September 2026)</t>
+          <t>PROVISIONAL SUM
+At Cost + Fee 15% (Provisional SUM  Akomodasi untuk crew well services di penginapan Yellow Toili Periode 01 sd 30 September 2026)</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>opname_046_BSS-JOB_WS_IX_2026_4500011739</t>
+          <t>opname_047_BSS-JOB_WS_IX_2026_4500011739</t>
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
       <c r="C101" t="inlineStr"/>
       <c r="D101" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -5399,20 +5399,20 @@
         </is>
       </c>
       <c r="G101" t="n">
-        <v>120</v>
+        <v>4</v>
       </c>
       <c r="H101" t="n">
-        <v>1600000</v>
+        <v>25000000</v>
       </c>
       <c r="I101" t="n">
-        <v>22</v>
+        <v>0.48</v>
       </c>
       <c r="J101" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>046/BSS-JOB/WS/IX/2026</t>
+          <t>047/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -5422,21 +5422,21 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION
-Double cabin 4x4, diesel engine + driver + BBM, (Kendaraan Double Cabin Hilux DN 1917 CH  Support Well Services Periode tanggal 01 sd 30 September 2026)</t>
+          <t>ADDITIONAL CAMP SERVICES
+Portacamp - Office Camp,  ukuran 40 FT (Support Well Services Senoro Periode 01 sd 30 September 2026)</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>opname_048_BSS-JOB_WS_IX_2026_4500011739</t>
+          <t>opname_047_BSS-JOB_WS_IX_2026_4500011739</t>
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
       <c r="C102" t="inlineStr"/>
       <c r="D102" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -5449,20 +5449,20 @@
         </is>
       </c>
       <c r="G102" t="n">
-        <v>4600</v>
+        <v>4</v>
       </c>
       <c r="H102" t="n">
-        <v>25000</v>
+        <v>17500000</v>
       </c>
       <c r="I102" t="n">
-        <v>806.6</v>
+        <v>0.48</v>
       </c>
       <c r="J102" t="n">
-        <v>458.4</v>
+        <v>1</v>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>048/BSS-JOB/WS/IX/2026</t>
+          <t>047/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -5473,20 +5473,20 @@
       <c r="M102" t="inlineStr">
         <is>
           <t>ADDITIONAL CAMP SERVICES
-Laundry services (Laundry services, Untuk Personel Serco Periode 01 sd 30 September 2026)</t>
+Portacamp - Living camp,ukuran 40FT (4 sleepers) (Support Well Services Senoro Periode 01 sd 30 September 2026)</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>opname_049_BSS-JOB_WS_IX_2026_-</t>
+          <t>opname_047_BSS-JOB_WS_IX_2026_4500011739</t>
         </is>
       </c>
       <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr"/>
       <c r="D103" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -5499,44 +5499,44 @@
         </is>
       </c>
       <c r="G103" t="n">
-        <v>2188</v>
+        <v>4</v>
       </c>
       <c r="H103" t="n">
-        <v>7500</v>
+        <v>60000000</v>
       </c>
       <c r="I103" t="n">
-        <v>0</v>
+        <v>0.74</v>
       </c>
       <c r="J103" t="n">
-        <v>2188</v>
+        <v>1</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>049/BSS-JOB/WS/IX/2026</t>
+          <t>047/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM
-Aqua 600 ml (Etimated SUM Penyediaan  Air Mineral Aqua 600 ml untuk Support Pekerjaan Well Services di Senoro Periode 01 sd 30 September 2026)</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL
+Genset, cap min 80 KVA, silent type, include maintenance (Operasi Shift Siang Periode 01 sd 30 September 2026)</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>opname_049_BSS-JOB_WS_IX_2026_-</t>
+          <t>opname_047_BSS-JOB_WS_IX_2026_4500011739</t>
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr"/>
       <c r="D104" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -5549,44 +5549,44 @@
         </is>
       </c>
       <c r="G104" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="H104" t="n">
-        <v>53300</v>
+        <v>60000000</v>
       </c>
       <c r="I104" t="n">
-        <v>0</v>
+        <v>0.74</v>
       </c>
       <c r="J104" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>049/BSS-JOB/WS/IX/2026</t>
+          <t>047/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM
-Aqua Galon Segel (Etimated SUM Penyediaan  Air Mineral Aqua Galon Segel untuk Support Pekerjaan Well Services di Senoro Periode 01 sd 30 September 2026)</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL
+Genset, cap min 80 KVA, silent type, include maintenance (Operasi Shift Malam Periode 01 sd 30 September 2026)</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>opname_050_BSS-JOB_WS_IX_2026_-</t>
+          <t>opname_047_BSS-JOB_WS_IX_2026_4500011739</t>
         </is>
       </c>
       <c r="B105" t="inlineStr"/>
       <c r="C105" t="inlineStr"/>
       <c r="D105" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -5599,31 +5599,31 @@
         </is>
       </c>
       <c r="G105" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H105" t="n">
-        <v>69000000</v>
+        <v>15000000</v>
       </c>
       <c r="I105" t="n">
-        <v>0</v>
+        <v>0.74</v>
       </c>
       <c r="J105" t="n">
         <v>1</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>050/BSS-JOB/WS/IX/2026</t>
+          <t>047/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM
-At Cost + Fee 15% (Provisional SUM  Akomodasi untuk crew well services di penginapan Yellow Toili Periode 01 sd 30 September 2026)</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL
+Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories (Operasi Shift Malam Periode 01 sd 30 September 2026)</t>
         </is>
       </c>
     </row>
@@ -5636,7 +5636,7 @@
       <c r="B106" t="inlineStr"/>
       <c r="C106" t="inlineStr"/>
       <c r="D106" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -5652,10 +5652,10 @@
         <v>4</v>
       </c>
       <c r="H106" t="n">
-        <v>25000000</v>
+        <v>15000000</v>
       </c>
       <c r="I106" t="n">
-        <v>0.48</v>
+        <v>0.74</v>
       </c>
       <c r="J106" t="n">
         <v>1</v>
@@ -5672,21 +5672,21 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES
-Portacamp - Office Camp,  ukuran 40 FT (Support Well Services Senoro Periode 01 sd 30 September 2026)</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL
+Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories (Operasi Shift Malam Periode 01 sd 30 September 2026)</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>opname_047_BSS-JOB_WS_IX_2026_4500011739</t>
+          <t>opname_039_BSS-JOB_WS_VIII_2026_4500011739</t>
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
       <c r="C107" t="inlineStr"/>
       <c r="D107" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -5695,24 +5695,24 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G107" t="n">
         <v>4</v>
       </c>
       <c r="H107" t="n">
-        <v>17500000</v>
+        <v>7500000</v>
       </c>
       <c r="I107" t="n">
-        <v>0.48</v>
+        <v>0</v>
       </c>
       <c r="J107" t="n">
         <v>1</v>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>047/BSS-JOB/WS/IX/2026</t>
+          <t>039/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -5722,21 +5722,21 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES
-Portacamp - Living camp,ukuran 40FT (4 sleepers) (Support Well Services Senoro Periode 01 sd 30 September 2026)</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL
+Mobilization/ Demobilization of Rental Equipments (Genset/ Air Compressor/ Light Tower/ Fuel Tank, etc) to/from Company Wellsite/ Contractor base (Tronton Muat Mesin Genset dan Light tower dari Lamo ke Cluster B)</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>opname_047_BSS-JOB_WS_IX_2026_4500011739</t>
+          <t>opname_039_BSS-JOB_WS_VIII_2026_4500011739</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
       <c r="C108" t="inlineStr"/>
       <c r="D108" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -5745,24 +5745,24 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G108" t="n">
         <v>4</v>
       </c>
       <c r="H108" t="n">
-        <v>60000000</v>
+        <v>7500000</v>
       </c>
       <c r="I108" t="n">
-        <v>0.74</v>
+        <v>0</v>
       </c>
       <c r="J108" t="n">
         <v>1</v>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>047/BSS-JOB/WS/IX/2026</t>
+          <t>039/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -5773,20 +5773,20 @@
       <c r="M108" t="inlineStr">
         <is>
           <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL
-Genset, cap min 80 KVA, silent type, include maintenance (Operasi Shift Siang Periode 01 sd 30 September 2026)</t>
+Mobilization/ Demobilization of Rental Equipments (Genset/ Air Compressor/ Light Tower/ Fuel Tank, etc) to/from Company Wellsite/ Contractor base (Tronton Muat  Tenda, Meja, Kursi dan Counter Weight dari Lamo ke Cluster B)</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>opname_047_BSS-JOB_WS_IX_2026_4500011739</t>
+          <t>opname_039A_BSS-JOB_WS_VIII_2026_-</t>
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
       <c r="C109" t="inlineStr"/>
       <c r="D109" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -5795,48 +5795,48 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G109" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H109" t="n">
-        <v>60000000</v>
+        <v>7600000</v>
       </c>
       <c r="I109" t="n">
-        <v>0.74</v>
+        <v>0</v>
       </c>
       <c r="J109" t="n">
         <v>1</v>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>047/BSS-JOB/WS/IX/2026</t>
+          <t>039A/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL
-Genset, cap min 80 KVA, silent type, include maintenance (Operasi Shift Malam Periode 01 sd 30 September 2026)</t>
+          <t>ADDITIONAL CAMP SERVICES
+Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base (Trailler 40 feet Mobilisasi Portacamp Office dari Lamo ke Cluster B)</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>opname_047_BSS-JOB_WS_IX_2026_4500011739</t>
+          <t>opname_039A_BSS-JOB_WS_VIII_2026_-</t>
         </is>
       </c>
       <c r="B110" t="inlineStr"/>
       <c r="C110" t="inlineStr"/>
       <c r="D110" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -5845,48 +5845,48 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G110" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H110" t="n">
-        <v>15000000</v>
+        <v>7600000</v>
       </c>
       <c r="I110" t="n">
-        <v>0.74</v>
+        <v>0</v>
       </c>
       <c r="J110" t="n">
         <v>1</v>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>047/BSS-JOB/WS/IX/2026</t>
+          <t>039A/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL
-Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories (Operasi Shift Malam Periode 01 sd 30 September 2026)</t>
+          <t>ADDITIONAL CAMP SERVICES
+Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base (Trailler 40 feet Mobilisasi Portacamp Sleeper  dari Lamo ke Cluster B)</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>opname_047_BSS-JOB_WS_IX_2026_4500011739</t>
+          <t>opname_039B_BSS-JOB_WS_VIII_2026_-</t>
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
       <c r="C111" t="inlineStr"/>
       <c r="D111" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -5895,48 +5895,48 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G111" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H111" t="n">
-        <v>15000000</v>
+        <v>5290000</v>
       </c>
       <c r="I111" t="n">
-        <v>0.74</v>
+        <v>0</v>
       </c>
       <c r="J111" t="n">
         <v>1</v>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>047/BSS-JOB/WS/IX/2026</t>
+          <t>039B/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL
-Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories (Operasi Shift Malam Periode 01 sd 30 September 2026)</t>
+          <t>LAND TRANSPORTATION
+trailer 20" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver (Tronton DN 8639 CH muat tenda, meja - kursi dan Counter Weight)</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>opname_039_BSS-JOB_WS_VIII_2026_4500011739</t>
+          <t>opname_039B_BSS-JOB_WS_VIII_2026_-</t>
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
       <c r="C112" t="inlineStr"/>
       <c r="D112" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -5945,14 +5945,14 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G112" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H112" t="n">
-        <v>7500000</v>
+        <v>5290000</v>
       </c>
       <c r="I112" t="n">
         <v>0</v>
@@ -5962,31 +5962,31 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>039/BSS-JOB/WS/VIII/2026</t>
+          <t>039B/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL
-Mobilization/ Demobilization of Rental Equipments (Genset/ Air Compressor/ Light Tower/ Fuel Tank, etc) to/from Company Wellsite/ Contractor base (Tronton Muat Mesin Genset dan Light tower dari Lamo ke Cluster B)</t>
+          <t>LAND TRANSPORTATION
+trailer 20" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver (Tronton DN 8140 CA Muat Mesin Genset 2 unit, Lighting tower 2 unit dan panel Listrik)</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>opname_039_BSS-JOB_WS_VIII_2026_4500011739</t>
+          <t>opname_039B_BSS-JOB_WS_VIII_2026_-</t>
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
       <c r="C113" t="inlineStr"/>
       <c r="D113" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -5995,14 +5995,14 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G113" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H113" t="n">
-        <v>7500000</v>
+        <v>6555000</v>
       </c>
       <c r="I113" t="n">
         <v>0</v>
@@ -6012,31 +6012,31 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>039/BSS-JOB/WS/VIII/2026</t>
+          <t>039B/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL
-Mobilization/ Demobilization of Rental Equipments (Genset/ Air Compressor/ Light Tower/ Fuel Tank, etc) to/from Company Wellsite/ Contractor base (Tronton Muat  Tenda, Meja, Kursi dan Counter Weight dari Lamo ke Cluster B)</t>
+          <t>LAND TRANSPORTATION
+trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver (Trailler 40 feet DN 8785 RA muat equipment well services)</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>opname_039A_BSS-JOB_WS_VIII_2026_-</t>
+          <t>opname_039B_BSS-JOB_WS_VIII_2026_-</t>
         </is>
       </c>
       <c r="B114" t="inlineStr"/>
       <c r="C114" t="inlineStr"/>
       <c r="D114" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -6045,14 +6045,14 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G114" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H114" t="n">
-        <v>7600000</v>
+        <v>6555000</v>
       </c>
       <c r="I114" t="n">
         <v>0</v>
@@ -6062,7 +6062,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>039A/BSS-JOB/WS/VIII/2026</t>
+          <t>039B/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -6072,21 +6072,21 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES
-Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base (Trailler 40 feet Mobilisasi Portacamp Office dari Lamo ke Cluster B)</t>
+          <t>LAND TRANSPORTATION
+trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver (Trailler 40 feet DN 8950 RA muat Portacamp sleeper 40 feet)</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>opname_039A_BSS-JOB_WS_VIII_2026_-</t>
+          <t>opname_039B_BSS-JOB_WS_VIII_2026_-</t>
         </is>
       </c>
       <c r="B115" t="inlineStr"/>
       <c r="C115" t="inlineStr"/>
       <c r="D115" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -6095,14 +6095,14 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G115" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H115" t="n">
-        <v>7600000</v>
+        <v>6555000</v>
       </c>
       <c r="I115" t="n">
         <v>0</v>
@@ -6112,7 +6112,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>039A/BSS-JOB/WS/VIII/2026</t>
+          <t>039B/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -6122,15 +6122,15 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES
-Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base (Trailler 40 feet Mobilisasi Portacamp Sleeper  dari Lamo ke Cluster B)</t>
+          <t>LAND TRANSPORTATION
+trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver (Trailler 40 feet DN 8959 RA muat Portacamp Office 40 feet)</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>opname_039B_BSS-JOB_WS_VIII_2026_-</t>
+          <t>opname_039C_BSS-JOB_WS_VIII_2026_-</t>
         </is>
       </c>
       <c r="B116" t="inlineStr"/>
@@ -6145,7 +6145,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -6162,7 +6162,7 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>039B/BSS-JOB/WS/VIII/2026</t>
+          <t>039C/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -6173,14 +6173,14 @@
       <c r="M116" t="inlineStr">
         <is>
           <t>LAND TRANSPORTATION
-trailer 20" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver (Tronton DN 8639 CH muat tenda, meja - kursi dan Counter Weight)</t>
+trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver (tronton DN 8639 CH muat tenda, meja-kursi, Counter Weight ABC)</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>opname_039B_BSS-JOB_WS_VIII_2026_-</t>
+          <t>opname_039C_BSS-JOB_WS_VIII_2026_-</t>
         </is>
       </c>
       <c r="B117" t="inlineStr"/>
@@ -6195,7 +6195,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -6212,7 +6212,7 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>039B/BSS-JOB/WS/VIII/2026</t>
+          <t>039C/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -6223,14 +6223,14 @@
       <c r="M117" t="inlineStr">
         <is>
           <t>LAND TRANSPORTATION
-trailer 20" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver (Tronton DN 8140 CA Muat Mesin Genset 2 unit, Lighting tower 2 unit dan panel Listrik)</t>
+trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver (Tronton DN 8140 CA Muat Mesin Genset 2 unit, Lighting tower 2 unit dan panel Listrik)</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>opname_039B_BSS-JOB_WS_VIII_2026_-</t>
+          <t>opname_039C_BSS-JOB_WS_VIII_2026_-</t>
         </is>
       </c>
       <c r="B118" t="inlineStr"/>
@@ -6245,7 +6245,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -6262,7 +6262,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>039B/BSS-JOB/WS/VIII/2026</t>
+          <t>039C/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -6273,14 +6273,14 @@
       <c r="M118" t="inlineStr">
         <is>
           <t>LAND TRANSPORTATION
-trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver (Trailler 40 feet DN 8785 RA muat equipment well services)</t>
+trailer 40" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver (Trailler 40 feet DN 8950 RA muat Equipment Well Services)</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>opname_039B_BSS-JOB_WS_VIII_2026_-</t>
+          <t>opname_039C_BSS-JOB_WS_VIII_2026_-</t>
         </is>
       </c>
       <c r="B119" t="inlineStr"/>
@@ -6295,14 +6295,14 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G119" t="n">
         <v>1</v>
       </c>
       <c r="H119" t="n">
-        <v>6555000</v>
+        <v>7600000</v>
       </c>
       <c r="I119" t="n">
         <v>0</v>
@@ -6312,7 +6312,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>039B/BSS-JOB/WS/VIII/2026</t>
+          <t>039C/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -6322,15 +6322,15 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>LAND TRANSPORTATION
-trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver (Trailler 40 feet DN 8950 RA muat Portacamp sleeper 40 feet)</t>
+          <t>ADDITIONAL CAMP SERVICES
+Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base (Trailler 40 feet DN 8785 RA Demobilisasi portacamp Sleeper 40 feet  dari Senoro 2 ke Lamo)</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>opname_039B_BSS-JOB_WS_VIII_2026_-</t>
+          <t>opname_039C_BSS-JOB_WS_VIII_2026_-</t>
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
@@ -6345,14 +6345,14 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G120" t="n">
         <v>1</v>
       </c>
       <c r="H120" t="n">
-        <v>6555000</v>
+        <v>7600000</v>
       </c>
       <c r="I120" t="n">
         <v>0</v>
@@ -6362,7 +6362,7 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>039B/BSS-JOB/WS/VIII/2026</t>
+          <t>039C/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -6372,15 +6372,15 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>LAND TRANSPORTATION
-trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver (Trailler 40 feet DN 8959 RA muat Portacamp Office 40 feet)</t>
+          <t>ADDITIONAL CAMP SERVICES
+Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base (Trailler 40 feet DN 8959 RA  Demobilisasi portacamp Office 40 feet  dari Senoro 2 ke Lamo)</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>opname_039C_BSS-JOB_WS_VIII_2026_-</t>
+          <t>opname_039D_BSS-JOB_WS_VIII_2026_-</t>
         </is>
       </c>
       <c r="B121" t="inlineStr"/>
@@ -6395,14 +6395,14 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="G121" t="n">
         <v>1</v>
       </c>
       <c r="H121" t="n">
-        <v>5290000</v>
+        <v>7600000</v>
       </c>
       <c r="I121" t="n">
         <v>0</v>
@@ -6412,7 +6412,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>039C/BSS-JOB/WS/VIII/2026</t>
+          <t>039D/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -6422,15 +6422,15 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>LAND TRANSPORTATION
-trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver (tronton DN 8639 CH muat tenda, meja-kursi, Counter Weight ABC)</t>
+          <t>ADDITIONAL CAMP SERVICES
+Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base (Trailler 40 feet DN 8785 RA mobilisasi Portacamp office dari Lamo ke Senoro)</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>opname_039C_BSS-JOB_WS_VIII_2026_-</t>
+          <t>opname_039D_BSS-JOB_WS_VIII_2026_-</t>
         </is>
       </c>
       <c r="B122" t="inlineStr"/>
@@ -6445,14 +6445,14 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="G122" t="n">
         <v>1</v>
       </c>
       <c r="H122" t="n">
-        <v>5290000</v>
+        <v>7600000</v>
       </c>
       <c r="I122" t="n">
         <v>0</v>
@@ -6462,7 +6462,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>039C/BSS-JOB/WS/VIII/2026</t>
+          <t>039D/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -6472,15 +6472,15 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>LAND TRANSPORTATION
-trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver (Tronton DN 8140 CA Muat Mesin Genset 2 unit, Lighting tower 2 unit dan panel Listrik)</t>
+          <t>ADDITIONAL CAMP SERVICES
+Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base (Trailler 40 feet DN 8959 RA mobilisasi Portacamp Sleeper  dari Lamo ke Senoro)</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>opname_039C_BSS-JOB_WS_VIII_2026_-</t>
+          <t>opname_039D_BSS-JOB_WS_VIII_2026_-</t>
         </is>
       </c>
       <c r="B123" t="inlineStr"/>
@@ -6495,14 +6495,14 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="G123" t="n">
         <v>1</v>
       </c>
       <c r="H123" t="n">
-        <v>6555000</v>
+        <v>5520000</v>
       </c>
       <c r="I123" t="n">
         <v>0</v>
@@ -6512,7 +6512,7 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>039C/BSS-JOB/WS/VIII/2026</t>
+          <t>039D/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -6523,20 +6523,20 @@
       <c r="M123" t="inlineStr">
         <is>
           <t>LAND TRANSPORTATION
-trailer 40" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver (Trailler 40 feet DN 8950 RA muat Equipment Well Services)</t>
+trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Contractor's alternative jetty atau sebaliknya c/w BBM &amp; driver (Tronton 20 feet DN 9639 CH dari Lamo ke Senoro 2 pindahkan Barang TGE di lokasi senoro 2)</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>opname_039C_BSS-JOB_WS_VIII_2026_-</t>
+          <t>opname_038_BSS-JOB_WS_IX_2026_4500011739</t>
         </is>
       </c>
       <c r="B124" t="inlineStr"/>
       <c r="C124" t="inlineStr"/>
       <c r="D124" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -6545,48 +6545,48 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G124" t="n">
-        <v>1</v>
+        <v>18300</v>
       </c>
       <c r="H124" t="n">
-        <v>7600000</v>
+        <v>65000</v>
       </c>
       <c r="I124" t="n">
-        <v>0</v>
+        <v>2578</v>
       </c>
       <c r="J124" t="n">
-        <v>1</v>
+        <v>3195</v>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>039C/BSS-JOB/WS/VIII/2026</t>
+          <t>038/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
         <is>
           <t>ADDITIONAL CAMP SERVICES
-Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base (Trailler 40 feet DN 8785 RA Demobilisasi portacamp Sleeper 40 feet  dari Senoro 2 ke Lamo)</t>
+Food &amp; beverage, main course (DDITIONAL CAMP SERVICES, Operational Consumption)</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>opname_039C_BSS-JOB_WS_VIII_2026_-</t>
+          <t>opname_038_BSS-JOB_WS_IX_2026_4500011739</t>
         </is>
       </c>
       <c r="B125" t="inlineStr"/>
       <c r="C125" t="inlineStr"/>
       <c r="D125" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -6595,42 +6595,42 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G125" t="n">
-        <v>1</v>
+        <v>9200</v>
       </c>
       <c r="H125" t="n">
-        <v>7600000</v>
+        <v>33000</v>
       </c>
       <c r="I125" t="n">
-        <v>0</v>
+        <v>1157</v>
       </c>
       <c r="J125" t="n">
-        <v>1</v>
+        <v>1488</v>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>039C/BSS-JOB/WS/VIII/2026</t>
+          <t>038/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
         <is>
           <t>ADDITIONAL CAMP SERVICES
-Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base (Trailler 40 feet DN 8959 RA  Demobilisasi portacamp Office 40 feet  dari Senoro 2 ke Lamo)</t>
+Food &amp; beverage, snack coffee/ tea &amp; desert (ADDITIONAL CAMP SERVICES, Operational side consumption)</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>opname_039D_BSS-JOB_WS_VIII_2026_-</t>
+          <t>opname_046_BSS-JOB_WS_IX_2026_4500011739</t>
         </is>
       </c>
       <c r="B126" t="inlineStr"/>
@@ -6645,42 +6645,42 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G126" t="n">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="H126" t="n">
-        <v>7600000</v>
+        <v>1600000</v>
       </c>
       <c r="I126" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J126" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>039D/BSS-JOB/WS/VIII/2026</t>
+          <t>046/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES
-Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base (Trailler 40 feet DN 8785 RA mobilisasi Portacamp office dari Lamo ke Senoro)</t>
+          <t>CAR &amp; TANSPORTATION
+Station wagon 7 seater diesel engine + driver + BBM, (Kendaraan Inova DN 1259 CL  Support Well Services Periode tanggal 01 sd 30 September 2026)</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>opname_039D_BSS-JOB_WS_VIII_2026_-</t>
+          <t>opname_046_BSS-JOB_WS_IX_2026_4500011739</t>
         </is>
       </c>
       <c r="B127" t="inlineStr"/>
@@ -6695,42 +6695,42 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G127" t="n">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="H127" t="n">
-        <v>7600000</v>
+        <v>1600000</v>
       </c>
       <c r="I127" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J127" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>039D/BSS-JOB/WS/VIII/2026</t>
+          <t>046/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES
-Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base (Trailler 40 feet DN 8959 RA mobilisasi Portacamp Sleeper  dari Lamo ke Senoro)</t>
+          <t>CAR &amp; TANSPORTATION
+Station wagon 7 seater diesel engine + driver + BBM, (Kendaraan Inova DN 1257 CL  Support Well Services Periode tanggal 01 sd 30 September 2026)</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>opname_039D_BSS-JOB_WS_VIII_2026_-</t>
+          <t>opname_046_BSS-JOB_WS_IX_2026_4500011739</t>
         </is>
       </c>
       <c r="B128" t="inlineStr"/>
@@ -6745,48 +6745,48 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G128" t="n">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="H128" t="n">
-        <v>5520000</v>
+        <v>1600000</v>
       </c>
       <c r="I128" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="J128" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>039D/BSS-JOB/WS/VIII/2026</t>
+          <t>046/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>LAND TRANSPORTATION
-trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Contractor's alternative jetty atau sebaliknya c/w BBM &amp; driver (Tronton 20 feet DN 9639 CH dari Lamo ke Senoro 2 pindahkan Barang TGE di lokasi senoro 2)</t>
+          <t>CAR &amp; TANSPORTATION
+Station wagon 7 seater diesel engine + driver + BBM, (Kendaraan Inova DN 1258 CL  Support Well Services Periode tanggal 27 sd 30 September 2026)</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>opname_038_BSS-JOB_WS_IX_2026_4500011739</t>
+          <t>opname_046_BSS-JOB_WS_IX_2026_4500011739</t>
         </is>
       </c>
       <c r="B129" t="inlineStr"/>
       <c r="C129" t="inlineStr"/>
       <c r="D129" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -6799,20 +6799,20 @@
         </is>
       </c>
       <c r="G129" t="n">
-        <v>18300</v>
+        <v>120</v>
       </c>
       <c r="H129" t="n">
-        <v>65000</v>
+        <v>1600000</v>
       </c>
       <c r="I129" t="n">
-        <v>2578</v>
+        <v>26</v>
       </c>
       <c r="J129" t="n">
-        <v>3195</v>
+        <v>30</v>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>038/BSS-JOB/WS/IX/2026</t>
+          <t>046/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -6822,21 +6822,21 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES
-Food &amp; beverage, main course (DDITIONAL CAMP SERVICES, Operational Consumption)</t>
+          <t>CAR &amp; TANSPORTATION
+Double cabin 4x4, diesel engine + driver + BBM, (Kendaraan Double Cabin Hilux DN 8916 CH  Support Well Services Periode tanggal 01 sd 30 September 2026)</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>opname_038_BSS-JOB_WS_IX_2026_4500011739</t>
+          <t>opname_046_BSS-JOB_WS_IX_2026_4500011739</t>
         </is>
       </c>
       <c r="B130" t="inlineStr"/>
       <c r="C130" t="inlineStr"/>
       <c r="D130" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -6849,20 +6849,20 @@
         </is>
       </c>
       <c r="G130" t="n">
-        <v>9200</v>
+        <v>120</v>
       </c>
       <c r="H130" t="n">
-        <v>33000</v>
+        <v>1600000</v>
       </c>
       <c r="I130" t="n">
-        <v>1157</v>
+        <v>22</v>
       </c>
       <c r="J130" t="n">
-        <v>1488</v>
+        <v>30</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>038/BSS-JOB/WS/IX/2026</t>
+          <t>046/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -6872,8 +6872,8 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES
-Food &amp; beverage, snack coffee/ tea &amp; desert (ADDITIONAL CAMP SERVICES, Operational side consumption)</t>
+          <t>CAR &amp; TANSPORTATION
+Double cabin 4x4, diesel engine + driver + BBM, (Kendaraan Double Cabin Hilux DN 8917 CH  Support Well Services Periode tanggal 01 sd 30 September 2026)</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_opname_parameter.xlsx
+++ b/database_penyimpanan_aman/database_opname_parameter.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M130"/>
+  <dimension ref="A1:M132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6877,6 +6877,106 @@
         </is>
       </c>
     </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>opname_051_BSS-JOB_WS_VIII_2026_-</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr"/>
+      <c r="C131" t="inlineStr"/>
+      <c r="D131" t="n">
+        <v>1</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G131" t="n">
+        <v>1</v>
+      </c>
+      <c r="H131" t="n">
+        <v>1725000</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0</v>
+      </c>
+      <c r="J131" t="n">
+        <v>1</v>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>051/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>PROVISIONAL SUM
+At Cost + Fee 15% (Provisional SUM  Pengurusan Dokumen Surat Persetujuan Pengeluaran Barang (SPPB) 3 colly di Pelabuhan Batam)</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>opname_052_BSS-JOB_WS_IX_2026_-</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr"/>
+      <c r="C132" t="inlineStr"/>
+      <c r="D132" t="n">
+        <v>1</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="G132" t="n">
+        <v>1</v>
+      </c>
+      <c r="H132" t="n">
+        <v>8625000</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0</v>
+      </c>
+      <c r="J132" t="n">
+        <v>1</v>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>052/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>PROVISIONAL SUM
+At Cost + Fee 15% (Provisional SUM  Pengiriman Barang  Pup Joint dari Pertamina EP Cepu ke Lamda Multi Dinamika Yard di Bogor)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database_penyimpanan_aman/database_opname_parameter.xlsx
+++ b/database_penyimpanan_aman/database_opname_parameter.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M132"/>
+  <dimension ref="A1:M136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6977,6 +6977,206 @@
         </is>
       </c>
     </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>opname_002_BSS-JOB_WS_I_2026_4500011794</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr"/>
+      <c r="C133" t="inlineStr"/>
+      <c r="D133" t="n">
+        <v>1</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="G133" t="n">
+        <v>50</v>
+      </c>
+      <c r="H133" t="n">
+        <v>11500</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0</v>
+      </c>
+      <c r="J133" t="n">
+        <v>50</v>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>002/BSS-JOB/WS/I/2026</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>4500011794</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>PROVISIONAL SUM
+At Cost + Fee 15% (Garam Kasar Untuk Pekerjaan Sealant di Cluster B)</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>opname_002_BSS-JOB_WS_I_2026_4500011794</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr"/>
+      <c r="C134" t="inlineStr"/>
+      <c r="D134" t="n">
+        <v>2</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="G134" t="n">
+        <v>50</v>
+      </c>
+      <c r="H134" t="n">
+        <v>17250</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0</v>
+      </c>
+      <c r="J134" t="n">
+        <v>50</v>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>002/BSS-JOB/WS/I/2026</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>4500011794</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>PROVISIONAL SUM
+At Cost + Fee 15% (Belerang Untuk Pekerjaan Sealant di Cluster B)</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>opname_021_BSS-JOB_WS_IX_2026_4500011795</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr"/>
+      <c r="C135" t="inlineStr"/>
+      <c r="D135" t="n">
+        <v>1</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G135" t="n">
+        <v>2</v>
+      </c>
+      <c r="H135" t="n">
+        <v>201250</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0</v>
+      </c>
+      <c r="J135" t="n">
+        <v>2</v>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>021/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>4500011795</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>PROVISIONAL SUM
+At Cost + Fee 15% (Kontainer box ukuran 95 untuk Penyimpanan APD dan Dokument)</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>opname_021_BSS-JOB_WS_IX_2026_4500011795</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr"/>
+      <c r="C136" t="inlineStr"/>
+      <c r="D136" t="n">
+        <v>2</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G136" t="n">
+        <v>1</v>
+      </c>
+      <c r="H136" t="n">
+        <v>115000</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0</v>
+      </c>
+      <c r="J136" t="n">
+        <v>1</v>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>021/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>4500011795</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>PROVISIONAL SUM
+At Cost + Fee 15% (Kontainer box ukuran 52 untuk Penyimpanan APD dan Dokument)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database_penyimpanan_aman/database_opname_parameter.xlsx
+++ b/database_penyimpanan_aman/database_opname_parameter.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M136"/>
+  <dimension ref="A1:M137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7177,6 +7177,56 @@
         </is>
       </c>
     </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>opname_012_BSS-JOB_WS_VIII_2026_4500011586</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr"/>
+      <c r="C137" t="inlineStr"/>
+      <c r="D137" t="n">
+        <v>1</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="G137" t="n">
+        <v>1</v>
+      </c>
+      <c r="H137" t="n">
+        <v>24150000</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0</v>
+      </c>
+      <c r="J137" t="n">
+        <v>1</v>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>012/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>4500011586</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>PROVISIONAL SUM
+At Cost + Fee 15% (Meeting package pelatihan HSE untuk kegiatan wellservices 2026)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database_penyimpanan_aman/database_opname_parameter.xlsx
+++ b/database_penyimpanan_aman/database_opname_parameter.xlsx
@@ -576,7 +576,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>opname_016_BSS-JOB_WS_VIII_2026_4500011739</t>
+          <t>opname_017_BSS-JOB_WS_VIII_2026_4500011682</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -591,47 +591,47 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>18300</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>65000</v>
+        <v>1334000</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>2578</v>
+        <v>1</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>016/BSS-JOB/WS/VIII/2026</t>
+          <t>017/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>4500011682</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES - Food &amp; beverage, main course (ADDITIONAL CAMP SERVICES, Operational Consumption)</t>
+          <t>PROVISIONAL SUM - Add Cost + Fee 15% (Penyediaan electric cable pendukung wellservice camp Ukuran 3x25 mm NYM)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>opname_016_BSS-JOB_WS_VIII_2026_4500011739</t>
+          <t>opname_018_BSS-JOB_WS_VIII_2026_4500011683</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -640,41 +640,41 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>9200</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>33000</v>
+        <v>1600000</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>1157</v>
+        <v>1</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>016/BSS-JOB/WS/VIII/2026</t>
+          <t>018/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>4500011683</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES - Food &amp; beverage, snack coffee/ tea &amp; desert (ADDITIONAL CAMP SERVICES, Operational side consumption)</t>
+          <t>CAR &amp; TANSPORTATION - Double cabin 4x4, diesel engine + driver + BBM, (Transport pengangkut electric cable pendukung wellservice camp)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>opname_017_BSS-JOB_WS_VIII_2026_4500011682</t>
+          <t>opname_023_BSS-JOB_WS_VIII_2026_4500011739</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -689,41 +689,41 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>240</v>
       </c>
       <c r="H6" t="n">
-        <v>1334000</v>
+        <v>750000</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>017/BSS-JOB/WS/VIII/2026</t>
+          <t>023/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>4500011682</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM - Add Cost + Fee 15% (Penyediaan electric cable pendukung wellservice camp Ukuran 3x25 mm NYM)</t>
+          <t>PERSONEL ON CALL - Personnel GS in-charge di lokasi pemboran/ wellservices/ workover, personnel in charge (Personel GS - Koordinator Lapangan atas Nama Nur Afiata)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>opname_018_BSS-JOB_WS_VIII_2026_4500011683</t>
+          <t>opname_023A_BSS-JOB_WS_VIII_2026_4500011739</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -738,47 +738,47 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="H7" t="n">
-        <v>1600000</v>
+        <v>500000</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>018/BSS-JOB/WS/VIII/2026</t>
+          <t>023A/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>4500011683</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION - Double cabin 4x4, diesel engine + driver + BBM, (Transport pengangkut electric cable pendukung wellservice camp)</t>
+          <t>PERSONEL ON CALL - Welder (GTAW) (Supporting equipment kegiatan Wellservices 2026  Welder = Personel HSE Officer  ( Gusti Ngurah Dwipayana ))</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>opname_023_BSS-JOB_WS_VIII_2026_4500011739</t>
+          <t>opname_023A_BSS-JOB_WS_VIII_2026_4500011739</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -791,20 +791,20 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>240</v>
+        <v>120</v>
       </c>
       <c r="H8" t="n">
-        <v>750000</v>
+        <v>500000</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>023/BSS-JOB/WS/VIII/2026</t>
+          <t>023A/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL - Personnel GS in-charge di lokasi pemboran/ wellservices/ workover, personnel in charge (Personel GS - Koordinator Lapangan atas Nama Nur Afiata)</t>
+          <t>PERSONEL ON CALL - Welder (GTAW) (Supporting equipment kegiatan Wellservices 2026  Welder = Personel Paramedic  ( Melita Bella ))</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -863,20 +863,20 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL - Welder (GTAW) (Supporting equipment kegiatan Wellservices 2026  Welder = Personel HSE Officer  ( Gusti Ngurah Dwipayana ))</t>
+          <t>PERSONEL ON CALL - Welder (GTAW) (Supporting equipment kegiatan Wellservices 2026  Welder = Personel Paramedic  ( Widiya Satuwo ))</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>opname_023A_BSS-JOB_WS_VIII_2026_4500011739</t>
+          <t>opname_024A_BSS-JOB_WS_VIII_2026_4500011739</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -898,11 +898,11 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>023A/BSS-JOB/WS/VIII/2026</t>
+          <t>024A/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -912,20 +912,20 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL - Welder (GTAW) (Supporting equipment kegiatan Wellservices 2026  Welder = Personel Paramedic  ( Melita Bella ))</t>
+          <t>PERSONEL ON CALL - Operator Heavy Equipment (Vacuum Truck) (Supporting equipment kegiatan Wellservices 2026, Operator Heavy Equipment (Vacuum Truck))</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>opname_023A_BSS-JOB_WS_VIII_2026_4500011739</t>
+          <t>opname_027_BSS-JOB_WS_VIII_2026_4500011739</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -934,24 +934,24 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>120</v>
+        <v>7</v>
       </c>
       <c r="H11" t="n">
-        <v>500000</v>
+        <v>8500000</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>023A/BSS-JOB/WS/VIII/2026</t>
+          <t>027/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -961,20 +961,20 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL - Welder (GTAW) (Supporting equipment kegiatan Wellservices 2026  Welder = Personel Paramedic  ( Widiya Satuwo ))</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL - crane min 70 ton, call out, (hanya unit) (Crane Tadano 70 ton Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>opname_024A_BSS-JOB_WS_VIII_2026_4500011739</t>
+          <t>opname_027_BSS-JOB_WS_VIII_2026_4500011739</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -987,20 +987,20 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="H12" t="n">
-        <v>500000</v>
+        <v>8500000</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>024A/BSS-JOB/WS/VIII/2026</t>
+          <t>027/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL - Operator Heavy Equipment (Vacuum Truck) (Supporting equipment kegiatan Wellservices 2026, Operator Heavy Equipment (Vacuum Truck))</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL - crane min 70 ton, call out, (hanya unit) (Crane Sany 100 Ton untuk menggantikan Crane Tadano 70 Ton yang rusak)</t>
         </is>
       </c>
     </row>
@@ -1023,7 +1023,7 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1036,16 +1036,16 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>7</v>
+        <v>120</v>
       </c>
       <c r="H13" t="n">
-        <v>8500000</v>
+        <v>2750000</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1059,20 +1059,20 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL - crane min 70 ton, call out, (hanya unit) (Crane Tadano 70 ton Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL - Vacuum Truck , Call out, Cap  5000 ltr c/w vacuum pump &amp; acessories, call out, (hanya unit) (Vacuum Truck  5000 L DN 8806 CH untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>opname_027_BSS-JOB_WS_VIII_2026_4500011739</t>
+          <t>opname_022_BSS-JOB_WS_IX_2026_4500011739</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1081,24 +1081,24 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>113</v>
+        <v>240</v>
       </c>
       <c r="H14" t="n">
-        <v>8500000</v>
+        <v>750000</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="J14" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>027/BSS-JOB/WS/VIII/2026</t>
+          <t>022/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1108,20 +1108,20 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL - crane min 70 ton, call out, (hanya unit) (Crane Sany 100 Ton untuk menggantikan Crane Tadano 70 Ton yang rusak)</t>
+          <t>PERSONEL ON CALL - Personnel GS in-charge di lokasi pemboran/ wellservices/ workover, personnel in charge (Tenaga Civil Engineer melakukan survey di Lokasi Sumur Senoro 16)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>opname_027_BSS-JOB_WS_VIII_2026_4500011739</t>
+          <t>opname_022_BSS-JOB_WS_IX_2026_4500011739</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1130,24 +1130,24 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G15" t="n">
         <v>120</v>
       </c>
       <c r="H15" t="n">
-        <v>2750000</v>
+        <v>1600000</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>027/BSS-JOB/WS/VIII/2026</t>
+          <t>022/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1157,14 +1157,14 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL - Vacuum Truck , Call out, Cap  5000 ltr c/w vacuum pump &amp; acessories, call out, (hanya unit) (Vacuum Truck  5000 L DN 8806 CH untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
+          <t>CAR &amp; TANSPORTATION - Double cabin 4x4, diesel engine + driver + BBM, (Kendaraan Operasional Double Cabin DN 8890 RG untuk transportasi Survey ke Lokasi)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>opname_022_BSS-JOB_WS_IX_2026_4500011739</t>
+          <t>opname_033_BSS-JOB_WS_VIII_2026_4500011739</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -1179,24 +1179,24 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>240</v>
+        <v>2</v>
       </c>
       <c r="H16" t="n">
-        <v>750000</v>
+        <v>12500000</v>
       </c>
       <c r="I16" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
         <v>1</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>022/BSS-JOB/WS/IX/2026</t>
+          <t>033/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1206,20 +1206,20 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL - Personnel GS in-charge di lokasi pemboran/ wellservices/ workover, personnel in charge (Tenaga Civil Engineer melakukan survey di Lokasi Sumur Senoro 16)</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL - Mobilisasi/ Demobilisasi crane min 70 ton to/from Company Wellsite/ Contractor base (Mobilisasi Crane Mobile Tadano Kapasitas 70 ton dari Workshop di Lamo ke Cluster B)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>opname_022_BSS-JOB_WS_IX_2026_4500011739</t>
+          <t>opname_031_BSS-JOB_WS_VIII_2026_4500011739</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1228,24 +1228,24 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>120</v>
+        <v>4600</v>
       </c>
       <c r="H17" t="n">
-        <v>1600000</v>
+        <v>25000</v>
       </c>
       <c r="I17" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>316.8</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>022/BSS-JOB/WS/IX/2026</t>
+          <t>031/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1255,14 +1255,14 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION - Double cabin 4x4, diesel engine + driver + BBM, (Kendaraan Operasional Double Cabin DN 8890 RG untuk transportasi Survey ke Lokasi)</t>
+          <t>ADDITIONAL CAMP SERVICES - Laundry services (ADDITIONAL CAMP SERVICES Laundry services , crew di Lokasi)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>opname_033_BSS-JOB_WS_VIII_2026_4500011739</t>
+          <t>opname_029_BSS-JOB_WS_VIII_2026_0</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -1277,47 +1277,47 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>2</v>
+        <v>250</v>
       </c>
       <c r="H18" t="n">
-        <v>12500000</v>
+        <v>25000</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>250</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>033/BSS-JOB/WS/VIII/2026</t>
+          <t>029/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL - Mobilisasi/ Demobilisasi crane min 70 ton to/from Company Wellsite/ Contractor base (Mobilisasi Crane Mobile Tadano Kapasitas 70 ton dari Workshop di Lamo ke Cluster B)</t>
+          <t>PENGADAAN MATERIAL - Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee, (Pengadaan Diesel Fuel include Tranportir fee, untuk Crane 70 Ton)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>opname_031_BSS-JOB_WS_VIII_2026_4500011739</t>
+          <t>opname_029_BSS-JOB_WS_VIII_2026_0</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>4600</v>
+        <v>200</v>
       </c>
       <c r="H19" t="n">
         <v>25000</v>
@@ -1339,21 +1339,21 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>316.8</v>
+        <v>200</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>031/BSS-JOB/WS/VIII/2026</t>
+          <t>029/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES - Laundry services (ADDITIONAL CAMP SERVICES Laundry services , crew di Lokasi)</t>
+          <t>PENGADAAN MATERIAL - Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee, (Pengadaan Diesel Fuel include Tranportir fee, untuk Crane 100 Ton)</t>
         </is>
       </c>
     </row>
@@ -1366,7 +1366,7 @@
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>250</v>
+        <v>50</v>
       </c>
       <c r="H20" t="n">
         <v>25000</v>
@@ -1388,7 +1388,7 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>250</v>
+        <v>50</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL - Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee, (Pengadaan Diesel Fuel include Tranportir fee, untuk Crane 70 Ton)</t>
+          <t>PENGADAAN MATERIAL - Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee, (Pengadaan Diesel Fuel include Tranportir fee, untuk Genset 80 KVa)</t>
         </is>
       </c>
     </row>
@@ -1415,7 +1415,7 @@
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         </is>
       </c>
       <c r="G21" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="H21" t="n">
         <v>25000</v>
@@ -1437,7 +1437,7 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL - Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee, (Pengadaan Diesel Fuel include Tranportir fee, untuk Crane 100 Ton)</t>
+          <t>PENGADAAN MATERIAL - Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee, (Pengadaan Diesel Fuel include Tranportir fee, untuk Genset 80 KVa)</t>
         </is>
       </c>
     </row>
@@ -1464,7 +1464,7 @@
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL - Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee, (Pengadaan Diesel Fuel include Tranportir fee, untuk Genset 80 KVa)</t>
+          <t>PENGADAAN MATERIAL - Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee, (Pengadaan Diesel Fuel include Tranportir fee, untuk Lighting Tower 05)</t>
         </is>
       </c>
     </row>
@@ -1513,7 +1513,7 @@
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL - Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee, (Pengadaan Diesel Fuel include Tranportir fee, untuk Genset 80 KVa)</t>
+          <t>PENGADAAN MATERIAL - Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee, (Pengadaan Diesel Fuel include Tranportir fee, untuk Lighting Tower 06)</t>
         </is>
       </c>
     </row>
@@ -1562,7 +1562,7 @@
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>50</v>
+        <v>115</v>
       </c>
       <c r="H24" t="n">
         <v>25000</v>
@@ -1584,7 +1584,7 @@
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>50</v>
+        <v>115</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -1598,20 +1598,20 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL - Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee, (Pengadaan Diesel Fuel include Tranportir fee, untuk Lighting Tower 05)</t>
+          <t>PENGADAAN MATERIAL - Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee, (Pengadaan Diesel Fuel include Tranportir fee, untuk Vacuum Truck 5000 L)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>opname_029_BSS-JOB_WS_VIII_2026_0</t>
+          <t>opname_025_BSS-JOB_WS_VIII_2026_4500011739</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1624,43 +1624,43 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="H25" t="n">
-        <v>25000</v>
+        <v>25000000</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>50</v>
+        <v>0.48</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>029/BSS-JOB/WS/VIII/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL - Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee, (Pengadaan Diesel Fuel include Tranportir fee, untuk Lighting Tower 06)</t>
+          <t>ADDITIONAL CAMP SERVICES - Portacamp - Office Camp,  ukuran 40 FT (Portacamp - Office Camp,  ukuran 40 FT Untuk Support Well Services di Lokasi Senoro)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>opname_029_BSS-JOB_WS_VIII_2026_0</t>
+          <t>opname_025_BSS-JOB_WS_VIII_2026_4500011739</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1673,30 +1673,30 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>115</v>
+        <v>4</v>
       </c>
       <c r="H26" t="n">
-        <v>25000</v>
+        <v>17500000</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>115</v>
+        <v>0.48</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>029/BSS-JOB/WS/VIII/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL - Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee, (Pengadaan Diesel Fuel include Tranportir fee, untuk Vacuum Truck 5000 L)</t>
+          <t>ADDITIONAL CAMP SERVICES - Portacamp - Living camp,ukuran 40FT (4 sleepers) (Portacamp - Living camp,ukuran 40FT (4 sleepers) Untuk Support Well Services di Lokasi Senoro)</t>
         </is>
       </c>
     </row>
@@ -1709,7 +1709,7 @@
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1725,13 +1725,13 @@
         <v>4</v>
       </c>
       <c r="H27" t="n">
-        <v>25000000</v>
+        <v>60000000</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0.48</v>
+        <v>0.74</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES - Portacamp - Office Camp,  ukuran 40 FT (Portacamp - Office Camp,  ukuran 40 FT Untuk Support Well Services di Lokasi Senoro)</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL - Genset, cap min 80 KVA, silent type, include maintenance (Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Siang)</t>
         </is>
       </c>
     </row>
@@ -1758,7 +1758,7 @@
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1774,13 +1774,13 @@
         <v>4</v>
       </c>
       <c r="H28" t="n">
-        <v>17500000</v>
+        <v>60000000</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>0.48</v>
+        <v>0.74</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES - Portacamp - Living camp,ukuran 40FT (4 sleepers) (Portacamp - Living camp,ukuran 40FT (4 sleepers) Untuk Support Well Services di Lokasi Senoro)</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL - Genset, cap min 80 KVA, silent type, include maintenance (Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Malam)</t>
         </is>
       </c>
     </row>
@@ -1807,7 +1807,7 @@
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>4</v>
       </c>
       <c r="H29" t="n">
-        <v>60000000</v>
+        <v>15000000</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL - Genset, cap min 80 KVA, silent type, include maintenance (Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Siang)</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL - Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories (Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam)</t>
         </is>
       </c>
     </row>
@@ -1856,7 +1856,7 @@
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         <v>4</v>
       </c>
       <c r="H30" t="n">
-        <v>60000000</v>
+        <v>15000000</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -1892,20 +1892,20 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL - Genset, cap min 80 KVA, silent type, include maintenance (Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Malam)</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL - Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories (Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>opname_025_BSS-JOB_WS_VIII_2026_4500011739</t>
+          <t>opname_024_BSS-JOB_WS_VIII_2026_4500011739</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1918,20 +1918,20 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="H31" t="n">
-        <v>15000000</v>
+        <v>750000</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>0.74</v>
+        <v>13</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>024/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -1941,20 +1941,20 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL - Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories (Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam)</t>
+          <t>PERSONEL ON CALL - Operator Crane (Operator Crane Shift Siang atas nama Rasid A Laugi)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>opname_025_BSS-JOB_WS_VIII_2026_4500011739</t>
+          <t>opname_024_BSS-JOB_WS_VIII_2026_4500011739</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1967,20 +1967,20 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>4</v>
+        <v>120</v>
       </c>
       <c r="H32" t="n">
-        <v>15000000</v>
+        <v>750000</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>0.74</v>
+        <v>9</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>024/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -1990,7 +1990,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL - Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories (Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam)</t>
+          <t>PERSONEL ON CALL - Operator Crane (Operator Crane Shift Siang atas nama Wanhar)</t>
         </is>
       </c>
     </row>
@@ -2003,7 +2003,7 @@
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -2016,7 +2016,7 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>13</v>
+        <v>107</v>
       </c>
       <c r="H33" t="n">
         <v>750000</v>
@@ -2025,7 +2025,7 @@
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL - Operator Crane (Operator Crane Shift Siang atas nama Rasid A Laugi)</t>
+          <t>PERSONEL ON CALL - Operator Crane (Operator Crane Shift Malam  atas nama Ilsan Adjedar)</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -2068,13 +2068,13 @@
         <v>120</v>
       </c>
       <c r="H34" t="n">
-        <v>750000</v>
+        <v>650000</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL - Operator Crane (Operator Crane Shift Siang atas nama Wanhar)</t>
+          <t>PERSONEL ON CALL - Rigger (Rigger  Crane Shift Siang  atas nama Tison)</t>
         </is>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -2114,16 +2114,16 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="H35" t="n">
-        <v>750000</v>
+        <v>650000</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -2137,7 +2137,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL - Operator Crane (Operator Crane Shift Malam  atas nama Ilsan Adjedar)</t>
+          <t>PERSONEL ON CALL - Rigger (Rigger  Crane Shift Malam  atas nama Agus Dg Mangata)</t>
         </is>
       </c>
     </row>
@@ -2150,7 +2150,7 @@
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -2163,16 +2163,16 @@
         </is>
       </c>
       <c r="G36" t="n">
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="H36" t="n">
-        <v>650000</v>
+        <v>600000</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL - Rigger (Rigger  Crane Shift Siang  atas nama Tison)</t>
+          <t>PERSONEL ON CALL - Mechanic/ Electrician (Mechanic/ Electrician operasikan Mesin Genset dan Lighting Tower atas nama Sugeng)</t>
         </is>
       </c>
     </row>
@@ -2199,7 +2199,7 @@
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -2212,16 +2212,16 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="H37" t="n">
-        <v>650000</v>
+        <v>600000</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
@@ -2235,20 +2235,20 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL - Rigger (Rigger  Crane Shift Malam  atas nama Agus Dg Mangata)</t>
+          <t>PERSONEL ON CALL - Mechanic/ Electrician (Mechanic/ Electrician operasikan Mesin Genset dan Lighting Tower atas nama Ahmad Dhani)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>opname_024_BSS-JOB_WS_VIII_2026_4500011739</t>
+          <t>opname_026_BSS-JOB_WS_VIII_2026_4500011739</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -2261,20 +2261,20 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>240</v>
+        <v>120</v>
       </c>
       <c r="H38" t="n">
-        <v>600000</v>
+        <v>1600000</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>024/BSS-JOB/WS/VIII/2026</t>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2284,20 +2284,20 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL - Mechanic/ Electrician (Mechanic/ Electrician operasikan Mesin Genset dan Lighting Tower atas nama Sugeng)</t>
+          <t>CAR &amp; TANSPORTATION - Station wagon 7 seater diesel engine + driver + BBM, (Kendaraan Innova DN 1259 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>opname_024_BSS-JOB_WS_VIII_2026_4500011739</t>
+          <t>opname_026_BSS-JOB_WS_VIII_2026_4500011739</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -2310,20 +2310,20 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>240</v>
+        <v>120</v>
       </c>
       <c r="H39" t="n">
-        <v>600000</v>
+        <v>1600000</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>024/BSS-JOB/WS/VIII/2026</t>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2333,7 +2333,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL - Mechanic/ Electrician (Mechanic/ Electrician operasikan Mesin Genset dan Lighting Tower atas nama Ahmad Dhani)</t>
+          <t>CAR &amp; TANSPORTATION - Station wagon 7 seater diesel engine + driver + BBM, (Kendaraan Innova DN 1258 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
         </is>
       </c>
     </row>
@@ -2346,7 +2346,7 @@
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="H40" t="n">
         <v>1600000</v>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION - Station wagon 7 seater diesel engine + driver + BBM, (Kendaraan Innova DN 1259 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
+          <t>CAR &amp; TANSPORTATION - Station wagon 7 seater diesel engine + driver + BBM, (Kendaraan Innova DN 1257 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
         </is>
       </c>
     </row>
@@ -2395,7 +2395,7 @@
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -2408,7 +2408,7 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>120</v>
+        <v>4</v>
       </c>
       <c r="H41" t="n">
         <v>1600000</v>
@@ -2417,7 +2417,7 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION - Station wagon 7 seater diesel engine + driver + BBM, (Kendaraan Innova DN 1258 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
+          <t>CAR &amp; TANSPORTATION - Station wagon 7 seater diesel engine + driver + BBM, (Kendaraan Pajero DN 1904 RA Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
         </is>
       </c>
     </row>
@@ -2444,7 +2444,7 @@
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="H42" t="n">
         <v>1600000</v>
@@ -2480,7 +2480,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION - Station wagon 7 seater diesel engine + driver + BBM, (Kendaraan Innova DN 1257 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
+          <t>CAR &amp; TANSPORTATION - Double cabin 4x4, diesel engine + driver + BBM, (Kendaraan Hilux DN 1916 CH Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
         </is>
       </c>
     </row>
@@ -2493,7 +2493,7 @@
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -2506,7 +2506,7 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>4</v>
+        <v>120</v>
       </c>
       <c r="H43" t="n">
         <v>1600000</v>
@@ -2515,7 +2515,7 @@
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -2529,20 +2529,20 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION - Station wagon 7 seater diesel engine + driver + BBM, (Kendaraan Pajero DN 1904 RA Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
+          <t>CAR &amp; TANSPORTATION - Double cabin 4x4, diesel engine + driver + BBM, (Kendaraan Hilux DN 1917 CH Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>opname_026_BSS-JOB_WS_VIII_2026_4500011739</t>
+          <t>opname_032_BSS-JOB_WS_VIII_2026_4500011739</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -2551,24 +2551,24 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>120</v>
+        <v>300</v>
       </c>
       <c r="H44" t="n">
-        <v>1600000</v>
+        <v>250000</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>026/BSS-JOB/WS/VIII/2026</t>
+          <t>032/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -2578,20 +2578,20 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION - Double cabin 4x4, diesel engine + driver + BBM, (Kendaraan Hilux DN 1916 CH Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
+          <t>PERSONEL ON CALL - Helper Local (non Skilled) (Upah harian Flagman Periode 08 sd 30 Agustus 2026)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>opname_026_BSS-JOB_WS_VIII_2026_4500011739</t>
+          <t>opname_035_BSS-JOB_WS_X_2026_0</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -2600,41 +2600,41 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>120</v>
+        <v>1</v>
       </c>
       <c r="H45" t="n">
-        <v>1600000</v>
+        <v>151397500</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>026/BSS-JOB/WS/VIII/2026</t>
+          <t>035/BSS-JOB/WS/X/2026</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION - Double cabin 4x4, diesel engine + driver + BBM, (Kendaraan Hilux DN 1917 CH Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
+          <t>PROVISIONAL SUM - At Cost + Fee 15% (Akomodasi Personel JOB Tomori dan Serco di Hotel King Amear Periode 07 Agustus 2026 sd 10 September 2026, Sesuai rekap  dan Kwitansi terlampir)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>opname_032_BSS-JOB_WS_VIII_2026_4500011739</t>
+          <t>opname_036_BSS-JOB_WS_IX_2026_4500011739</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -2649,24 +2649,24 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>300</v>
+        <v>4600</v>
       </c>
       <c r="H46" t="n">
-        <v>250000</v>
+        <v>25000</v>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
+        <v>316.8</v>
       </c>
       <c r="J46" t="n">
-        <v>48</v>
+        <v>489.8</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>032/BSS-JOB/WS/VIII/2026</t>
+          <t>036/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -2676,14 +2676,14 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL - Helper Local (non Skilled) (Upah harian Flagman Periode 08 sd 30 Agustus 2026)</t>
+          <t>ADDITIONAL CAMP SERVICES - Laundry services (Loundry Untuk Personel JOB dan Serco di Hotel King Amear Periode tanggal 07 Agustus sd 10 September 2026)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>opname_035_BSS-JOB_WS_X_2026_0</t>
+          <t>opname_030_BSS-JOB_WS_VIII_2026_-</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -2698,14 +2698,14 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G47" t="n">
         <v>1</v>
       </c>
       <c r="H47" t="n">
-        <v>151397500</v>
+        <v>53762499.99999999</v>
       </c>
       <c r="I47" t="n">
         <v>0</v>
@@ -2715,24 +2715,24 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>035/BSS-JOB/WS/X/2026</t>
+          <t>030/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM - At Cost + Fee 15% (Akomodasi Personel JOB Tomori dan Serco di Hotel King Amear Periode 07 Agustus 2026 sd 10 September 2026, Sesuai rekap  dan Kwitansi terlampir)</t>
+          <t>PROVISIONAL SUM - At Cost + Fee 15% (Provsum Akomodasi untuk crew well services di penginapan Yellow Toili Periode tanggal 07 Agustus sd 31 Agustus 2026)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>opname_036_BSS-JOB_WS_IX_2026_4500011739</t>
+          <t>opname_005_BSS-JOB_WS_V_2026_-</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -2747,47 +2747,48 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>4600</v>
+        <v>16</v>
       </c>
       <c r="H48" t="n">
-        <v>25000</v>
+        <v>200000</v>
       </c>
       <c r="I48" t="n">
-        <v>316.8</v>
+        <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>489.8</v>
+        <v>16</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>036/BSS-JOB/WS/IX/2026</t>
+          <t>005/BSS-JOB/WS/V/2026</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES - Laundry services (Loundry Untuk Personel JOB dan Serco di Hotel King Amear Periode tanggal 07 Agustus sd 10 September 2026)</t>
+          <t>MOVING AIR FREIGHT TRANSPORT
+Jabodetabek - Luwuk/ Senoro atau sebaliknya (Pengiriman Sample air dari Lokasi Cluster B ke Jakarta)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>opname_030_BSS-JOB_WS_VIII_2026_-</t>
+          <t>opname_005_BSS-JOB_WS_V_2026_-</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2796,14 +2797,14 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G49" t="n">
         <v>1</v>
       </c>
       <c r="H49" t="n">
-        <v>53762499.99999999</v>
+        <v>250000</v>
       </c>
       <c r="I49" t="n">
         <v>0</v>
@@ -2813,7 +2814,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>030/BSS-JOB/WS/VIII/2026</t>
+          <t>005/BSS-JOB/WS/V/2026</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -2823,7 +2824,8 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM - At Cost + Fee 15% (Provsum Akomodasi untuk crew well services di penginapan Yellow Toili Periode tanggal 07 Agustus sd 31 Agustus 2026)</t>
+          <t>MOVING AIR FREIGHT TRANSPORT
+Jasa repacking for Airfreight, estimasi ukuran pallet 100x100x100 cm (Pembuatan Pallet Sample Air (packing Barang))</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2838,7 @@
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2849,16 +2851,16 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="H50" t="n">
-        <v>200000</v>
+        <v>1600000</v>
       </c>
       <c r="I50" t="n">
         <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -2872,8 +2874,8 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>MOVING AIR FREIGHT TRANSPORT
-Jabodetabek - Luwuk/ Senoro atau sebaliknya (Pengiriman Sample air dari Lokasi Cluster B ke Jakarta)</t>
+          <t>CAR &amp; TANSPORTATION
+Double cabin 4x4, diesel engine + driver + BBM, (Pickup Material di Luwuk tgl 18 Mei 2026 dari Lokasi ke Bandara)</t>
         </is>
       </c>
     </row>
@@ -2886,29 +2888,29 @@
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="n">
+        <v>4</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
         <v>2</v>
       </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>Luwuk</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="G51" t="n">
-        <v>1</v>
-      </c>
       <c r="H51" t="n">
-        <v>250000</v>
+        <v>350000</v>
       </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -2922,8 +2924,8 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>MOVING AIR FREIGHT TRANSPORT
-Jasa repacking for Airfreight, estimasi ukuran pallet 100x100x100 cm (Pembuatan Pallet Sample Air (packing Barang))</t>
+          <t>PERSONEL ON CALL
+Helper Local (Skilled) (Personel untuk pengurusan Barang di Luwuk dan Personel untuk pengurusan barang di Jakarta)</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2938,7 @@
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2952,7 +2954,7 @@
         <v>1</v>
       </c>
       <c r="H52" t="n">
-        <v>1600000</v>
+        <v>3250000</v>
       </c>
       <c r="I52" t="n">
         <v>0</v>
@@ -2972,21 +2974,21 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION
-Double cabin 4x4, diesel engine + driver + BBM, (Pickup Material di Luwuk tgl 18 Mei 2026 dari Lokasi ke Bandara)</t>
+          <t>ESTIMATED SUM
+Jasa Transportasi dari dan ke Bandara Jasa transportasi menggunakan Pickup Air Port Cengkareng ke Jabodetabek dan sebaliknya (Land transportasi dari bandara Cengkareng ke alamat penerima sample air PT.Haliburton)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>opname_005_BSS-JOB_WS_V_2026_-</t>
+          <t>opname_011_BSS-JOB_WS_VIII_2026_-</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2995,24 +2997,24 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H53" t="n">
-        <v>350000</v>
+        <v>1600000</v>
       </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>005/BSS-JOB/WS/V/2026</t>
+          <t>011/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3022,21 +3024,21 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL
-Helper Local (Skilled) (Personel untuk pengurusan Barang di Luwuk dan Personel untuk pengurusan barang di Jakarta)</t>
+          <t>CAR &amp; TANSPORTATION
+Double cabin 4x4, diesel engine + driver + BBM, (Pengambilan Material Pop Joint di Senoro 2 ke Luwuk)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>opname_005_BSS-JOB_WS_V_2026_-</t>
+          <t>opname_011_BSS-JOB_WS_VIII_2026_-</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -3045,14 +3047,14 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="G54" t="n">
         <v>1</v>
       </c>
       <c r="H54" t="n">
-        <v>3250000</v>
+        <v>250000</v>
       </c>
       <c r="I54" t="n">
         <v>0</v>
@@ -3062,7 +3064,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>005/BSS-JOB/WS/V/2026</t>
+          <t>011/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3072,8 +3074,8 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM
-Jasa Transportasi dari dan ke Bandara Jasa transportasi menggunakan Pickup Air Port Cengkareng ke Jabodetabek dan sebaliknya (Land transportasi dari bandara Cengkareng ke alamat penerima sample air PT.Haliburton)</t>
+          <t>MOVING AIR FREIGHT TRANSPORT
+Jasa repacking for Airfreight, estimasi ukuran pallet 100x100x100 cm (Pembuatan Pallet untuk Pop Joint)</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3088,7 @@
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -3099,16 +3101,16 @@
         </is>
       </c>
       <c r="G55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H55" t="n">
-        <v>1600000</v>
+        <v>350000</v>
       </c>
       <c r="I55" t="n">
         <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
@@ -3122,8 +3124,8 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION
-Double cabin 4x4, diesel engine + driver + BBM, (Pengambilan Material Pop Joint di Senoro 2 ke Luwuk)</t>
+          <t>PERSONEL ON CALL
+Helper Local (Skilled) (Personel Handling di Luwuk-Bandara 1 orang dan Jakarta-Bogor 1 orang)</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3138,7 @@
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -3149,16 +3151,16 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>1</v>
+        <v>105</v>
       </c>
       <c r="H56" t="n">
-        <v>250000</v>
+        <v>200000</v>
       </c>
       <c r="I56" t="n">
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>1</v>
+        <v>105</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -3173,7 +3175,7 @@
       <c r="M56" t="inlineStr">
         <is>
           <t>MOVING AIR FREIGHT TRANSPORT
-Jasa repacking for Airfreight, estimasi ukuran pallet 100x100x100 cm (Pembuatan Pallet untuk Pop Joint)</t>
+Jabodetabek - Luwuk/ Senoro atau sebaliknya (Cargo Barang   Air Freight Material Pop Joint yang dikirim)</t>
         </is>
       </c>
     </row>
@@ -3186,7 +3188,7 @@
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr"/>
       <c r="D57" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -3199,16 +3201,16 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H57" t="n">
-        <v>350000</v>
+        <v>3250000</v>
       </c>
       <c r="I57" t="n">
         <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
@@ -3222,21 +3224,21 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL
-Helper Local (Skilled) (Personel Handling di Luwuk-Bandara 1 orang dan Jakarta-Bogor 1 orang)</t>
+          <t>ESTIMATED SUM
+Jasa Transportasi dari dan ke Bandara Jasa transportasi menggunakan Pickup Air Port Cengkareng ke Jabodetabek dan sebaliknya (Pengiriman barang Pop Joint dari Bandara Cengkareng ke Bogor alamat  Lamda Multi Dinamika yard)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>opname_011_BSS-JOB_WS_VIII_2026_-</t>
+          <t>opname_034_BSS-JOB_WS_IX_2026_0</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -3245,85 +3247,85 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>105</v>
+        <v>6</v>
       </c>
       <c r="H58" t="n">
-        <v>200000</v>
+        <v>84500</v>
       </c>
       <c r="I58" t="n">
         <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>105</v>
+        <v>6</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>011/BSS-JOB/WS/VIII/2026</t>
+          <t>034/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>MOVING AIR FREIGHT TRANSPORT
-Jabodetabek - Luwuk/ Senoro atau sebaliknya (Cargo Barang   Air Freight Material Pop Joint yang dikirim)</t>
+          <t>ESTIMATED SUM
+Kopi Kapal Api 380 g (Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>opname_011_BSS-JOB_WS_VIII_2026_-</t>
+          <t>opname_034_BSS-JOB_WS_IX_2026_0</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="n">
+        <v>3</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
         <v>5</v>
       </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>Luwuk</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="G59" t="n">
-        <v>1</v>
-      </c>
       <c r="H59" t="n">
-        <v>3250000</v>
+        <v>26000</v>
       </c>
       <c r="I59" t="n">
         <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>011/BSS-JOB/WS/VIII/2026</t>
+          <t>034/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
           <t>ESTIMATED SUM
-Jasa Transportasi dari dan ke Bandara Jasa transportasi menggunakan Pickup Air Port Cengkareng ke Jabodetabek dan sebaliknya (Pengiriman barang Pop Joint dari Bandara Cengkareng ke Bogor alamat  Lamda Multi Dinamika yard)</t>
+Nescafe Classic renteng (Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -3336,7 +3338,7 @@
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -3349,16 +3351,16 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>6</v>
+        <v>72</v>
       </c>
       <c r="H60" t="n">
-        <v>84500</v>
+        <v>9750</v>
       </c>
       <c r="I60" t="n">
         <v>0</v>
       </c>
       <c r="J60" t="n">
-        <v>6</v>
+        <v>72</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
@@ -3373,7 +3375,7 @@
       <c r="M60" t="inlineStr">
         <is>
           <t>ESTIMATED SUM
-Kopi Kapal Api 380 g (Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026)</t>
+Pop Mie (Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3388,7 @@
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -3399,16 +3401,16 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H61" t="n">
-        <v>26000</v>
+        <v>19500</v>
       </c>
       <c r="I61" t="n">
         <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -3423,7 +3425,7 @@
       <c r="M61" t="inlineStr">
         <is>
           <t>ESTIMATED SUM
-Nescafe Classic renteng (Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026)</t>
+Chitato 68 g (Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -3436,7 +3438,7 @@
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -3452,7 +3454,7 @@
         <v>72</v>
       </c>
       <c r="H62" t="n">
-        <v>9750</v>
+        <v>13000</v>
       </c>
       <c r="I62" t="n">
         <v>0</v>
@@ -3473,7 +3475,7 @@
       <c r="M62" t="inlineStr">
         <is>
           <t>ESTIMATED SUM
-Pop Mie (Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026)</t>
+Pocari Sweat (Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -3486,7 +3488,7 @@
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -3499,16 +3501,16 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>10</v>
+        <v>72</v>
       </c>
       <c r="H63" t="n">
-        <v>19500</v>
+        <v>9750</v>
       </c>
       <c r="I63" t="n">
         <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>10</v>
+        <v>72</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
@@ -3523,7 +3525,7 @@
       <c r="M63" t="inlineStr">
         <is>
           <t>ESTIMATED SUM
-Chitato 68 g (Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026)</t>
+Teh Kotak (Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -3536,7 +3538,7 @@
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -3552,7 +3554,7 @@
         <v>72</v>
       </c>
       <c r="H64" t="n">
-        <v>13000</v>
+        <v>19500</v>
       </c>
       <c r="I64" t="n">
         <v>0</v>
@@ -3573,7 +3575,7 @@
       <c r="M64" t="inlineStr">
         <is>
           <t>ESTIMATED SUM
-Pocari Sweat (Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026)</t>
+Susu Beruang (Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -3586,7 +3588,7 @@
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -3599,16 +3601,16 @@
         </is>
       </c>
       <c r="G65" t="n">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="H65" t="n">
-        <v>9750</v>
+        <v>15600</v>
       </c>
       <c r="I65" t="n">
         <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
@@ -3623,7 +3625,7 @@
       <c r="M65" t="inlineStr">
         <is>
           <t>ESTIMATED SUM
-Teh Kotak (Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026)</t>
+Coffe Nescafe Kaleng 220 ml (Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3638,7 @@
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -3649,16 +3651,16 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>72</v>
+        <v>10</v>
       </c>
       <c r="H66" t="n">
-        <v>19500</v>
+        <v>32500</v>
       </c>
       <c r="I66" t="n">
         <v>0</v>
       </c>
       <c r="J66" t="n">
-        <v>72</v>
+        <v>10</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
@@ -3673,7 +3675,7 @@
       <c r="M66" t="inlineStr">
         <is>
           <t>ESTIMATED SUM
-Susu Beruang (Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026)</t>
+Roti Sari Roti Coklat (Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -3686,7 +3688,7 @@
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -3699,16 +3701,16 @@
         </is>
       </c>
       <c r="G67" t="n">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="H67" t="n">
-        <v>15600</v>
+        <v>32500</v>
       </c>
       <c r="I67" t="n">
         <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
@@ -3723,7 +3725,7 @@
       <c r="M67" t="inlineStr">
         <is>
           <t>ESTIMATED SUM
-Coffe Nescafe Kaleng 220 ml (Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026)</t>
+Roti Sari Roti Keju (Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -3736,7 +3738,7 @@
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -3773,20 +3775,20 @@
       <c r="M68" t="inlineStr">
         <is>
           <t>ESTIMATED SUM
-Roti Sari Roti Coklat (Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026)</t>
+Roti Tawar Sari Roti (Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>opname_034_BSS-JOB_WS_IX_2026_0</t>
+          <t>opname_037_BSS-JOB_WS_IX_2026_0</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -3799,7 +3801,7 @@
         </is>
       </c>
       <c r="G69" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H69" t="n">
         <v>32500</v>
@@ -3808,11 +3810,11 @@
         <v>0</v>
       </c>
       <c r="J69" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>034/BSS-JOB/WS/IX/2026</t>
+          <t>037/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -3823,20 +3825,20 @@
       <c r="M69" t="inlineStr">
         <is>
           <t>ESTIMATED SUM
-Roti Sari Roti Keju (Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026)</t>
+Indocafe Coffemix Renteng (Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>opname_034_BSS-JOB_WS_IX_2026_0</t>
+          <t>opname_037_BSS-JOB_WS_IX_2026_0</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr"/>
       <c r="D70" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -3849,20 +3851,20 @@
         </is>
       </c>
       <c r="G70" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H70" t="n">
-        <v>32500</v>
+        <v>84500</v>
       </c>
       <c r="I70" t="n">
         <v>0</v>
       </c>
       <c r="J70" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>034/BSS-JOB/WS/IX/2026</t>
+          <t>037/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -3873,7 +3875,7 @@
       <c r="M70" t="inlineStr">
         <is>
           <t>ESTIMATED SUM
-Roti Tawar Sari Roti (Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026)</t>
+Kopi Kapal Api 380 g (Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026)</t>
         </is>
       </c>
     </row>
@@ -3886,7 +3888,7 @@
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -3902,7 +3904,7 @@
         <v>5</v>
       </c>
       <c r="H71" t="n">
-        <v>32500</v>
+        <v>26000</v>
       </c>
       <c r="I71" t="n">
         <v>0</v>
@@ -3923,7 +3925,7 @@
       <c r="M71" t="inlineStr">
         <is>
           <t>ESTIMATED SUM
-Indocafe Coffemix Renteng (Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026)</t>
+Nescafe Classic renteng (Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026)</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3938,7 @@
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr"/>
       <c r="D72" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -3949,16 +3951,16 @@
         </is>
       </c>
       <c r="G72" t="n">
-        <v>6</v>
+        <v>72</v>
       </c>
       <c r="H72" t="n">
-        <v>84500</v>
+        <v>9750</v>
       </c>
       <c r="I72" t="n">
         <v>0</v>
       </c>
       <c r="J72" t="n">
-        <v>6</v>
+        <v>72</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
@@ -3973,7 +3975,7 @@
       <c r="M72" t="inlineStr">
         <is>
           <t>ESTIMATED SUM
-Kopi Kapal Api 380 g (Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026)</t>
+Pop Mie (Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026)</t>
         </is>
       </c>
     </row>
@@ -3986,7 +3988,7 @@
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr"/>
       <c r="D73" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -3999,16 +4001,16 @@
         </is>
       </c>
       <c r="G73" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H73" t="n">
-        <v>26000</v>
+        <v>19500</v>
       </c>
       <c r="I73" t="n">
         <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
@@ -4023,7 +4025,7 @@
       <c r="M73" t="inlineStr">
         <is>
           <t>ESTIMATED SUM
-Nescafe Classic renteng (Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026)</t>
+Chitato 68 g (Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026)</t>
         </is>
       </c>
     </row>
@@ -4036,7 +4038,7 @@
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="inlineStr"/>
       <c r="D74" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -4052,7 +4054,7 @@
         <v>72</v>
       </c>
       <c r="H74" t="n">
-        <v>9750</v>
+        <v>13000</v>
       </c>
       <c r="I74" t="n">
         <v>0</v>
@@ -4073,7 +4075,7 @@
       <c r="M74" t="inlineStr">
         <is>
           <t>ESTIMATED SUM
-Pop Mie (Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026)</t>
+Pocari Sweat (Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026)</t>
         </is>
       </c>
     </row>
@@ -4086,7 +4088,7 @@
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="inlineStr"/>
       <c r="D75" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -4099,16 +4101,16 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>10</v>
+        <v>72</v>
       </c>
       <c r="H75" t="n">
-        <v>19500</v>
+        <v>9750</v>
       </c>
       <c r="I75" t="n">
         <v>0</v>
       </c>
       <c r="J75" t="n">
-        <v>10</v>
+        <v>72</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
@@ -4123,7 +4125,7 @@
       <c r="M75" t="inlineStr">
         <is>
           <t>ESTIMATED SUM
-Chitato 68 g (Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026)</t>
+Teh Kotak (Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026)</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4138,7 @@
       <c r="B76" t="inlineStr"/>
       <c r="C76" t="inlineStr"/>
       <c r="D76" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -4152,7 +4154,7 @@
         <v>72</v>
       </c>
       <c r="H76" t="n">
-        <v>13000</v>
+        <v>19500</v>
       </c>
       <c r="I76" t="n">
         <v>0</v>
@@ -4173,7 +4175,7 @@
       <c r="M76" t="inlineStr">
         <is>
           <t>ESTIMATED SUM
-Pocari Sweat (Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026)</t>
+Susu Beruang (Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026)</t>
         </is>
       </c>
     </row>
@@ -4186,7 +4188,7 @@
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -4199,16 +4201,16 @@
         </is>
       </c>
       <c r="G77" t="n">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="H77" t="n">
-        <v>9750</v>
+        <v>15600</v>
       </c>
       <c r="I77" t="n">
         <v>0</v>
       </c>
       <c r="J77" t="n">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
@@ -4223,7 +4225,7 @@
       <c r="M77" t="inlineStr">
         <is>
           <t>ESTIMATED SUM
-Teh Kotak (Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026)</t>
+Coffe Nescafe Kaleng 220 ml (Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026)</t>
         </is>
       </c>
     </row>
@@ -4236,7 +4238,7 @@
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="inlineStr"/>
       <c r="D78" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -4249,16 +4251,16 @@
         </is>
       </c>
       <c r="G78" t="n">
-        <v>72</v>
+        <v>10</v>
       </c>
       <c r="H78" t="n">
-        <v>19500</v>
+        <v>32500</v>
       </c>
       <c r="I78" t="n">
         <v>0</v>
       </c>
       <c r="J78" t="n">
-        <v>72</v>
+        <v>10</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
@@ -4273,7 +4275,7 @@
       <c r="M78" t="inlineStr">
         <is>
           <t>ESTIMATED SUM
-Susu Beruang (Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026)</t>
+Roti Sari Roti Coklat (Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026)</t>
         </is>
       </c>
     </row>
@@ -4286,7 +4288,7 @@
       <c r="B79" t="inlineStr"/>
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -4299,16 +4301,16 @@
         </is>
       </c>
       <c r="G79" t="n">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="H79" t="n">
-        <v>15600</v>
+        <v>32500</v>
       </c>
       <c r="I79" t="n">
         <v>0</v>
       </c>
       <c r="J79" t="n">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
@@ -4323,7 +4325,7 @@
       <c r="M79" t="inlineStr">
         <is>
           <t>ESTIMATED SUM
-Coffe Nescafe Kaleng 220 ml (Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026)</t>
+Roti Sari Roti Keju (Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026)</t>
         </is>
       </c>
     </row>
@@ -4336,7 +4338,7 @@
       <c r="B80" t="inlineStr"/>
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -4373,20 +4375,20 @@
       <c r="M80" t="inlineStr">
         <is>
           <t>ESTIMATED SUM
-Roti Sari Roti Coklat (Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026)</t>
+Roti Tawar Sari Roti (Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026)</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>opname_037_BSS-JOB_WS_IX_2026_0</t>
+          <t>opname_040_BSS-JOB_WS_IX_2026_4500011739</t>
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
       <c r="C81" t="inlineStr"/>
       <c r="D81" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -4395,48 +4397,48 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G81" t="n">
-        <v>10</v>
+        <v>240</v>
       </c>
       <c r="H81" t="n">
-        <v>32500</v>
+        <v>750000</v>
       </c>
       <c r="I81" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="J81" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>037/BSS-JOB/WS/IX/2026</t>
+          <t>040/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM
-Roti Sari Roti Keju (Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026)</t>
+          <t>PERSONEL ON CALL
+Personnel GS in-charge di lokasi pemboran/ wellservices/ workover, personnel in charge (Personnel GS - Koordinator Lapangan atas nama Nur Afiata Periode 01 sd 30 September 2026)</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>opname_037_BSS-JOB_WS_IX_2026_0</t>
+          <t>opname_041_BSS-JOB_WS_IX_2026_4500011739</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
       <c r="C82" t="inlineStr"/>
       <c r="D82" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -4445,48 +4447,48 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G82" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="H82" t="n">
-        <v>32500</v>
+        <v>500000</v>
       </c>
       <c r="I82" t="n">
         <v>0</v>
       </c>
       <c r="J82" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>037/BSS-JOB/WS/IX/2026</t>
+          <t>041/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM
-Roti Tawar Sari Roti (Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026)</t>
+          <t>PERSONEL ON CALL
+Welder (GTAW) (Support Kegiatan Well Services di Senoro personel  Welder = HSE Officer ( Gusti Ngurah Dwipayana))</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>opname_040_BSS-JOB_WS_IX_2026_4500011739</t>
+          <t>opname_041_BSS-JOB_WS_IX_2026_4500011739</t>
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -4499,20 +4501,20 @@
         </is>
       </c>
       <c r="G83" t="n">
-        <v>240</v>
+        <v>30</v>
       </c>
       <c r="H83" t="n">
-        <v>750000</v>
+        <v>500000</v>
       </c>
       <c r="I83" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="J83" t="n">
         <v>30</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>040/BSS-JOB/WS/IX/2026</t>
+          <t>041/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -4523,7 +4525,7 @@
       <c r="M83" t="inlineStr">
         <is>
           <t>PERSONEL ON CALL
-Personnel GS in-charge di lokasi pemboran/ wellservices/ workover, personnel in charge (Personnel GS - Koordinator Lapangan atas nama Nur Afiata Periode 01 sd 30 September 2026)</t>
+Welder (GTAW) (Support Kegiatan Well Services di Senoro personel  Welder = Paramedic  ( Meliita Bella))</t>
         </is>
       </c>
     </row>
@@ -4536,7 +4538,7 @@
       <c r="B84" t="inlineStr"/>
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -4573,20 +4575,20 @@
       <c r="M84" t="inlineStr">
         <is>
           <t>PERSONEL ON CALL
-Welder (GTAW) (Support Kegiatan Well Services di Senoro personel  Welder = HSE Officer ( Gusti Ngurah Dwipayana))</t>
+Welder (GTAW) (Support Kegiatan Well Services di Senoro personel  Welder = Paramedic  ( Widiya Satuo))</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>opname_041_BSS-JOB_WS_IX_2026_4500011739</t>
+          <t>opname_042_BSS-JOB_WS_IX_2026_4500011739</t>
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="inlineStr"/>
       <c r="D85" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -4599,20 +4601,20 @@
         </is>
       </c>
       <c r="G85" t="n">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="H85" t="n">
-        <v>500000</v>
+        <v>750000</v>
       </c>
       <c r="I85" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J85" t="n">
         <v>30</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>041/BSS-JOB/WS/IX/2026</t>
+          <t>042/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -4623,20 +4625,20 @@
       <c r="M85" t="inlineStr">
         <is>
           <t>PERSONEL ON CALL
-Welder (GTAW) (Support Kegiatan Well Services di Senoro personel  Welder = Paramedic  ( Meliita Bella))</t>
+Operator Crane (Operator Crane Shift Siang atas Nama Wanhar Renaldi)</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>opname_041_BSS-JOB_WS_IX_2026_4500011739</t>
+          <t>opname_042_BSS-JOB_WS_IX_2026_4500011739</t>
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
       <c r="C86" t="inlineStr"/>
       <c r="D86" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -4649,20 +4651,20 @@
         </is>
       </c>
       <c r="G86" t="n">
+        <v>120</v>
+      </c>
+      <c r="H86" t="n">
+        <v>750000</v>
+      </c>
+      <c r="I86" t="n">
         <v>30</v>
-      </c>
-      <c r="H86" t="n">
-        <v>500000</v>
-      </c>
-      <c r="I86" t="n">
-        <v>0</v>
       </c>
       <c r="J86" t="n">
         <v>30</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>041/BSS-JOB/WS/IX/2026</t>
+          <t>042/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -4673,7 +4675,7 @@
       <c r="M86" t="inlineStr">
         <is>
           <t>PERSONEL ON CALL
-Welder (GTAW) (Support Kegiatan Well Services di Senoro personel  Welder = Paramedic  ( Widiya Satuo))</t>
+Operator Crane (Operator Crane Shift Malam atas Nama Ilsan Adjedar)</t>
         </is>
       </c>
     </row>
@@ -4686,7 +4688,7 @@
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -4702,10 +4704,10 @@
         <v>120</v>
       </c>
       <c r="H87" t="n">
-        <v>750000</v>
+        <v>650000</v>
       </c>
       <c r="I87" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="J87" t="n">
         <v>30</v>
@@ -4723,7 +4725,7 @@
       <c r="M87" t="inlineStr">
         <is>
           <t>PERSONEL ON CALL
-Operator Crane (Operator Crane Shift Siang atas Nama Wanhar Renaldi)</t>
+Rigger (RIgger Crane Shift Siang atas Nama Tison)</t>
         </is>
       </c>
     </row>
@@ -4736,7 +4738,7 @@
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="inlineStr"/>
       <c r="D88" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -4752,10 +4754,10 @@
         <v>120</v>
       </c>
       <c r="H88" t="n">
-        <v>750000</v>
+        <v>650000</v>
       </c>
       <c r="I88" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="J88" t="n">
         <v>30</v>
@@ -4773,7 +4775,7 @@
       <c r="M88" t="inlineStr">
         <is>
           <t>PERSONEL ON CALL
-Operator Crane (Operator Crane Shift Malam atas Nama Ilsan Adjedar)</t>
+Rigger (Rigger Crane Shift Malam atas Nama Agus Dg Mangata)</t>
         </is>
       </c>
     </row>
@@ -4786,7 +4788,7 @@
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="inlineStr"/>
       <c r="D89" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -4799,13 +4801,13 @@
         </is>
       </c>
       <c r="G89" t="n">
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="H89" t="n">
-        <v>650000</v>
+        <v>600000</v>
       </c>
       <c r="I89" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J89" t="n">
         <v>30</v>
@@ -4823,7 +4825,7 @@
       <c r="M89" t="inlineStr">
         <is>
           <t>PERSONEL ON CALL
-Rigger (RIgger Crane Shift Siang atas Nama Tison)</t>
+Mechanic/ Electrician (Operator Mesin Genset dan Ligting Tower Shift Siang atas nama Sugeng)</t>
         </is>
       </c>
     </row>
@@ -4836,7 +4838,7 @@
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="inlineStr"/>
       <c r="D90" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -4849,13 +4851,13 @@
         </is>
       </c>
       <c r="G90" t="n">
-        <v>120</v>
+        <v>240</v>
       </c>
       <c r="H90" t="n">
-        <v>650000</v>
+        <v>600000</v>
       </c>
       <c r="I90" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J90" t="n">
         <v>30</v>
@@ -4873,20 +4875,20 @@
       <c r="M90" t="inlineStr">
         <is>
           <t>PERSONEL ON CALL
-Rigger (Rigger Crane Shift Malam atas Nama Agus Dg Mangata)</t>
+Mechanic/ Electrician (Operator Mesin Genset dan Ligting Tower Shift Siang atas nama Ahmad Dhani)</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>opname_042_BSS-JOB_WS_IX_2026_4500011739</t>
+          <t>opname_043_BSS-JOB_WS_IX_2026_4500011739</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="inlineStr"/>
       <c r="D91" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -4899,20 +4901,20 @@
         </is>
       </c>
       <c r="G91" t="n">
-        <v>240</v>
+        <v>30</v>
       </c>
       <c r="H91" t="n">
-        <v>600000</v>
+        <v>500000</v>
       </c>
       <c r="I91" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="J91" t="n">
         <v>30</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>042/BSS-JOB/WS/IX/2026</t>
+          <t>043/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -4923,20 +4925,20 @@
       <c r="M91" t="inlineStr">
         <is>
           <t>PERSONEL ON CALL
-Mechanic/ Electrician (Operator Mesin Genset dan Ligting Tower Shift Siang atas nama Sugeng)</t>
+Operator Heavy Equipment (Vacuum Truck) (Driver Vacuum Truck atas nama Wijayanto Sucipto)</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>opname_042_BSS-JOB_WS_IX_2026_4500011739</t>
+          <t>opname_044_BSS-JOB_WS_IX_2026_4500011739</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="inlineStr"/>
       <c r="D92" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -4945,24 +4947,24 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G92" t="n">
-        <v>240</v>
+        <v>300</v>
       </c>
       <c r="H92" t="n">
-        <v>600000</v>
+        <v>250000</v>
       </c>
       <c r="I92" t="n">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="J92" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>042/BSS-JOB/WS/IX/2026</t>
+          <t>044/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -4973,14 +4975,14 @@
       <c r="M92" t="inlineStr">
         <is>
           <t>PERSONEL ON CALL
-Mechanic/ Electrician (Operator Mesin Genset dan Ligting Tower Shift Siang atas nama Ahmad Dhani)</t>
+Helper Local (non Skilled) (PERSONNEL ON-CALL Helper Local (non Skilled) Tenaga Flagman Periode tgl 4 sd 11 September 2026)</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>opname_043_BSS-JOB_WS_IX_2026_4500011739</t>
+          <t>opname_045_BSS-JOB_WS_IX_2026_4500011739</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
@@ -4999,20 +5001,20 @@
         </is>
       </c>
       <c r="G93" t="n">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="H93" t="n">
-        <v>500000</v>
+        <v>8500000</v>
       </c>
       <c r="I93" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J93" t="n">
         <v>30</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>043/BSS-JOB/WS/IX/2026</t>
+          <t>045/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -5022,21 +5024,21 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL
-Operator Heavy Equipment (Vacuum Truck) (Driver Vacuum Truck atas nama Wijayanto Sucipto)</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL
+crane min 70 ton, call out, (hanya unit) (Crane Sany 100 ton menggantikan Crane Tadano 70 ton yang rusak Operasi periode 01 sd 30 September 2026)</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>opname_044_BSS-JOB_WS_IX_2026_4500011739</t>
+          <t>opname_045_BSS-JOB_WS_IX_2026_4500011739</t>
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="inlineStr"/>
       <c r="D94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -5045,24 +5047,24 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G94" t="n">
-        <v>300</v>
+        <v>120</v>
       </c>
       <c r="H94" t="n">
-        <v>250000</v>
+        <v>2750000</v>
       </c>
       <c r="I94" t="n">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="J94" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>044/BSS-JOB/WS/IX/2026</t>
+          <t>045/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -5072,15 +5074,15 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL
-Helper Local (non Skilled) (PERSONNEL ON-CALL Helper Local (non Skilled) Tenaga Flagman Periode tgl 4 sd 11 September 2026)</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL
+Vacuum Truck , Call out, Cap  5000 ltr c/w vacuum pump &amp; acessories, call out, (hanya unit) (Vacuum Truck , Call out, Cap  5000 ltr  Operasi periode 01 sd 30 September 2026)</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>opname_045_BSS-JOB_WS_IX_2026_4500011739</t>
+          <t>opname_048_BSS-JOB_WS_IX_2026_4500011739</t>
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
@@ -5099,20 +5101,20 @@
         </is>
       </c>
       <c r="G95" t="n">
-        <v>120</v>
+        <v>4600</v>
       </c>
       <c r="H95" t="n">
-        <v>8500000</v>
+        <v>25000</v>
       </c>
       <c r="I95" t="n">
-        <v>16</v>
+        <v>806.6</v>
       </c>
       <c r="J95" t="n">
-        <v>30</v>
+        <v>458.4</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>045/BSS-JOB/WS/IX/2026</t>
+          <t>048/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -5122,21 +5124,21 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL
-crane min 70 ton, call out, (hanya unit) (Crane Sany 100 ton menggantikan Crane Tadano 70 ton yang rusak Operasi periode 01 sd 30 September 2026)</t>
+          <t>ADDITIONAL CAMP SERVICES
+Laundry services (Laundry services, Untuk Personel Serco Periode 01 sd 30 September 2026)</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>opname_045_BSS-JOB_WS_IX_2026_4500011739</t>
+          <t>opname_049_BSS-JOB_WS_IX_2026_-</t>
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="inlineStr"/>
       <c r="D96" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -5149,44 +5151,44 @@
         </is>
       </c>
       <c r="G96" t="n">
-        <v>120</v>
+        <v>2188</v>
       </c>
       <c r="H96" t="n">
-        <v>2750000</v>
+        <v>7500</v>
       </c>
       <c r="I96" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="J96" t="n">
-        <v>30</v>
+        <v>2188</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>045/BSS-JOB/WS/IX/2026</t>
+          <t>049/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL
-Vacuum Truck , Call out, Cap  5000 ltr c/w vacuum pump &amp; acessories, call out, (hanya unit) (Vacuum Truck , Call out, Cap  5000 ltr  Operasi periode 01 sd 30 September 2026)</t>
+          <t>ESTIMATED SUM
+Aqua 600 ml (Etimated SUM Penyediaan  Air Mineral Aqua 600 ml untuk Support Pekerjaan Well Services di Senoro Periode 01 sd 30 September 2026)</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>opname_048_BSS-JOB_WS_IX_2026_4500011739</t>
+          <t>opname_049_BSS-JOB_WS_IX_2026_-</t>
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="inlineStr"/>
       <c r="D97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -5199,38 +5201,38 @@
         </is>
       </c>
       <c r="G97" t="n">
-        <v>4600</v>
+        <v>15</v>
       </c>
       <c r="H97" t="n">
-        <v>25000</v>
+        <v>53300</v>
       </c>
       <c r="I97" t="n">
-        <v>806.6</v>
+        <v>0</v>
       </c>
       <c r="J97" t="n">
-        <v>458.4</v>
+        <v>15</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>048/BSS-JOB/WS/IX/2026</t>
+          <t>049/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES
-Laundry services (Laundry services, Untuk Personel Serco Periode 01 sd 30 September 2026)</t>
+          <t>ESTIMATED SUM
+Aqua Galon Segel (Etimated SUM Penyediaan  Air Mineral Aqua Galon Segel untuk Support Pekerjaan Well Services di Senoro Periode 01 sd 30 September 2026)</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>opname_049_BSS-JOB_WS_IX_2026_-</t>
+          <t>opname_050_BSS-JOB_WS_IX_2026_-</t>
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
@@ -5249,20 +5251,20 @@
         </is>
       </c>
       <c r="G98" t="n">
-        <v>2188</v>
+        <v>1</v>
       </c>
       <c r="H98" t="n">
-        <v>7500</v>
+        <v>69000000</v>
       </c>
       <c r="I98" t="n">
         <v>0</v>
       </c>
       <c r="J98" t="n">
-        <v>2188</v>
+        <v>1</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>049/BSS-JOB/WS/IX/2026</t>
+          <t>050/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -5272,21 +5274,21 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM
-Aqua 600 ml (Etimated SUM Penyediaan  Air Mineral Aqua 600 ml untuk Support Pekerjaan Well Services di Senoro Periode 01 sd 30 September 2026)</t>
+          <t>PROVISIONAL SUM
+At Cost + Fee 15% (Provisional SUM  Akomodasi untuk crew well services di penginapan Yellow Toili Periode 01 sd 30 September 2026)</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>opname_049_BSS-JOB_WS_IX_2026_-</t>
+          <t>opname_047_BSS-JOB_WS_IX_2026_4500011739</t>
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="inlineStr"/>
       <c r="D99" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -5299,44 +5301,44 @@
         </is>
       </c>
       <c r="G99" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="H99" t="n">
-        <v>53300</v>
+        <v>25000000</v>
       </c>
       <c r="I99" t="n">
-        <v>0</v>
+        <v>0.48</v>
       </c>
       <c r="J99" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>049/BSS-JOB/WS/IX/2026</t>
+          <t>047/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM
-Aqua Galon Segel (Etimated SUM Penyediaan  Air Mineral Aqua Galon Segel untuk Support Pekerjaan Well Services di Senoro Periode 01 sd 30 September 2026)</t>
+          <t>ADDITIONAL CAMP SERVICES
+Portacamp - Office Camp,  ukuran 40 FT (Support Well Services Senoro Periode 01 sd 30 September 2026)</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>opname_050_BSS-JOB_WS_IX_2026_-</t>
+          <t>opname_047_BSS-JOB_WS_IX_2026_4500011739</t>
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
       <c r="C100" t="inlineStr"/>
       <c r="D100" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -5349,31 +5351,31 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H100" t="n">
-        <v>69000000</v>
+        <v>17500000</v>
       </c>
       <c r="I100" t="n">
-        <v>0</v>
+        <v>0.48</v>
       </c>
       <c r="J100" t="n">
         <v>1</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>050/BSS-JOB/WS/IX/2026</t>
+          <t>047/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM
-At Cost + Fee 15% (Provisional SUM  Akomodasi untuk crew well services di penginapan Yellow Toili Periode 01 sd 30 September 2026)</t>
+          <t>ADDITIONAL CAMP SERVICES
+Portacamp - Living camp,ukuran 40FT (4 sleepers) (Support Well Services Senoro Periode 01 sd 30 September 2026)</t>
         </is>
       </c>
     </row>
@@ -5386,7 +5388,7 @@
       <c r="B101" t="inlineStr"/>
       <c r="C101" t="inlineStr"/>
       <c r="D101" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -5402,10 +5404,10 @@
         <v>4</v>
       </c>
       <c r="H101" t="n">
-        <v>25000000</v>
+        <v>60000000</v>
       </c>
       <c r="I101" t="n">
-        <v>0.48</v>
+        <v>0.74</v>
       </c>
       <c r="J101" t="n">
         <v>1</v>
@@ -5422,8 +5424,8 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES
-Portacamp - Office Camp,  ukuran 40 FT (Support Well Services Senoro Periode 01 sd 30 September 2026)</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL
+Genset, cap min 80 KVA, silent type, include maintenance (Operasi Shift Siang Periode 01 sd 30 September 2026)</t>
         </is>
       </c>
     </row>
@@ -5436,7 +5438,7 @@
       <c r="B102" t="inlineStr"/>
       <c r="C102" t="inlineStr"/>
       <c r="D102" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -5452,10 +5454,10 @@
         <v>4</v>
       </c>
       <c r="H102" t="n">
-        <v>17500000</v>
+        <v>60000000</v>
       </c>
       <c r="I102" t="n">
-        <v>0.48</v>
+        <v>0.74</v>
       </c>
       <c r="J102" t="n">
         <v>1</v>
@@ -5472,8 +5474,8 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES
-Portacamp - Living camp,ukuran 40FT (4 sleepers) (Support Well Services Senoro Periode 01 sd 30 September 2026)</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL
+Genset, cap min 80 KVA, silent type, include maintenance (Operasi Shift Malam Periode 01 sd 30 September 2026)</t>
         </is>
       </c>
     </row>
@@ -5486,7 +5488,7 @@
       <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr"/>
       <c r="D103" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -5502,7 +5504,7 @@
         <v>4</v>
       </c>
       <c r="H103" t="n">
-        <v>60000000</v>
+        <v>15000000</v>
       </c>
       <c r="I103" t="n">
         <v>0.74</v>
@@ -5523,7 +5525,7 @@
       <c r="M103" t="inlineStr">
         <is>
           <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL
-Genset, cap min 80 KVA, silent type, include maintenance (Operasi Shift Siang Periode 01 sd 30 September 2026)</t>
+Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories (Operasi Shift Malam Periode 01 sd 30 September 2026)</t>
         </is>
       </c>
     </row>
@@ -5536,7 +5538,7 @@
       <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr"/>
       <c r="D104" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -5552,7 +5554,7 @@
         <v>4</v>
       </c>
       <c r="H104" t="n">
-        <v>60000000</v>
+        <v>15000000</v>
       </c>
       <c r="I104" t="n">
         <v>0.74</v>
@@ -5573,20 +5575,20 @@
       <c r="M104" t="inlineStr">
         <is>
           <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL
-Genset, cap min 80 KVA, silent type, include maintenance (Operasi Shift Malam Periode 01 sd 30 September 2026)</t>
+Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories (Operasi Shift Malam Periode 01 sd 30 September 2026)</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>opname_047_BSS-JOB_WS_IX_2026_4500011739</t>
+          <t>opname_039_BSS-JOB_WS_VIII_2026_4500011739</t>
         </is>
       </c>
       <c r="B105" t="inlineStr"/>
       <c r="C105" t="inlineStr"/>
       <c r="D105" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -5595,24 +5597,24 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G105" t="n">
         <v>4</v>
       </c>
       <c r="H105" t="n">
-        <v>15000000</v>
+        <v>7500000</v>
       </c>
       <c r="I105" t="n">
-        <v>0.74</v>
+        <v>0</v>
       </c>
       <c r="J105" t="n">
         <v>1</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>047/BSS-JOB/WS/IX/2026</t>
+          <t>039/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -5623,20 +5625,20 @@
       <c r="M105" t="inlineStr">
         <is>
           <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL
-Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories (Operasi Shift Malam Periode 01 sd 30 September 2026)</t>
+Mobilization/ Demobilization of Rental Equipments (Genset/ Air Compressor/ Light Tower/ Fuel Tank, etc) to/from Company Wellsite/ Contractor base (Tronton Muat Mesin Genset dan Light tower dari Lamo ke Cluster B)</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>opname_047_BSS-JOB_WS_IX_2026_4500011739</t>
+          <t>opname_039_BSS-JOB_WS_VIII_2026_4500011739</t>
         </is>
       </c>
       <c r="B106" t="inlineStr"/>
       <c r="C106" t="inlineStr"/>
       <c r="D106" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -5645,24 +5647,24 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G106" t="n">
         <v>4</v>
       </c>
       <c r="H106" t="n">
-        <v>15000000</v>
+        <v>7500000</v>
       </c>
       <c r="I106" t="n">
-        <v>0.74</v>
+        <v>0</v>
       </c>
       <c r="J106" t="n">
         <v>1</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>047/BSS-JOB/WS/IX/2026</t>
+          <t>039/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -5673,14 +5675,14 @@
       <c r="M106" t="inlineStr">
         <is>
           <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL
-Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories (Operasi Shift Malam Periode 01 sd 30 September 2026)</t>
+Mobilization/ Demobilization of Rental Equipments (Genset/ Air Compressor/ Light Tower/ Fuel Tank, etc) to/from Company Wellsite/ Contractor base (Tronton Muat  Tenda, Meja, Kursi dan Counter Weight dari Lamo ke Cluster B)</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>opname_039_BSS-JOB_WS_VIII_2026_4500011739</t>
+          <t>opname_039A_BSS-JOB_WS_VIII_2026_-</t>
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
@@ -5699,10 +5701,10 @@
         </is>
       </c>
       <c r="G107" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H107" t="n">
-        <v>7500000</v>
+        <v>7600000</v>
       </c>
       <c r="I107" t="n">
         <v>0</v>
@@ -5712,25 +5714,25 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>039/BSS-JOB/WS/VIII/2026</t>
+          <t>039A/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL
-Mobilization/ Demobilization of Rental Equipments (Genset/ Air Compressor/ Light Tower/ Fuel Tank, etc) to/from Company Wellsite/ Contractor base (Tronton Muat Mesin Genset dan Light tower dari Lamo ke Cluster B)</t>
+          <t>ADDITIONAL CAMP SERVICES
+Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base (Trailler 40 feet Mobilisasi Portacamp Office dari Lamo ke Cluster B)</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>opname_039_BSS-JOB_WS_VIII_2026_4500011739</t>
+          <t>opname_039A_BSS-JOB_WS_VIII_2026_-</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
@@ -5749,10 +5751,10 @@
         </is>
       </c>
       <c r="G108" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H108" t="n">
-        <v>7500000</v>
+        <v>7600000</v>
       </c>
       <c r="I108" t="n">
         <v>0</v>
@@ -5762,25 +5764,25 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>039/BSS-JOB/WS/VIII/2026</t>
+          <t>039A/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL
-Mobilization/ Demobilization of Rental Equipments (Genset/ Air Compressor/ Light Tower/ Fuel Tank, etc) to/from Company Wellsite/ Contractor base (Tronton Muat  Tenda, Meja, Kursi dan Counter Weight dari Lamo ke Cluster B)</t>
+          <t>ADDITIONAL CAMP SERVICES
+Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base (Trailler 40 feet Mobilisasi Portacamp Sleeper  dari Lamo ke Cluster B)</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>opname_039A_BSS-JOB_WS_VIII_2026_-</t>
+          <t>opname_039B_BSS-JOB_WS_VIII_2026_-</t>
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
@@ -5795,14 +5797,14 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G109" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H109" t="n">
-        <v>7600000</v>
+        <v>5290000</v>
       </c>
       <c r="I109" t="n">
         <v>0</v>
@@ -5812,7 +5814,7 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>039A/BSS-JOB/WS/VIII/2026</t>
+          <t>039B/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -5822,15 +5824,15 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES
-Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base (Trailler 40 feet Mobilisasi Portacamp Office dari Lamo ke Cluster B)</t>
+          <t>LAND TRANSPORTATION
+trailer 20" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver (Tronton DN 8639 CH muat tenda, meja - kursi dan Counter Weight)</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>opname_039A_BSS-JOB_WS_VIII_2026_-</t>
+          <t>opname_039B_BSS-JOB_WS_VIII_2026_-</t>
         </is>
       </c>
       <c r="B110" t="inlineStr"/>
@@ -5845,14 +5847,14 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G110" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H110" t="n">
-        <v>7600000</v>
+        <v>5290000</v>
       </c>
       <c r="I110" t="n">
         <v>0</v>
@@ -5862,7 +5864,7 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>039A/BSS-JOB/WS/VIII/2026</t>
+          <t>039B/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -5872,8 +5874,8 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES
-Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base (Trailler 40 feet Mobilisasi Portacamp Sleeper  dari Lamo ke Cluster B)</t>
+          <t>LAND TRANSPORTATION
+trailer 20" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver (Tronton DN 8140 CA Muat Mesin Genset 2 unit, Lighting tower 2 unit dan panel Listrik)</t>
         </is>
       </c>
     </row>
@@ -5886,7 +5888,7 @@
       <c r="B111" t="inlineStr"/>
       <c r="C111" t="inlineStr"/>
       <c r="D111" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -5902,7 +5904,7 @@
         <v>1</v>
       </c>
       <c r="H111" t="n">
-        <v>5290000</v>
+        <v>6555000</v>
       </c>
       <c r="I111" t="n">
         <v>0</v>
@@ -5923,7 +5925,7 @@
       <c r="M111" t="inlineStr">
         <is>
           <t>LAND TRANSPORTATION
-trailer 20" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver (Tronton DN 8639 CH muat tenda, meja - kursi dan Counter Weight)</t>
+trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver (Trailler 40 feet DN 8785 RA muat equipment well services)</t>
         </is>
       </c>
     </row>
@@ -5936,7 +5938,7 @@
       <c r="B112" t="inlineStr"/>
       <c r="C112" t="inlineStr"/>
       <c r="D112" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -5952,7 +5954,7 @@
         <v>1</v>
       </c>
       <c r="H112" t="n">
-        <v>5290000</v>
+        <v>6555000</v>
       </c>
       <c r="I112" t="n">
         <v>0</v>
@@ -5973,7 +5975,7 @@
       <c r="M112" t="inlineStr">
         <is>
           <t>LAND TRANSPORTATION
-trailer 20" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver (Tronton DN 8140 CA Muat Mesin Genset 2 unit, Lighting tower 2 unit dan panel Listrik)</t>
+trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver (Trailler 40 feet DN 8950 RA muat Portacamp sleeper 40 feet)</t>
         </is>
       </c>
     </row>
@@ -5986,7 +5988,7 @@
       <c r="B113" t="inlineStr"/>
       <c r="C113" t="inlineStr"/>
       <c r="D113" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -6023,20 +6025,20 @@
       <c r="M113" t="inlineStr">
         <is>
           <t>LAND TRANSPORTATION
-trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver (Trailler 40 feet DN 8785 RA muat equipment well services)</t>
+trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver (Trailler 40 feet DN 8959 RA muat Portacamp Office 40 feet)</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>opname_039B_BSS-JOB_WS_VIII_2026_-</t>
+          <t>opname_039C_BSS-JOB_WS_VIII_2026_-</t>
         </is>
       </c>
       <c r="B114" t="inlineStr"/>
       <c r="C114" t="inlineStr"/>
       <c r="D114" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -6045,14 +6047,14 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G114" t="n">
         <v>1</v>
       </c>
       <c r="H114" t="n">
-        <v>6555000</v>
+        <v>5290000</v>
       </c>
       <c r="I114" t="n">
         <v>0</v>
@@ -6062,7 +6064,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>039B/BSS-JOB/WS/VIII/2026</t>
+          <t>039C/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -6073,20 +6075,20 @@
       <c r="M114" t="inlineStr">
         <is>
           <t>LAND TRANSPORTATION
-trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver (Trailler 40 feet DN 8950 RA muat Portacamp sleeper 40 feet)</t>
+trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver (tronton DN 8639 CH muat tenda, meja-kursi, Counter Weight ABC)</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>opname_039B_BSS-JOB_WS_VIII_2026_-</t>
+          <t>opname_039C_BSS-JOB_WS_VIII_2026_-</t>
         </is>
       </c>
       <c r="B115" t="inlineStr"/>
       <c r="C115" t="inlineStr"/>
       <c r="D115" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -6095,14 +6097,14 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G115" t="n">
         <v>1</v>
       </c>
       <c r="H115" t="n">
-        <v>6555000</v>
+        <v>5290000</v>
       </c>
       <c r="I115" t="n">
         <v>0</v>
@@ -6112,7 +6114,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>039B/BSS-JOB/WS/VIII/2026</t>
+          <t>039C/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -6123,7 +6125,7 @@
       <c r="M115" t="inlineStr">
         <is>
           <t>LAND TRANSPORTATION
-trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver (Trailler 40 feet DN 8959 RA muat Portacamp Office 40 feet)</t>
+trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver (Tronton DN 8140 CA Muat Mesin Genset 2 unit, Lighting tower 2 unit dan panel Listrik)</t>
         </is>
       </c>
     </row>
@@ -6136,7 +6138,7 @@
       <c r="B116" t="inlineStr"/>
       <c r="C116" t="inlineStr"/>
       <c r="D116" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -6152,7 +6154,7 @@
         <v>1</v>
       </c>
       <c r="H116" t="n">
-        <v>5290000</v>
+        <v>6555000</v>
       </c>
       <c r="I116" t="n">
         <v>0</v>
@@ -6173,7 +6175,7 @@
       <c r="M116" t="inlineStr">
         <is>
           <t>LAND TRANSPORTATION
-trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver (tronton DN 8639 CH muat tenda, meja-kursi, Counter Weight ABC)</t>
+trailer 40" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver (Trailler 40 feet DN 8950 RA muat Equipment Well Services)</t>
         </is>
       </c>
     </row>
@@ -6186,7 +6188,7 @@
       <c r="B117" t="inlineStr"/>
       <c r="C117" t="inlineStr"/>
       <c r="D117" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -6202,7 +6204,7 @@
         <v>1</v>
       </c>
       <c r="H117" t="n">
-        <v>5290000</v>
+        <v>7600000</v>
       </c>
       <c r="I117" t="n">
         <v>0</v>
@@ -6222,8 +6224,8 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>LAND TRANSPORTATION
-trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver (Tronton DN 8140 CA Muat Mesin Genset 2 unit, Lighting tower 2 unit dan panel Listrik)</t>
+          <t>ADDITIONAL CAMP SERVICES
+Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base (Trailler 40 feet DN 8785 RA Demobilisasi portacamp Sleeper 40 feet  dari Senoro 2 ke Lamo)</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6238,7 @@
       <c r="B118" t="inlineStr"/>
       <c r="C118" t="inlineStr"/>
       <c r="D118" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -6252,7 +6254,7 @@
         <v>1</v>
       </c>
       <c r="H118" t="n">
-        <v>6555000</v>
+        <v>7600000</v>
       </c>
       <c r="I118" t="n">
         <v>0</v>
@@ -6272,21 +6274,21 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>LAND TRANSPORTATION
-trailer 40" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver (Trailler 40 feet DN 8950 RA muat Equipment Well Services)</t>
+          <t>ADDITIONAL CAMP SERVICES
+Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base (Trailler 40 feet DN 8959 RA  Demobilisasi portacamp Office 40 feet  dari Senoro 2 ke Lamo)</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>opname_039C_BSS-JOB_WS_VIII_2026_-</t>
+          <t>opname_039D_BSS-JOB_WS_VIII_2026_-</t>
         </is>
       </c>
       <c r="B119" t="inlineStr"/>
       <c r="C119" t="inlineStr"/>
       <c r="D119" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -6295,7 +6297,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -6312,7 +6314,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>039C/BSS-JOB/WS/VIII/2026</t>
+          <t>039D/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -6323,20 +6325,20 @@
       <c r="M119" t="inlineStr">
         <is>
           <t>ADDITIONAL CAMP SERVICES
-Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base (Trailler 40 feet DN 8785 RA Demobilisasi portacamp Sleeper 40 feet  dari Senoro 2 ke Lamo)</t>
+Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base (Trailler 40 feet DN 8785 RA mobilisasi Portacamp office dari Lamo ke Senoro)</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>opname_039C_BSS-JOB_WS_VIII_2026_-</t>
+          <t>opname_039D_BSS-JOB_WS_VIII_2026_-</t>
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
       <c r="C120" t="inlineStr"/>
       <c r="D120" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -6345,7 +6347,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -6362,7 +6364,7 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>039C/BSS-JOB/WS/VIII/2026</t>
+          <t>039D/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -6373,7 +6375,7 @@
       <c r="M120" t="inlineStr">
         <is>
           <t>ADDITIONAL CAMP SERVICES
-Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base (Trailler 40 feet DN 8959 RA  Demobilisasi portacamp Office 40 feet  dari Senoro 2 ke Lamo)</t>
+Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base (Trailler 40 feet DN 8959 RA mobilisasi Portacamp Sleeper  dari Lamo ke Senoro)</t>
         </is>
       </c>
     </row>
@@ -6386,7 +6388,7 @@
       <c r="B121" t="inlineStr"/>
       <c r="C121" t="inlineStr"/>
       <c r="D121" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -6402,7 +6404,7 @@
         <v>1</v>
       </c>
       <c r="H121" t="n">
-        <v>7600000</v>
+        <v>5520000</v>
       </c>
       <c r="I121" t="n">
         <v>0</v>
@@ -6422,21 +6424,21 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES
-Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base (Trailler 40 feet DN 8785 RA mobilisasi Portacamp office dari Lamo ke Senoro)</t>
+          <t>LAND TRANSPORTATION
+trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Contractor's alternative jetty atau sebaliknya c/w BBM &amp; driver (Tronton 20 feet DN 9639 CH dari Lamo ke Senoro 2 pindahkan Barang TGE di lokasi senoro 2)</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>opname_039D_BSS-JOB_WS_VIII_2026_-</t>
+          <t>opname_046_BSS-JOB_WS_IX_2026_4500011739</t>
         </is>
       </c>
       <c r="B122" t="inlineStr"/>
       <c r="C122" t="inlineStr"/>
       <c r="D122" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -6445,48 +6447,48 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G122" t="n">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="H122" t="n">
-        <v>7600000</v>
+        <v>1600000</v>
       </c>
       <c r="I122" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J122" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>039D/BSS-JOB/WS/VIII/2026</t>
+          <t>046/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES
-Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base (Trailler 40 feet DN 8959 RA mobilisasi Portacamp Sleeper  dari Lamo ke Senoro)</t>
+          <t>CAR &amp; TANSPORTATION
+Station wagon 7 seater diesel engine + driver + BBM, (Kendaraan Inova DN 1259 CL  Support Well Services Periode tanggal 01 sd 30 September 2026)</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>opname_039D_BSS-JOB_WS_VIII_2026_-</t>
+          <t>opname_046_BSS-JOB_WS_IX_2026_4500011739</t>
         </is>
       </c>
       <c r="B123" t="inlineStr"/>
       <c r="C123" t="inlineStr"/>
       <c r="D123" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -6495,48 +6497,48 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G123" t="n">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="H123" t="n">
-        <v>5520000</v>
+        <v>1600000</v>
       </c>
       <c r="I123" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J123" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>039D/BSS-JOB/WS/VIII/2026</t>
+          <t>046/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>LAND TRANSPORTATION
-trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Contractor's alternative jetty atau sebaliknya c/w BBM &amp; driver (Tronton 20 feet DN 9639 CH dari Lamo ke Senoro 2 pindahkan Barang TGE di lokasi senoro 2)</t>
+          <t>CAR &amp; TANSPORTATION
+Station wagon 7 seater diesel engine + driver + BBM, (Kendaraan Inova DN 1257 CL  Support Well Services Periode tanggal 01 sd 30 September 2026)</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>opname_038_BSS-JOB_WS_IX_2026_4500011739</t>
+          <t>opname_046_BSS-JOB_WS_IX_2026_4500011739</t>
         </is>
       </c>
       <c r="B124" t="inlineStr"/>
       <c r="C124" t="inlineStr"/>
       <c r="D124" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -6549,20 +6551,20 @@
         </is>
       </c>
       <c r="G124" t="n">
-        <v>18300</v>
+        <v>120</v>
       </c>
       <c r="H124" t="n">
-        <v>65000</v>
+        <v>1600000</v>
       </c>
       <c r="I124" t="n">
-        <v>2578</v>
+        <v>19</v>
       </c>
       <c r="J124" t="n">
-        <v>3195</v>
+        <v>4</v>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>038/BSS-JOB/WS/IX/2026</t>
+          <t>046/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -6572,21 +6574,21 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES
-Food &amp; beverage, main course (DDITIONAL CAMP SERVICES, Operational Consumption)</t>
+          <t>CAR &amp; TANSPORTATION
+Station wagon 7 seater diesel engine + driver + BBM, (Kendaraan Inova DN 1258 CL  Support Well Services Periode tanggal 27 sd 30 September 2026)</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>opname_038_BSS-JOB_WS_IX_2026_4500011739</t>
+          <t>opname_046_BSS-JOB_WS_IX_2026_4500011739</t>
         </is>
       </c>
       <c r="B125" t="inlineStr"/>
       <c r="C125" t="inlineStr"/>
       <c r="D125" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -6599,20 +6601,20 @@
         </is>
       </c>
       <c r="G125" t="n">
-        <v>9200</v>
+        <v>120</v>
       </c>
       <c r="H125" t="n">
-        <v>33000</v>
+        <v>1600000</v>
       </c>
       <c r="I125" t="n">
-        <v>1157</v>
+        <v>26</v>
       </c>
       <c r="J125" t="n">
-        <v>1488</v>
+        <v>30</v>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>038/BSS-JOB/WS/IX/2026</t>
+          <t>046/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -6622,8 +6624,8 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES
-Food &amp; beverage, snack coffee/ tea &amp; desert (ADDITIONAL CAMP SERVICES, Operational side consumption)</t>
+          <t>CAR &amp; TANSPORTATION
+Double cabin 4x4, diesel engine + driver + BBM, (Kendaraan Double Cabin Hilux DN 8916 CH  Support Well Services Periode tanggal 01 sd 30 September 2026)</t>
         </is>
       </c>
     </row>
@@ -6636,7 +6638,7 @@
       <c r="B126" t="inlineStr"/>
       <c r="C126" t="inlineStr"/>
       <c r="D126" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -6655,7 +6657,7 @@
         <v>1600000</v>
       </c>
       <c r="I126" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J126" t="n">
         <v>30</v>
@@ -6673,20 +6675,20 @@
       <c r="M126" t="inlineStr">
         <is>
           <t>CAR &amp; TANSPORTATION
-Station wagon 7 seater diesel engine + driver + BBM, (Kendaraan Inova DN 1259 CL  Support Well Services Periode tanggal 01 sd 30 September 2026)</t>
+Double cabin 4x4, diesel engine + driver + BBM, (Kendaraan Double Cabin Hilux DN 8917 CH  Support Well Services Periode tanggal 01 sd 30 September 2026)</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>opname_046_BSS-JOB_WS_IX_2026_4500011739</t>
+          <t>opname_051_BSS-JOB_WS_VIII_2026_-</t>
         </is>
       </c>
       <c r="B127" t="inlineStr"/>
       <c r="C127" t="inlineStr"/>
       <c r="D127" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -6695,48 +6697,48 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G127" t="n">
-        <v>120</v>
+        <v>1</v>
       </c>
       <c r="H127" t="n">
-        <v>1600000</v>
+        <v>1725000</v>
       </c>
       <c r="I127" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="J127" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>046/BSS-JOB/WS/IX/2026</t>
+          <t>051/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION
-Station wagon 7 seater diesel engine + driver + BBM, (Kendaraan Inova DN 1257 CL  Support Well Services Periode tanggal 01 sd 30 September 2026)</t>
+          <t>PROVISIONAL SUM
+At Cost + Fee 15% (Provisional SUM  Pengurusan Dokumen Surat Persetujuan Pengeluaran Barang (SPPB) 3 colly di Pelabuhan Batam)</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>opname_046_BSS-JOB_WS_IX_2026_4500011739</t>
+          <t>opname_052_BSS-JOB_WS_IX_2026_-</t>
         </is>
       </c>
       <c r="B128" t="inlineStr"/>
       <c r="C128" t="inlineStr"/>
       <c r="D128" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
@@ -6745,48 +6747,48 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G128" t="n">
-        <v>120</v>
+        <v>1</v>
       </c>
       <c r="H128" t="n">
-        <v>1600000</v>
+        <v>8625000</v>
       </c>
       <c r="I128" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J128" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>046/BSS-JOB/WS/IX/2026</t>
+          <t>052/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION
-Station wagon 7 seater diesel engine + driver + BBM, (Kendaraan Inova DN 1258 CL  Support Well Services Periode tanggal 27 sd 30 September 2026)</t>
+          <t>PROVISIONAL SUM
+At Cost + Fee 15% (Provisional SUM  Pengiriman Barang  Pup Joint dari Pertamina EP Cepu ke Lamda Multi Dinamika Yard di Bogor)</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>opname_046_BSS-JOB_WS_IX_2026_4500011739</t>
+          <t>opname_002_BSS-JOB_WS_I_2026_4500011794</t>
         </is>
       </c>
       <c r="B129" t="inlineStr"/>
       <c r="C129" t="inlineStr"/>
       <c r="D129" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -6795,48 +6797,48 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="G129" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="H129" t="n">
-        <v>1600000</v>
+        <v>11500</v>
       </c>
       <c r="I129" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J129" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>046/BSS-JOB/WS/IX/2026</t>
+          <t>002/BSS-JOB/WS/I/2026</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>4500011794</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION
-Double cabin 4x4, diesel engine + driver + BBM, (Kendaraan Double Cabin Hilux DN 8916 CH  Support Well Services Periode tanggal 01 sd 30 September 2026)</t>
+          <t>PROVISIONAL SUM
+At Cost + Fee 15% (Garam Kasar Untuk Pekerjaan Sealant di Cluster B)</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>opname_046_BSS-JOB_WS_IX_2026_4500011739</t>
+          <t>opname_002_BSS-JOB_WS_I_2026_4500011794</t>
         </is>
       </c>
       <c r="B130" t="inlineStr"/>
       <c r="C130" t="inlineStr"/>
       <c r="D130" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -6845,42 +6847,42 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="G130" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="H130" t="n">
-        <v>1600000</v>
+        <v>17250</v>
       </c>
       <c r="I130" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="J130" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>046/BSS-JOB/WS/IX/2026</t>
+          <t>002/BSS-JOB/WS/I/2026</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>4500011794</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION
-Double cabin 4x4, diesel engine + driver + BBM, (Kendaraan Double Cabin Hilux DN 8917 CH  Support Well Services Periode tanggal 01 sd 30 September 2026)</t>
+          <t>PROVISIONAL SUM
+At Cost + Fee 15% (Belerang Untuk Pekerjaan Sealant di Cluster B)</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>opname_051_BSS-JOB_WS_VIII_2026_-</t>
+          <t>opname_021_BSS-JOB_WS_IX_2026_4500011795</t>
         </is>
       </c>
       <c r="B131" t="inlineStr"/>
@@ -6895,48 +6897,48 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G131" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H131" t="n">
-        <v>1725000</v>
+        <v>201250</v>
       </c>
       <c r="I131" t="n">
         <v>0</v>
       </c>
       <c r="J131" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>051/BSS-JOB/WS/VIII/2026</t>
+          <t>021/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011795</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
         <is>
           <t>PROVISIONAL SUM
-At Cost + Fee 15% (Provisional SUM  Pengurusan Dokumen Surat Persetujuan Pengeluaran Barang (SPPB) 3 colly di Pelabuhan Batam)</t>
+At Cost + Fee 15% (Kontainer box ukuran 95 untuk Penyimpanan APD dan Dokument)</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>opname_052_BSS-JOB_WS_IX_2026_-</t>
+          <t>opname_021_BSS-JOB_WS_IX_2026_4500011795</t>
         </is>
       </c>
       <c r="B132" t="inlineStr"/>
       <c r="C132" t="inlineStr"/>
       <c r="D132" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -6945,14 +6947,14 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G132" t="n">
         <v>1</v>
       </c>
       <c r="H132" t="n">
-        <v>8625000</v>
+        <v>115000</v>
       </c>
       <c r="I132" t="n">
         <v>0</v>
@@ -6962,25 +6964,25 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>052/BSS-JOB/WS/IX/2026</t>
+          <t>021/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011795</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
         <is>
           <t>PROVISIONAL SUM
-At Cost + Fee 15% (Provisional SUM  Pengiriman Barang  Pup Joint dari Pertamina EP Cepu ke Lamda Multi Dinamika Yard di Bogor)</t>
+At Cost + Fee 15% (Kontainer box ukuran 52 untuk Penyimpanan APD dan Dokument)</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>opname_002_BSS-JOB_WS_I_2026_4500011794</t>
+          <t>opname_012_BSS-JOB_WS_VIII_2026_4500011586</t>
         </is>
       </c>
       <c r="B133" t="inlineStr"/>
@@ -6995,48 +6997,48 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="G133" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="H133" t="n">
-        <v>11500</v>
+        <v>24150000</v>
       </c>
       <c r="I133" t="n">
         <v>0</v>
       </c>
       <c r="J133" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>002/BSS-JOB/WS/I/2026</t>
+          <t>012/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>4500011794</t>
+          <t>4500011586</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
         <is>
           <t>PROVISIONAL SUM
-At Cost + Fee 15% (Garam Kasar Untuk Pekerjaan Sealant di Cluster B)</t>
+At Cost + Fee 15% (Meeting package pelatihan HSE untuk kegiatan wellservices 2026)</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>opname_002_BSS-JOB_WS_I_2026_4500011794</t>
+          <t>opname_016_BSS-JOB_WS_VIII_2026_4500011739</t>
         </is>
       </c>
       <c r="B134" t="inlineStr"/>
       <c r="C134" t="inlineStr"/>
       <c r="D134" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -7045,48 +7047,48 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G134" t="n">
-        <v>50</v>
+        <v>18300</v>
       </c>
       <c r="H134" t="n">
-        <v>17250</v>
+        <v>65000</v>
       </c>
       <c r="I134" t="n">
         <v>0</v>
       </c>
       <c r="J134" t="n">
-        <v>50</v>
+        <v>2578</v>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>002/BSS-JOB/WS/I/2026</t>
+          <t>016/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>4500011794</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM
-At Cost + Fee 15% (Belerang Untuk Pekerjaan Sealant di Cluster B)</t>
+          <t>ADDITIONAL CAMP SERVICES
+operational consumption (ADDITIONAL CAMP SERVICES, Operational Consumption)</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>opname_021_BSS-JOB_WS_IX_2026_4500011795</t>
+          <t>opname_016_BSS-JOB_WS_VIII_2026_4500011739</t>
         </is>
       </c>
       <c r="B135" t="inlineStr"/>
       <c r="C135" t="inlineStr"/>
       <c r="D135" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
@@ -7095,48 +7097,48 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G135" t="n">
-        <v>2</v>
+        <v>9200</v>
       </c>
       <c r="H135" t="n">
-        <v>201250</v>
+        <v>33000</v>
       </c>
       <c r="I135" t="n">
         <v>0</v>
       </c>
       <c r="J135" t="n">
-        <v>2</v>
+        <v>1157</v>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>021/BSS-JOB/WS/IX/2026</t>
+          <t>016/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>4500011795</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM
-At Cost + Fee 15% (Kontainer box ukuran 95 untuk Penyimpanan APD dan Dokument)</t>
+          <t>ADDITIONAL CAMP SERVICES
+Operational side consumption (ADDITIONAL CAMP SERVICES, Operational side consumption)</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>opname_021_BSS-JOB_WS_IX_2026_4500011795</t>
+          <t>opname_038_BSS-JOB_WS_IX_2026_4500011739</t>
         </is>
       </c>
       <c r="B136" t="inlineStr"/>
       <c r="C136" t="inlineStr"/>
       <c r="D136" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
@@ -7145,48 +7147,48 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G136" t="n">
-        <v>1</v>
+        <v>18300</v>
       </c>
       <c r="H136" t="n">
-        <v>115000</v>
+        <v>65000</v>
       </c>
       <c r="I136" t="n">
-        <v>0</v>
+        <v>2578</v>
       </c>
       <c r="J136" t="n">
-        <v>1</v>
+        <v>3195</v>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>021/BSS-JOB/WS/IX/2026</t>
+          <t>038/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>4500011795</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM
-At Cost + Fee 15% (Kontainer box ukuran 52 untuk Penyimpanan APD dan Dokument)</t>
+          <t>ADDITIONAL CAMP SERVICES
+operational consumption (DDITIONAL CAMP SERVICES, Operational Consumption)</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>opname_012_BSS-JOB_WS_VIII_2026_4500011586</t>
+          <t>opname_038_BSS-JOB_WS_IX_2026_4500011739</t>
         </is>
       </c>
       <c r="B137" t="inlineStr"/>
       <c r="C137" t="inlineStr"/>
       <c r="D137" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
@@ -7195,35 +7197,35 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G137" t="n">
-        <v>1</v>
+        <v>9200</v>
       </c>
       <c r="H137" t="n">
-        <v>24150000</v>
+        <v>33000</v>
       </c>
       <c r="I137" t="n">
-        <v>0</v>
+        <v>1157</v>
       </c>
       <c r="J137" t="n">
-        <v>1</v>
+        <v>1488</v>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>012/BSS-JOB/WS/VIII/2026</t>
+          <t>038/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>4500011586</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM
-At Cost + Fee 15% (Meeting package pelatihan HSE untuk kegiatan wellservices 2026)</t>
+          <t>ADDITIONAL CAMP SERVICES
+Operational side consumption (ADDITIONAL CAMP SERVICES, Operational side consumption)</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_opname_parameter.xlsx
+++ b/database_penyimpanan_aman/database_opname_parameter.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M137"/>
+  <dimension ref="A1:M172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5582,7 +5582,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>opname_039_BSS-JOB_WS_VIII_2026_4500011739</t>
+          <t>opname_039A_BSS-JOB_WS_VIII_2026_-</t>
         </is>
       </c>
       <c r="B105" t="inlineStr"/>
@@ -5601,10 +5601,10 @@
         </is>
       </c>
       <c r="G105" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H105" t="n">
-        <v>7500000</v>
+        <v>7600000</v>
       </c>
       <c r="I105" t="n">
         <v>0</v>
@@ -5614,25 +5614,25 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>039/BSS-JOB/WS/VIII/2026</t>
+          <t>039A/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL
-Mobilization/ Demobilization of Rental Equipments (Genset/ Air Compressor/ Light Tower/ Fuel Tank, etc) to/from Company Wellsite/ Contractor base (Tronton Muat Mesin Genset dan Light tower dari Lamo ke Cluster B)</t>
+          <t>ADDITIONAL CAMP SERVICES
+Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base (Trailler 40 feet Mobilisasi Portacamp Office dari Lamo ke Cluster B)</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>opname_039_BSS-JOB_WS_VIII_2026_4500011739</t>
+          <t>opname_039A_BSS-JOB_WS_VIII_2026_-</t>
         </is>
       </c>
       <c r="B106" t="inlineStr"/>
@@ -5651,10 +5651,10 @@
         </is>
       </c>
       <c r="G106" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H106" t="n">
-        <v>7500000</v>
+        <v>7600000</v>
       </c>
       <c r="I106" t="n">
         <v>0</v>
@@ -5664,25 +5664,25 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>039/BSS-JOB/WS/VIII/2026</t>
+          <t>039A/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL
-Mobilization/ Demobilization of Rental Equipments (Genset/ Air Compressor/ Light Tower/ Fuel Tank, etc) to/from Company Wellsite/ Contractor base (Tronton Muat  Tenda, Meja, Kursi dan Counter Weight dari Lamo ke Cluster B)</t>
+          <t>ADDITIONAL CAMP SERVICES
+Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base (Trailler 40 feet Mobilisasi Portacamp Sleeper  dari Lamo ke Cluster B)</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>opname_039A_BSS-JOB_WS_VIII_2026_-</t>
+          <t>opname_039B_BSS-JOB_WS_VIII_2026_-</t>
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
@@ -5697,14 +5697,14 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G107" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H107" t="n">
-        <v>7600000</v>
+        <v>5290000</v>
       </c>
       <c r="I107" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>039A/BSS-JOB/WS/VIII/2026</t>
+          <t>039B/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -5724,15 +5724,15 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES
-Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base (Trailler 40 feet Mobilisasi Portacamp Office dari Lamo ke Cluster B)</t>
+          <t>LAND TRANSPORTATION
+trailer 20" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver (Tronton DN 8639 CH muat tenda, meja - kursi dan Counter Weight)</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>opname_039A_BSS-JOB_WS_VIII_2026_-</t>
+          <t>opname_039B_BSS-JOB_WS_VIII_2026_-</t>
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
@@ -5747,14 +5747,14 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G108" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H108" t="n">
-        <v>7600000</v>
+        <v>5290000</v>
       </c>
       <c r="I108" t="n">
         <v>0</v>
@@ -5764,7 +5764,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>039A/BSS-JOB/WS/VIII/2026</t>
+          <t>039B/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -5774,8 +5774,8 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES
-Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base (Trailler 40 feet Mobilisasi Portacamp Sleeper  dari Lamo ke Cluster B)</t>
+          <t>LAND TRANSPORTATION
+trailer 20" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver (Tronton DN 8140 CA Muat Mesin Genset 2 unit, Lighting tower 2 unit dan panel Listrik)</t>
         </is>
       </c>
     </row>
@@ -5788,7 +5788,7 @@
       <c r="B109" t="inlineStr"/>
       <c r="C109" t="inlineStr"/>
       <c r="D109" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -5804,7 +5804,7 @@
         <v>1</v>
       </c>
       <c r="H109" t="n">
-        <v>5290000</v>
+        <v>6555000</v>
       </c>
       <c r="I109" t="n">
         <v>0</v>
@@ -5825,7 +5825,7 @@
       <c r="M109" t="inlineStr">
         <is>
           <t>LAND TRANSPORTATION
-trailer 20" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver (Tronton DN 8639 CH muat tenda, meja - kursi dan Counter Weight)</t>
+trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver (Trailler 40 feet DN 8785 RA muat equipment well services)</t>
         </is>
       </c>
     </row>
@@ -5838,7 +5838,7 @@
       <c r="B110" t="inlineStr"/>
       <c r="C110" t="inlineStr"/>
       <c r="D110" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -5854,7 +5854,7 @@
         <v>1</v>
       </c>
       <c r="H110" t="n">
-        <v>5290000</v>
+        <v>6555000</v>
       </c>
       <c r="I110" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       <c r="M110" t="inlineStr">
         <is>
           <t>LAND TRANSPORTATION
-trailer 20" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver (Tronton DN 8140 CA Muat Mesin Genset 2 unit, Lighting tower 2 unit dan panel Listrik)</t>
+trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver (Trailler 40 feet DN 8950 RA muat Portacamp sleeper 40 feet)</t>
         </is>
       </c>
     </row>
@@ -5888,7 +5888,7 @@
       <c r="B111" t="inlineStr"/>
       <c r="C111" t="inlineStr"/>
       <c r="D111" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -5925,20 +5925,20 @@
       <c r="M111" t="inlineStr">
         <is>
           <t>LAND TRANSPORTATION
-trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver (Trailler 40 feet DN 8785 RA muat equipment well services)</t>
+trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver (Trailler 40 feet DN 8959 RA muat Portacamp Office 40 feet)</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>opname_039B_BSS-JOB_WS_VIII_2026_-</t>
+          <t>opname_039C_BSS-JOB_WS_VIII_2026_-</t>
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
       <c r="C112" t="inlineStr"/>
       <c r="D112" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -5947,14 +5947,14 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G112" t="n">
         <v>1</v>
       </c>
       <c r="H112" t="n">
-        <v>6555000</v>
+        <v>5290000</v>
       </c>
       <c r="I112" t="n">
         <v>0</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>039B/BSS-JOB/WS/VIII/2026</t>
+          <t>039C/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -5975,20 +5975,20 @@
       <c r="M112" t="inlineStr">
         <is>
           <t>LAND TRANSPORTATION
-trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver (Trailler 40 feet DN 8950 RA muat Portacamp sleeper 40 feet)</t>
+trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver (tronton DN 8639 CH muat tenda, meja-kursi, Counter Weight ABC)</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>opname_039B_BSS-JOB_WS_VIII_2026_-</t>
+          <t>opname_039C_BSS-JOB_WS_VIII_2026_-</t>
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
       <c r="C113" t="inlineStr"/>
       <c r="D113" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -5997,14 +5997,14 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G113" t="n">
         <v>1</v>
       </c>
       <c r="H113" t="n">
-        <v>6555000</v>
+        <v>5290000</v>
       </c>
       <c r="I113" t="n">
         <v>0</v>
@@ -6014,7 +6014,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>039B/BSS-JOB/WS/VIII/2026</t>
+          <t>039C/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -6025,7 +6025,7 @@
       <c r="M113" t="inlineStr">
         <is>
           <t>LAND TRANSPORTATION
-trailer 40" atau tronton 15 ton, call out, Cluster Senoro 6 - Cluster B atau sebaliknya c/w BBM &amp; driver (Trailler 40 feet DN 8959 RA muat Portacamp Office 40 feet)</t>
+trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver (Tronton DN 8140 CA Muat Mesin Genset 2 unit, Lighting tower 2 unit dan panel Listrik)</t>
         </is>
       </c>
     </row>
@@ -6038,7 +6038,7 @@
       <c r="B114" t="inlineStr"/>
       <c r="C114" t="inlineStr"/>
       <c r="D114" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -6054,7 +6054,7 @@
         <v>1</v>
       </c>
       <c r="H114" t="n">
-        <v>5290000</v>
+        <v>6555000</v>
       </c>
       <c r="I114" t="n">
         <v>0</v>
@@ -6075,7 +6075,7 @@
       <c r="M114" t="inlineStr">
         <is>
           <t>LAND TRANSPORTATION
-trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver (tronton DN 8639 CH muat tenda, meja-kursi, Counter Weight ABC)</t>
+trailer 40" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver (Trailler 40 feet DN 8950 RA muat Equipment Well Services)</t>
         </is>
       </c>
     </row>
@@ -6088,7 +6088,7 @@
       <c r="B115" t="inlineStr"/>
       <c r="C115" t="inlineStr"/>
       <c r="D115" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -6104,7 +6104,7 @@
         <v>1</v>
       </c>
       <c r="H115" t="n">
-        <v>5290000</v>
+        <v>7600000</v>
       </c>
       <c r="I115" t="n">
         <v>0</v>
@@ -6124,8 +6124,8 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>LAND TRANSPORTATION
-trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver (Tronton DN 8140 CA Muat Mesin Genset 2 unit, Lighting tower 2 unit dan panel Listrik)</t>
+          <t>ADDITIONAL CAMP SERVICES
+Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base (Trailler 40 feet DN 8785 RA Demobilisasi portacamp Sleeper 40 feet  dari Senoro 2 ke Lamo)</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       <c r="B116" t="inlineStr"/>
       <c r="C116" t="inlineStr"/>
       <c r="D116" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -6154,7 +6154,7 @@
         <v>1</v>
       </c>
       <c r="H116" t="n">
-        <v>6555000</v>
+        <v>7600000</v>
       </c>
       <c r="I116" t="n">
         <v>0</v>
@@ -6174,21 +6174,21 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>LAND TRANSPORTATION
-trailer 40" atau tronton 15 ton, call out, Cluster Senoro 2 - Cluster Senoro 6 atau sebaliknya c/w BBM &amp; driver (Trailler 40 feet DN 8950 RA muat Equipment Well Services)</t>
+          <t>ADDITIONAL CAMP SERVICES
+Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base (Trailler 40 feet DN 8959 RA  Demobilisasi portacamp Office 40 feet  dari Senoro 2 ke Lamo)</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>opname_039C_BSS-JOB_WS_VIII_2026_-</t>
+          <t>opname_039D_BSS-JOB_WS_VIII_2026_-</t>
         </is>
       </c>
       <c r="B117" t="inlineStr"/>
       <c r="C117" t="inlineStr"/>
       <c r="D117" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -6197,7 +6197,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -6214,7 +6214,7 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>039C/BSS-JOB/WS/VIII/2026</t>
+          <t>039D/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -6225,20 +6225,20 @@
       <c r="M117" t="inlineStr">
         <is>
           <t>ADDITIONAL CAMP SERVICES
-Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base (Trailler 40 feet DN 8785 RA Demobilisasi portacamp Sleeper 40 feet  dari Senoro 2 ke Lamo)</t>
+Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base (Trailler 40 feet DN 8785 RA mobilisasi Portacamp office dari Lamo ke Senoro)</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>opname_039C_BSS-JOB_WS_VIII_2026_-</t>
+          <t>opname_039D_BSS-JOB_WS_VIII_2026_-</t>
         </is>
       </c>
       <c r="B118" t="inlineStr"/>
       <c r="C118" t="inlineStr"/>
       <c r="D118" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -6247,7 +6247,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -6264,7 +6264,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>039C/BSS-JOB/WS/VIII/2026</t>
+          <t>039D/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -6275,7 +6275,7 @@
       <c r="M118" t="inlineStr">
         <is>
           <t>ADDITIONAL CAMP SERVICES
-Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base (Trailler 40 feet DN 8959 RA  Demobilisasi portacamp Office 40 feet  dari Senoro 2 ke Lamo)</t>
+Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base (Trailler 40 feet DN 8959 RA mobilisasi Portacamp Sleeper  dari Lamo ke Senoro)</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       <c r="B119" t="inlineStr"/>
       <c r="C119" t="inlineStr"/>
       <c r="D119" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -6304,7 +6304,7 @@
         <v>1</v>
       </c>
       <c r="H119" t="n">
-        <v>7600000</v>
+        <v>5520000</v>
       </c>
       <c r="I119" t="n">
         <v>0</v>
@@ -6324,21 +6324,21 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES
-Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base (Trailler 40 feet DN 8785 RA mobilisasi Portacamp office dari Lamo ke Senoro)</t>
+          <t>LAND TRANSPORTATION
+trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Contractor's alternative jetty atau sebaliknya c/w BBM &amp; driver (Tronton 20 feet DN 9639 CH dari Lamo ke Senoro 2 pindahkan Barang TGE di lokasi senoro 2)</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>opname_039D_BSS-JOB_WS_VIII_2026_-</t>
+          <t>opname_046_BSS-JOB_WS_IX_2026_4500011739</t>
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
       <c r="C120" t="inlineStr"/>
       <c r="D120" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -6347,48 +6347,48 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G120" t="n">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="H120" t="n">
-        <v>7600000</v>
+        <v>1600000</v>
       </c>
       <c r="I120" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J120" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>039D/BSS-JOB/WS/VIII/2026</t>
+          <t>046/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES
-Mobilization/ Demobilization 40 ft Additional Camp to/from Company Wellsite/ Contractor base (Trailler 40 feet DN 8959 RA mobilisasi Portacamp Sleeper  dari Lamo ke Senoro)</t>
+          <t>CAR &amp; TANSPORTATION
+Station wagon 7 seater diesel engine + driver + BBM, (Kendaraan Inova DN 1259 CL  Support Well Services Periode tanggal 01 sd 30 September 2026)</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>opname_039D_BSS-JOB_WS_VIII_2026_-</t>
+          <t>opname_046_BSS-JOB_WS_IX_2026_4500011739</t>
         </is>
       </c>
       <c r="B121" t="inlineStr"/>
       <c r="C121" t="inlineStr"/>
       <c r="D121" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -6397,35 +6397,35 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G121" t="n">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="H121" t="n">
-        <v>5520000</v>
+        <v>1600000</v>
       </c>
       <c r="I121" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J121" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>039D/BSS-JOB/WS/VIII/2026</t>
+          <t>046/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>LAND TRANSPORTATION
-trailer 20" atau tronton 15 ton, call out, Cluster Senoro 2 - Contractor's alternative jetty atau sebaliknya c/w BBM &amp; driver (Tronton 20 feet DN 9639 CH dari Lamo ke Senoro 2 pindahkan Barang TGE di lokasi senoro 2)</t>
+          <t>CAR &amp; TANSPORTATION
+Station wagon 7 seater diesel engine + driver + BBM, (Kendaraan Inova DN 1257 CL  Support Well Services Periode tanggal 01 sd 30 September 2026)</t>
         </is>
       </c>
     </row>
@@ -6438,7 +6438,7 @@
       <c r="B122" t="inlineStr"/>
       <c r="C122" t="inlineStr"/>
       <c r="D122" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -6457,10 +6457,10 @@
         <v>1600000</v>
       </c>
       <c r="I122" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J122" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="K122" t="inlineStr">
         <is>
@@ -6475,7 +6475,7 @@
       <c r="M122" t="inlineStr">
         <is>
           <t>CAR &amp; TANSPORTATION
-Station wagon 7 seater diesel engine + driver + BBM, (Kendaraan Inova DN 1259 CL  Support Well Services Periode tanggal 01 sd 30 September 2026)</t>
+Station wagon 7 seater diesel engine + driver + BBM, (Kendaraan Inova DN 1258 CL  Support Well Services Periode tanggal 27 sd 30 September 2026)</t>
         </is>
       </c>
     </row>
@@ -6488,7 +6488,7 @@
       <c r="B123" t="inlineStr"/>
       <c r="C123" t="inlineStr"/>
       <c r="D123" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -6507,7 +6507,7 @@
         <v>1600000</v>
       </c>
       <c r="I123" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J123" t="n">
         <v>30</v>
@@ -6525,7 +6525,7 @@
       <c r="M123" t="inlineStr">
         <is>
           <t>CAR &amp; TANSPORTATION
-Station wagon 7 seater diesel engine + driver + BBM, (Kendaraan Inova DN 1257 CL  Support Well Services Periode tanggal 01 sd 30 September 2026)</t>
+Double cabin 4x4, diesel engine + driver + BBM, (Kendaraan Double Cabin Hilux DN 8916 CH  Support Well Services Periode tanggal 01 sd 30 September 2026)</t>
         </is>
       </c>
     </row>
@@ -6538,7 +6538,7 @@
       <c r="B124" t="inlineStr"/>
       <c r="C124" t="inlineStr"/>
       <c r="D124" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -6557,10 +6557,10 @@
         <v>1600000</v>
       </c>
       <c r="I124" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J124" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="K124" t="inlineStr">
         <is>
@@ -6575,20 +6575,20 @@
       <c r="M124" t="inlineStr">
         <is>
           <t>CAR &amp; TANSPORTATION
-Station wagon 7 seater diesel engine + driver + BBM, (Kendaraan Inova DN 1258 CL  Support Well Services Periode tanggal 27 sd 30 September 2026)</t>
+Double cabin 4x4, diesel engine + driver + BBM, (Kendaraan Double Cabin Hilux DN 8917 CH  Support Well Services Periode tanggal 01 sd 30 September 2026)</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>opname_046_BSS-JOB_WS_IX_2026_4500011739</t>
+          <t>opname_051_BSS-JOB_WS_VIII_2026_-</t>
         </is>
       </c>
       <c r="B125" t="inlineStr"/>
       <c r="C125" t="inlineStr"/>
       <c r="D125" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -6597,48 +6597,48 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G125" t="n">
-        <v>120</v>
+        <v>1</v>
       </c>
       <c r="H125" t="n">
-        <v>1600000</v>
+        <v>1725000</v>
       </c>
       <c r="I125" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J125" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>046/BSS-JOB/WS/IX/2026</t>
+          <t>051/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION
-Double cabin 4x4, diesel engine + driver + BBM, (Kendaraan Double Cabin Hilux DN 8916 CH  Support Well Services Periode tanggal 01 sd 30 September 2026)</t>
+          <t>PROVISIONAL SUM
+At Cost + Fee 15% (Provisional SUM  Pengurusan Dokumen Surat Persetujuan Pengeluaran Barang (SPPB) 3 colly di Pelabuhan Batam)</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>opname_046_BSS-JOB_WS_IX_2026_4500011739</t>
+          <t>opname_052_BSS-JOB_WS_IX_2026_-</t>
         </is>
       </c>
       <c r="B126" t="inlineStr"/>
       <c r="C126" t="inlineStr"/>
       <c r="D126" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -6647,42 +6647,42 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G126" t="n">
-        <v>120</v>
+        <v>1</v>
       </c>
       <c r="H126" t="n">
-        <v>1600000</v>
+        <v>8625000</v>
       </c>
       <c r="I126" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="J126" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>046/BSS-JOB/WS/IX/2026</t>
+          <t>052/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION
-Double cabin 4x4, diesel engine + driver + BBM, (Kendaraan Double Cabin Hilux DN 8917 CH  Support Well Services Periode tanggal 01 sd 30 September 2026)</t>
+          <t>PROVISIONAL SUM
+At Cost + Fee 15% (Provisional SUM  Pengiriman Barang  Pup Joint dari Pertamina EP Cepu ke Lamda Multi Dinamika Yard di Bogor)</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>opname_051_BSS-JOB_WS_VIII_2026_-</t>
+          <t>opname_002_BSS-JOB_WS_I_2026_4500011794</t>
         </is>
       </c>
       <c r="B127" t="inlineStr"/>
@@ -6697,48 +6697,48 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="G127" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="H127" t="n">
-        <v>1725000</v>
+        <v>11500</v>
       </c>
       <c r="I127" t="n">
         <v>0</v>
       </c>
       <c r="J127" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>051/BSS-JOB/WS/VIII/2026</t>
+          <t>002/BSS-JOB/WS/I/2026</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011794</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
         <is>
           <t>PROVISIONAL SUM
-At Cost + Fee 15% (Provisional SUM  Pengurusan Dokumen Surat Persetujuan Pengeluaran Barang (SPPB) 3 colly di Pelabuhan Batam)</t>
+At Cost + Fee 15% (Garam Kasar Untuk Pekerjaan Sealant di Cluster B)</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>opname_052_BSS-JOB_WS_IX_2026_-</t>
+          <t>opname_002_BSS-JOB_WS_I_2026_4500011794</t>
         </is>
       </c>
       <c r="B128" t="inlineStr"/>
       <c r="C128" t="inlineStr"/>
       <c r="D128" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
@@ -6747,42 +6747,42 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="G128" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="H128" t="n">
-        <v>8625000</v>
+        <v>17250</v>
       </c>
       <c r="I128" t="n">
         <v>0</v>
       </c>
       <c r="J128" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>052/BSS-JOB/WS/IX/2026</t>
+          <t>002/BSS-JOB/WS/I/2026</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4500011794</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
         <is>
           <t>PROVISIONAL SUM
-At Cost + Fee 15% (Provisional SUM  Pengiriman Barang  Pup Joint dari Pertamina EP Cepu ke Lamda Multi Dinamika Yard di Bogor)</t>
+At Cost + Fee 15% (Belerang Untuk Pekerjaan Sealant di Cluster B)</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>opname_002_BSS-JOB_WS_I_2026_4500011794</t>
+          <t>opname_021_BSS-JOB_WS_IX_2026_4500011795</t>
         </is>
       </c>
       <c r="B129" t="inlineStr"/>
@@ -6797,42 +6797,42 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G129" t="n">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="H129" t="n">
-        <v>11500</v>
+        <v>201250</v>
       </c>
       <c r="I129" t="n">
         <v>0</v>
       </c>
       <c r="J129" t="n">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>002/BSS-JOB/WS/I/2026</t>
+          <t>021/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>4500011794</t>
+          <t>4500011795</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
         <is>
           <t>PROVISIONAL SUM
-At Cost + Fee 15% (Garam Kasar Untuk Pekerjaan Sealant di Cluster B)</t>
+At Cost + Fee 15% (Kontainer box ukuran 95 untuk Penyimpanan APD dan Dokument)</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>opname_002_BSS-JOB_WS_I_2026_4500011794</t>
+          <t>opname_021_BSS-JOB_WS_IX_2026_4500011795</t>
         </is>
       </c>
       <c r="B130" t="inlineStr"/>
@@ -6847,42 +6847,42 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G130" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="H130" t="n">
-        <v>17250</v>
+        <v>115000</v>
       </c>
       <c r="I130" t="n">
         <v>0</v>
       </c>
       <c r="J130" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>002/BSS-JOB/WS/I/2026</t>
+          <t>021/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>4500011794</t>
+          <t>4500011795</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
         <is>
           <t>PROVISIONAL SUM
-At Cost + Fee 15% (Belerang Untuk Pekerjaan Sealant di Cluster B)</t>
+At Cost + Fee 15% (Kontainer box ukuran 52 untuk Penyimpanan APD dan Dokument)</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>opname_021_BSS-JOB_WS_IX_2026_4500011795</t>
+          <t>opname_012_BSS-JOB_WS_VIII_2026_4500011586</t>
         </is>
       </c>
       <c r="B131" t="inlineStr"/>
@@ -6897,48 +6897,48 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="G131" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H131" t="n">
-        <v>201250</v>
+        <v>24150000</v>
       </c>
       <c r="I131" t="n">
         <v>0</v>
       </c>
       <c r="J131" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>021/BSS-JOB/WS/IX/2026</t>
+          <t>012/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>4500011795</t>
+          <t>4500011586</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
         <is>
           <t>PROVISIONAL SUM
-At Cost + Fee 15% (Kontainer box ukuran 95 untuk Penyimpanan APD dan Dokument)</t>
+At Cost + Fee 15% (Meeting package pelatihan HSE untuk kegiatan wellservices 2026)</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>opname_021_BSS-JOB_WS_IX_2026_4500011795</t>
+          <t>opname_016_BSS-JOB_WS_VIII_2026_4500011739</t>
         </is>
       </c>
       <c r="B132" t="inlineStr"/>
       <c r="C132" t="inlineStr"/>
       <c r="D132" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -6947,48 +6947,48 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G132" t="n">
-        <v>1</v>
+        <v>18300</v>
       </c>
       <c r="H132" t="n">
-        <v>115000</v>
+        <v>65000</v>
       </c>
       <c r="I132" t="n">
         <v>0</v>
       </c>
       <c r="J132" t="n">
-        <v>1</v>
+        <v>2578</v>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>021/BSS-JOB/WS/IX/2026</t>
+          <t>016/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>4500011795</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM
-At Cost + Fee 15% (Kontainer box ukuran 52 untuk Penyimpanan APD dan Dokument)</t>
+          <t>ADDITIONAL CAMP SERVICES
+operational consumption (ADDITIONAL CAMP SERVICES, Operational Consumption)</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>opname_012_BSS-JOB_WS_VIII_2026_4500011586</t>
+          <t>opname_016_BSS-JOB_WS_VIII_2026_4500011739</t>
         </is>
       </c>
       <c r="B133" t="inlineStr"/>
       <c r="C133" t="inlineStr"/>
       <c r="D133" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -6997,42 +6997,42 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G133" t="n">
-        <v>1</v>
+        <v>9200</v>
       </c>
       <c r="H133" t="n">
-        <v>24150000</v>
+        <v>33000</v>
       </c>
       <c r="I133" t="n">
         <v>0</v>
       </c>
       <c r="J133" t="n">
-        <v>1</v>
+        <v>1157</v>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>012/BSS-JOB/WS/VIII/2026</t>
+          <t>016/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>4500011586</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM
-At Cost + Fee 15% (Meeting package pelatihan HSE untuk kegiatan wellservices 2026)</t>
+          <t>ADDITIONAL CAMP SERVICES
+Operational side consumption (ADDITIONAL CAMP SERVICES, Operational side consumption)</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>opname_016_BSS-JOB_WS_VIII_2026_4500011739</t>
+          <t>opname_038_BSS-JOB_WS_IX_2026_4500011739</t>
         </is>
       </c>
       <c r="B134" t="inlineStr"/>
@@ -7047,7 +7047,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -7057,14 +7057,14 @@
         <v>65000</v>
       </c>
       <c r="I134" t="n">
-        <v>0</v>
+        <v>2578</v>
       </c>
       <c r="J134" t="n">
-        <v>2578</v>
+        <v>3195</v>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>016/BSS-JOB/WS/VIII/2026</t>
+          <t>038/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -7075,14 +7075,14 @@
       <c r="M134" t="inlineStr">
         <is>
           <t>ADDITIONAL CAMP SERVICES
-operational consumption (ADDITIONAL CAMP SERVICES, Operational Consumption)</t>
+operational consumption (DDITIONAL CAMP SERVICES, Operational Consumption)</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>opname_016_BSS-JOB_WS_VIII_2026_4500011739</t>
+          <t>opname_038_BSS-JOB_WS_IX_2026_4500011739</t>
         </is>
       </c>
       <c r="B135" t="inlineStr"/>
@@ -7097,7 +7097,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -7107,14 +7107,14 @@
         <v>33000</v>
       </c>
       <c r="I135" t="n">
-        <v>0</v>
+        <v>1157</v>
       </c>
       <c r="J135" t="n">
-        <v>1157</v>
+        <v>1488</v>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>016/BSS-JOB/WS/VIII/2026</t>
+          <t>038/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -7132,7 +7132,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>opname_038_BSS-JOB_WS_IX_2026_4500011739</t>
+          <t>opname_013_BSS-JOB_WS_VIII_2026_4500011846</t>
         </is>
       </c>
       <c r="B136" t="inlineStr"/>
@@ -7147,42 +7147,42 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G136" t="n">
-        <v>18300</v>
+        <v>8</v>
       </c>
       <c r="H136" t="n">
-        <v>65000</v>
+        <v>32500</v>
       </c>
       <c r="I136" t="n">
-        <v>2578</v>
+        <v>0</v>
       </c>
       <c r="J136" t="n">
-        <v>3195</v>
+        <v>8</v>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>038/BSS-JOB/WS/IX/2026</t>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>4500011846</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES
-operational consumption (DDITIONAL CAMP SERVICES, Operational Consumption)</t>
+          <t>ESTIMATED SUM
+Indocafe Coffemix Renteng (Kebutuhan Logistic di Lapangan)</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>opname_038_BSS-JOB_WS_IX_2026_4500011739</t>
+          <t>opname_013_BSS-JOB_WS_VIII_2026_4500011846</t>
         </is>
       </c>
       <c r="B137" t="inlineStr"/>
@@ -7197,35 +7197,1785 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G137" t="n">
-        <v>9200</v>
+        <v>8</v>
       </c>
       <c r="H137" t="n">
-        <v>33000</v>
+        <v>84500</v>
       </c>
       <c r="I137" t="n">
-        <v>1157</v>
+        <v>0</v>
       </c>
       <c r="J137" t="n">
-        <v>1488</v>
+        <v>8</v>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>038/BSS-JOB/WS/IX/2026</t>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
         <is>
+          <t>4500011846</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM
+Kopi Kapal Api 380 g (Kebutuhan Logistic di Lapangan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>opname_013_BSS-JOB_WS_VIII_2026_4500011846</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr"/>
+      <c r="C138" t="inlineStr"/>
+      <c r="D138" t="n">
+        <v>3</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G138" t="n">
+        <v>9</v>
+      </c>
+      <c r="H138" t="n">
+        <v>26000</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0</v>
+      </c>
+      <c r="J138" t="n">
+        <v>9</v>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>4500011846</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM
+Nescafe Classic renteng (Kebutuhan Logistic di Lapangan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>opname_013_BSS-JOB_WS_VIII_2026_4500011846</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr"/>
+      <c r="C139" t="inlineStr"/>
+      <c r="D139" t="n">
+        <v>4</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G139" t="n">
+        <v>72</v>
+      </c>
+      <c r="H139" t="n">
+        <v>9750</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0</v>
+      </c>
+      <c r="J139" t="n">
+        <v>72</v>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>4500011846</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM
+Pop Mie (Kebutuhan Logistic di Lapangan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>opname_013_BSS-JOB_WS_VIII_2026_4500011846</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr"/>
+      <c r="C140" t="inlineStr"/>
+      <c r="D140" t="n">
+        <v>5</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G140" t="n">
+        <v>12</v>
+      </c>
+      <c r="H140" t="n">
+        <v>19500</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0</v>
+      </c>
+      <c r="J140" t="n">
+        <v>12</v>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>4500011846</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM
+Chitato 68 g (Kebutuhan Logistic di Lapangan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>opname_013_BSS-JOB_WS_VIII_2026_4500011846</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr"/>
+      <c r="C141" t="inlineStr"/>
+      <c r="D141" t="n">
+        <v>6</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G141" t="n">
+        <v>72</v>
+      </c>
+      <c r="H141" t="n">
+        <v>13000</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0</v>
+      </c>
+      <c r="J141" t="n">
+        <v>72</v>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>4500011846</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM
+Pocari Sweat (Kebutuhan Logistic di Lapangan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>opname_013_BSS-JOB_WS_VIII_2026_4500011846</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr"/>
+      <c r="C142" t="inlineStr"/>
+      <c r="D142" t="n">
+        <v>7</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G142" t="n">
+        <v>72</v>
+      </c>
+      <c r="H142" t="n">
+        <v>9750</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0</v>
+      </c>
+      <c r="J142" t="n">
+        <v>72</v>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>4500011846</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM
+Teh Kotak (Kebutuhan Logistic di Lapangan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>opname_013_BSS-JOB_WS_VIII_2026_4500011846</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr"/>
+      <c r="C143" t="inlineStr"/>
+      <c r="D143" t="n">
+        <v>8</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G143" t="n">
+        <v>72</v>
+      </c>
+      <c r="H143" t="n">
+        <v>19500</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0</v>
+      </c>
+      <c r="J143" t="n">
+        <v>72</v>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>4500011846</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM
+Susu Beruang (Kebutuhan Logistic di Lapangan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>opname_013_BSS-JOB_WS_VIII_2026_4500011846</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr"/>
+      <c r="C144" t="inlineStr"/>
+      <c r="D144" t="n">
+        <v>9</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G144" t="n">
+        <v>36</v>
+      </c>
+      <c r="H144" t="n">
+        <v>32500</v>
+      </c>
+      <c r="I144" t="n">
+        <v>0</v>
+      </c>
+      <c r="J144" t="n">
+        <v>36</v>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>4500011846</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM
+Roti Sari Roti Coklat (Kebutuhan Logistic di Lapangan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>opname_013_BSS-JOB_WS_VIII_2026_4500011846</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr"/>
+      <c r="C145" t="inlineStr"/>
+      <c r="D145" t="n">
+        <v>10</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G145" t="n">
+        <v>36</v>
+      </c>
+      <c r="H145" t="n">
+        <v>32500</v>
+      </c>
+      <c r="I145" t="n">
+        <v>0</v>
+      </c>
+      <c r="J145" t="n">
+        <v>36</v>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>4500011846</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM
+Roti Sari Roti Keju (Kebutuhan Logistic di Lapangan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>opname_013_BSS-JOB_WS_VIII_2026_4500011846</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr"/>
+      <c r="C146" t="inlineStr"/>
+      <c r="D146" t="n">
+        <v>11</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G146" t="n">
+        <v>36</v>
+      </c>
+      <c r="H146" t="n">
+        <v>32500</v>
+      </c>
+      <c r="I146" t="n">
+        <v>0</v>
+      </c>
+      <c r="J146" t="n">
+        <v>36</v>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>4500011846</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM
+Roti Tawar Sari Roti (Kebutuhan Logistic di Lapangan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>opname_013_BSS-JOB_WS_VIII_2026_4500011846</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr"/>
+      <c r="C147" t="inlineStr"/>
+      <c r="D147" t="n">
+        <v>12</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G147" t="n">
+        <v>72</v>
+      </c>
+      <c r="H147" t="n">
+        <v>15600</v>
+      </c>
+      <c r="I147" t="n">
+        <v>0</v>
+      </c>
+      <c r="J147" t="n">
+        <v>72</v>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>4500011846</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM
+Coffe Nescafe Kaleng 220 ml (Kebutuhan Logistic di Lapangan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>opname_020_BSS-JOB_WS_IX_2026_4500011844</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr"/>
+      <c r="C148" t="inlineStr"/>
+      <c r="D148" t="n">
+        <v>1</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G148" t="n">
+        <v>5</v>
+      </c>
+      <c r="H148" t="n">
+        <v>32500</v>
+      </c>
+      <c r="I148" t="n">
+        <v>0</v>
+      </c>
+      <c r="J148" t="n">
+        <v>5</v>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>020/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>4500011844</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM
+Indocafe Coffemix Renteng (Kebutuhan Additional Logistik di Lokasi Senoro)</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>opname_020_BSS-JOB_WS_IX_2026_4500011844</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr"/>
+      <c r="C149" t="inlineStr"/>
+      <c r="D149" t="n">
+        <v>2</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G149" t="n">
+        <v>6</v>
+      </c>
+      <c r="H149" t="n">
+        <v>84500</v>
+      </c>
+      <c r="I149" t="n">
+        <v>0</v>
+      </c>
+      <c r="J149" t="n">
+        <v>6</v>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>020/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>4500011844</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM
+Kopi Kapal Api 380 g (Kebutuhan Additional Logistik di Lokasi Senoro)</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>opname_020_BSS-JOB_WS_IX_2026_4500011844</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr"/>
+      <c r="C150" t="inlineStr"/>
+      <c r="D150" t="n">
+        <v>3</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G150" t="n">
+        <v>5</v>
+      </c>
+      <c r="H150" t="n">
+        <v>26000</v>
+      </c>
+      <c r="I150" t="n">
+        <v>0</v>
+      </c>
+      <c r="J150" t="n">
+        <v>5</v>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>020/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>4500011844</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM
+Nescafe Classic renteng (Kebutuhan Additional Logistik di Lokasi Senoro)</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>opname_020_BSS-JOB_WS_IX_2026_4500011844</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr"/>
+      <c r="C151" t="inlineStr"/>
+      <c r="D151" t="n">
+        <v>4</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G151" t="n">
+        <v>72</v>
+      </c>
+      <c r="H151" t="n">
+        <v>9750</v>
+      </c>
+      <c r="I151" t="n">
+        <v>0</v>
+      </c>
+      <c r="J151" t="n">
+        <v>72</v>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>020/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>4500011844</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM
+Pop Mie (Kebutuhan Additional Logistik di Lokasi Senoro)</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>opname_020_BSS-JOB_WS_IX_2026_4500011844</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr"/>
+      <c r="C152" t="inlineStr"/>
+      <c r="D152" t="n">
+        <v>5</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G152" t="n">
+        <v>10</v>
+      </c>
+      <c r="H152" t="n">
+        <v>19500</v>
+      </c>
+      <c r="I152" t="n">
+        <v>0</v>
+      </c>
+      <c r="J152" t="n">
+        <v>10</v>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>020/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>4500011844</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM
+Chitato 68 g (Kebutuhan Additional Logistik di Lokasi Senoro)</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>opname_020_BSS-JOB_WS_IX_2026_4500011844</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr"/>
+      <c r="C153" t="inlineStr"/>
+      <c r="D153" t="n">
+        <v>6</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G153" t="n">
+        <v>72</v>
+      </c>
+      <c r="H153" t="n">
+        <v>13000</v>
+      </c>
+      <c r="I153" t="n">
+        <v>0</v>
+      </c>
+      <c r="J153" t="n">
+        <v>72</v>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>020/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>4500011844</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM
+Pocari Sweat (Kebutuhan Additional Logistik di Lokasi Senoro)</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>opname_020_BSS-JOB_WS_IX_2026_4500011844</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr"/>
+      <c r="C154" t="inlineStr"/>
+      <c r="D154" t="n">
+        <v>7</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G154" t="n">
+        <v>72</v>
+      </c>
+      <c r="H154" t="n">
+        <v>9750</v>
+      </c>
+      <c r="I154" t="n">
+        <v>0</v>
+      </c>
+      <c r="J154" t="n">
+        <v>72</v>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>020/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>4500011844</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM
+Teh Kotak (Kebutuhan Additional Logistik di Lokasi Senoro)</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>opname_020_BSS-JOB_WS_IX_2026_4500011844</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr"/>
+      <c r="C155" t="inlineStr"/>
+      <c r="D155" t="n">
+        <v>8</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G155" t="n">
+        <v>72</v>
+      </c>
+      <c r="H155" t="n">
+        <v>19500</v>
+      </c>
+      <c r="I155" t="n">
+        <v>0</v>
+      </c>
+      <c r="J155" t="n">
+        <v>72</v>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>020/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>4500011844</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM
+Susu Beruang (Kebutuhan Additional Logistik di Lokasi Senoro)</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>opname_020_BSS-JOB_WS_IX_2026_4500011844</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr"/>
+      <c r="C156" t="inlineStr"/>
+      <c r="D156" t="n">
+        <v>9</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G156" t="n">
+        <v>48</v>
+      </c>
+      <c r="H156" t="n">
+        <v>15600</v>
+      </c>
+      <c r="I156" t="n">
+        <v>0</v>
+      </c>
+      <c r="J156" t="n">
+        <v>48</v>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>020/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>4500011844</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM
+Coffe Nescafe Kaleng 220 ml (Kebutuhan Additional Logistik di Lokasi Senoro)</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>opname_020_BSS-JOB_WS_IX_2026_4500011844</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr"/>
+      <c r="C157" t="inlineStr"/>
+      <c r="D157" t="n">
+        <v>10</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G157" t="n">
+        <v>10</v>
+      </c>
+      <c r="H157" t="n">
+        <v>32500</v>
+      </c>
+      <c r="I157" t="n">
+        <v>0</v>
+      </c>
+      <c r="J157" t="n">
+        <v>10</v>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>020/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>4500011844</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM
+Roti Sari Roti Coklat (Kebutuhan Additional Logistik di Lokasi Senoro)</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>opname_020_BSS-JOB_WS_IX_2026_4500011844</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr"/>
+      <c r="C158" t="inlineStr"/>
+      <c r="D158" t="n">
+        <v>11</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G158" t="n">
+        <v>10</v>
+      </c>
+      <c r="H158" t="n">
+        <v>32500</v>
+      </c>
+      <c r="I158" t="n">
+        <v>0</v>
+      </c>
+      <c r="J158" t="n">
+        <v>10</v>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>020/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>4500011844</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM
+Roti Sari Roti Keju (Kebutuhan Additional Logistik di Lokasi Senoro)</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>opname_020_BSS-JOB_WS_IX_2026_4500011844</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr"/>
+      <c r="C159" t="inlineStr"/>
+      <c r="D159" t="n">
+        <v>12</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="G159" t="n">
+        <v>10</v>
+      </c>
+      <c r="H159" t="n">
+        <v>32500</v>
+      </c>
+      <c r="I159" t="n">
+        <v>0</v>
+      </c>
+      <c r="J159" t="n">
+        <v>10</v>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>020/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>4500011844</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM
+Roti Tawar Sari Roti (Kebutuhan Additional Logistik di Lokasi Senoro)</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>opname_037_BSS-JOB_WS_IX_2026_4500011850</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr"/>
+      <c r="C160" t="inlineStr"/>
+      <c r="D160" t="n">
+        <v>1</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G160" t="n">
+        <v>5</v>
+      </c>
+      <c r="H160" t="n">
+        <v>32500</v>
+      </c>
+      <c r="I160" t="n">
+        <v>0</v>
+      </c>
+      <c r="J160" t="n">
+        <v>5</v>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>037/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>4500011850</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM
+Indocafe Coffemix Renteng (Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>opname_037_BSS-JOB_WS_IX_2026_4500011850</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr"/>
+      <c r="C161" t="inlineStr"/>
+      <c r="D161" t="n">
+        <v>2</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G161" t="n">
+        <v>6</v>
+      </c>
+      <c r="H161" t="n">
+        <v>84500</v>
+      </c>
+      <c r="I161" t="n">
+        <v>0</v>
+      </c>
+      <c r="J161" t="n">
+        <v>6</v>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>037/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>4500011850</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM
+Kopi Kapal Api 380 g (Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>opname_037_BSS-JOB_WS_IX_2026_4500011850</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr"/>
+      <c r="C162" t="inlineStr"/>
+      <c r="D162" t="n">
+        <v>3</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G162" t="n">
+        <v>5</v>
+      </c>
+      <c r="H162" t="n">
+        <v>26000</v>
+      </c>
+      <c r="I162" t="n">
+        <v>0</v>
+      </c>
+      <c r="J162" t="n">
+        <v>5</v>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>037/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>4500011850</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM
+Nescafe Classic renteng (Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>opname_037_BSS-JOB_WS_IX_2026_4500011850</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr"/>
+      <c r="C163" t="inlineStr"/>
+      <c r="D163" t="n">
+        <v>4</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G163" t="n">
+        <v>72</v>
+      </c>
+      <c r="H163" t="n">
+        <v>9750</v>
+      </c>
+      <c r="I163" t="n">
+        <v>0</v>
+      </c>
+      <c r="J163" t="n">
+        <v>72</v>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>037/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>4500011850</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM
+Pop Mie (Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>opname_037_BSS-JOB_WS_IX_2026_4500011850</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr"/>
+      <c r="C164" t="inlineStr"/>
+      <c r="D164" t="n">
+        <v>5</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G164" t="n">
+        <v>10</v>
+      </c>
+      <c r="H164" t="n">
+        <v>19500</v>
+      </c>
+      <c r="I164" t="n">
+        <v>0</v>
+      </c>
+      <c r="J164" t="n">
+        <v>10</v>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>037/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>4500011850</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM
+Chitato 68 g (Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>opname_037_BSS-JOB_WS_IX_2026_4500011850</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr"/>
+      <c r="C165" t="inlineStr"/>
+      <c r="D165" t="n">
+        <v>6</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G165" t="n">
+        <v>72</v>
+      </c>
+      <c r="H165" t="n">
+        <v>13000</v>
+      </c>
+      <c r="I165" t="n">
+        <v>0</v>
+      </c>
+      <c r="J165" t="n">
+        <v>72</v>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>037/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>4500011850</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM
+Pocari Sweat (Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>opname_037_BSS-JOB_WS_IX_2026_4500011850</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr"/>
+      <c r="C166" t="inlineStr"/>
+      <c r="D166" t="n">
+        <v>7</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G166" t="n">
+        <v>72</v>
+      </c>
+      <c r="H166" t="n">
+        <v>9750</v>
+      </c>
+      <c r="I166" t="n">
+        <v>0</v>
+      </c>
+      <c r="J166" t="n">
+        <v>72</v>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>037/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>4500011850</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM
+Teh Kotak (Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>opname_037_BSS-JOB_WS_IX_2026_4500011850</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr"/>
+      <c r="C167" t="inlineStr"/>
+      <c r="D167" t="n">
+        <v>8</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G167" t="n">
+        <v>72</v>
+      </c>
+      <c r="H167" t="n">
+        <v>19500</v>
+      </c>
+      <c r="I167" t="n">
+        <v>0</v>
+      </c>
+      <c r="J167" t="n">
+        <v>72</v>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>037/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>4500011850</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM
+Susu Beruang (Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>opname_037_BSS-JOB_WS_IX_2026_4500011850</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr"/>
+      <c r="C168" t="inlineStr"/>
+      <c r="D168" t="n">
+        <v>9</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G168" t="n">
+        <v>48</v>
+      </c>
+      <c r="H168" t="n">
+        <v>15600</v>
+      </c>
+      <c r="I168" t="n">
+        <v>0</v>
+      </c>
+      <c r="J168" t="n">
+        <v>48</v>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>037/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>4500011850</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM
+Coffe Nescafe Kaleng 220 ml (Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>opname_037_BSS-JOB_WS_IX_2026_4500011850</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr"/>
+      <c r="C169" t="inlineStr"/>
+      <c r="D169" t="n">
+        <v>10</v>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G169" t="n">
+        <v>10</v>
+      </c>
+      <c r="H169" t="n">
+        <v>32500</v>
+      </c>
+      <c r="I169" t="n">
+        <v>0</v>
+      </c>
+      <c r="J169" t="n">
+        <v>10</v>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>037/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>4500011850</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM
+Roti Sari Roti Coklat (Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>opname_037_BSS-JOB_WS_IX_2026_4500011850</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr"/>
+      <c r="C170" t="inlineStr"/>
+      <c r="D170" t="n">
+        <v>11</v>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G170" t="n">
+        <v>10</v>
+      </c>
+      <c r="H170" t="n">
+        <v>32500</v>
+      </c>
+      <c r="I170" t="n">
+        <v>0</v>
+      </c>
+      <c r="J170" t="n">
+        <v>10</v>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>037/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>4500011850</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM
+Roti Sari Roti Keju (Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>opname_037_BSS-JOB_WS_IX_2026_4500011850</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr"/>
+      <c r="C171" t="inlineStr"/>
+      <c r="D171" t="n">
+        <v>12</v>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="G171" t="n">
+        <v>10</v>
+      </c>
+      <c r="H171" t="n">
+        <v>32500</v>
+      </c>
+      <c r="I171" t="n">
+        <v>0</v>
+      </c>
+      <c r="J171" t="n">
+        <v>10</v>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>037/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>4500011850</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM
+Roti Tawar Sari Roti (Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>opname_039_BSS-JOB_WS_VIII_2026_4500011739</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr"/>
+      <c r="C172" t="inlineStr"/>
+      <c r="D172" t="n">
+        <v>1</v>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Luwuk</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="G172" t="n">
+        <v>8</v>
+      </c>
+      <c r="H172" t="n">
+        <v>7500000</v>
+      </c>
+      <c r="I172" t="n">
+        <v>0</v>
+      </c>
+      <c r="J172" t="n">
+        <v>4</v>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>039/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
           <t>4500011739</t>
         </is>
       </c>
-      <c r="M137" t="inlineStr">
-        <is>
-          <t>ADDITIONAL CAMP SERVICES
-Operational side consumption (ADDITIONAL CAMP SERVICES, Operational side consumption)</t>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL
+Mobilization/ Demobilization of Rental Equipments (Genset/ Air Compressor/ Light Tower/ Fuel Tank, etc) to/from Company Wellsite/ Contractor base (Mobilisasi 2 Unit Lighting Tower dan 2 Unit Mesin Genset 80 KVA dari Luwuk ke Senoro Cluster B)</t>
         </is>
       </c>
     </row>
